--- a/indicadores/GSF-EPUB_out.xlsx
+++ b/indicadores/GSF-EPUB_out.xlsx
@@ -8,13 +8,14 @@
   <sheets>
     <sheet name="Portada" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Data" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Correlograma" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Referencias" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Correlograma" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="177">
   <si>
     <t xml:space="preserve"/>
   </si>
@@ -70,9 +71,6 @@
     <t xml:space="preserve">Regresores</t>
   </si>
   <si>
-    <t xml:space="preserve">easter[1]</t>
-  </si>
-  <si>
     <t xml:space="preserve">Resumen del correlograma</t>
   </si>
   <si>
@@ -106,13 +104,13 @@
     <t xml:space="preserve">Fecha</t>
   </si>
   <si>
-    <t xml:space="preserve">07/11/2025</t>
+    <t xml:space="preserve">07/05/2026</t>
   </si>
   <si>
     <t xml:space="preserve">Usuario</t>
   </si>
   <si>
-    <t xml:space="preserve">pcohan</t>
+    <t xml:space="preserve">vcorvalan</t>
   </si>
   <si>
     <t xml:space="preserve">fecha</t>
@@ -458,6 +456,63 @@
   </si>
   <si>
     <t xml:space="preserve">2030T4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Referencias de las series incluidas en la hoja Data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">a_original | serie de datos brutos transformados, se importa directo desde base de datos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">a_original_fct_normal | serie original con 4 forecasts obtenidos del mejor modelo ARIMA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">a_original_fct_optimista | serie original con 4 forecasts, intervalo y límite optimista</t>
+  </si>
+  <si>
+    <t xml:space="preserve">a_original_fct_pesimista | serie original con 4 forecasts, intervalo y límite pesimista</t>
+  </si>
+  <si>
+    <t xml:space="preserve">b_d16 | salida D16 del X13-ARIMA-SEATS con los factores estacionales de la serie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c_c17 | salida C17 del X13-ARIMA-SEATS con pesos del irregular</t>
+  </si>
+  <si>
+    <t xml:space="preserve">d_d12 | salida D12 del X13-ARIMA-SEATS con el componente tendencia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">d_hp_1600 | tendencia HP de largo plazo con un lambda de 1.600</t>
+  </si>
+  <si>
+    <t xml:space="preserve">d_hp_200 | suavizado con filtro HP usando lambda de 200, sirve para determinar PG automáticos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">e_ajustada | serie ajustada por estacionalidad usando el mejor modelo (LOG o NIV según el caso)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">f_filtrada | serie ajustada por estacionalidad y corregida por irregularidad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">g_final | serie f_filtrada con o sin suavizado 2x2 según el caso (es la vieja española)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">g_final_fct_normal | a_original_fct ajustada por D16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gg_final_tctl | tasas de cambio trimestral logarítmicas de la serie g_final</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gg_var_interanual | variaciones interanuales de g_final</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gg_final_var_trimestral | variaciones trimestrales de g_final</t>
+  </si>
+  <si>
+    <t xml:space="preserve">h_irregular | g_final/d_d12 componente irregular</t>
+  </si>
+  <si>
+    <t xml:space="preserve">i_dt | g_final/d_hp_1600 desvíos respecto de la tendencia</t>
   </si>
   <si>
     <t xml:space="preserve">Coeficientes de correlación de TCTL del ICA-SFE y serie específica</t>
@@ -987,7 +1042,7 @@
         <v>17</v>
       </c>
       <c r="I6" t="s">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="J6" s="1"/>
     </row>
@@ -1005,7 +1060,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B8"/>
       <c r="C8"/>
@@ -1019,12 +1074,12 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B9"/>
       <c r="C9"/>
       <c r="D9" t="n">
-        <v>0.245138351461809</v>
+        <v>0.275871470742881</v>
       </c>
       <c r="E9"/>
       <c r="F9"/>
@@ -1035,7 +1090,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B10"/>
       <c r="C10"/>
@@ -1063,7 +1118,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B12"/>
       <c r="C12"/>
@@ -1077,12 +1132,12 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B13"/>
       <c r="C13"/>
       <c r="D13" t="n">
-        <v>0.0224831469176766</v>
+        <v>0.0223792843976097</v>
       </c>
       <c r="E13"/>
       <c r="F13"/>
@@ -1105,7 +1160,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B15"/>
       <c r="C15"/>
@@ -1119,7 +1174,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B16"/>
       <c r="C16"/>
@@ -1133,7 +1188,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B17"/>
       <c r="C17"/>
@@ -1147,12 +1202,12 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B18"/>
       <c r="C18"/>
       <c r="D18" t="n">
-        <v>0.0117139343637845</v>
+        <v>0.00704157508379751</v>
       </c>
       <c r="E18"/>
       <c r="F18"/>
@@ -1163,7 +1218,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B19"/>
       <c r="C19"/>
@@ -1177,12 +1232,12 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B20"/>
       <c r="C20"/>
       <c r="D20" t="n">
-        <v>0.951942138746262</v>
+        <v>0.79818838924137</v>
       </c>
       <c r="E20"/>
       <c r="F20"/>
@@ -1325,10 +1380,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
+        <v>28</v>
+      </c>
+      <c r="B32" t="s">
         <v>29</v>
-      </c>
-      <c r="B32" t="s">
-        <v>30</v>
       </c>
       <c r="C32"/>
       <c r="D32"/>
@@ -1341,10 +1396,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
+        <v>30</v>
+      </c>
+      <c r="B33" t="s">
         <v>31</v>
-      </c>
-      <c r="B33" t="s">
-        <v>32</v>
       </c>
       <c r="C33"/>
       <c r="D33"/>
@@ -1368,66 +1423,66 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B1" t="s">
         <v>33</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>34</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>35</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>36</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>37</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>38</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>39</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>40</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>41</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>42</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>43</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>44</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>45</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>46</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>47</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>48</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>49</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>50</v>
-      </c>
-      <c r="S1" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B2" s="2" t="n">
         <v>40.382</v>
@@ -1442,45 +1497,45 @@
         <v>40.382</v>
       </c>
       <c r="F2" s="6" t="n">
-        <v>1.05854342209245</v>
+        <v>1.03857367775495</v>
       </c>
       <c r="G2" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H2" s="8" t="n">
-        <v>38.4107867941744</v>
+        <v>38.5008451461163</v>
       </c>
       <c r="I2" s="9" t="n">
-        <v>36.8057955014891</v>
+        <v>37.0957764230862</v>
       </c>
       <c r="J2" s="10" t="n">
-        <v>37.4325593530772</v>
+        <v>37.9356008052722</v>
       </c>
       <c r="K2" s="11" t="n">
-        <v>38.1486476201192</v>
+        <v>38.8821716407183</v>
       </c>
       <c r="L2" s="12" t="n">
-        <v>38.1486476201192</v>
+        <v>38.8821716407183</v>
       </c>
       <c r="M2" s="13" t="n">
-        <v>38.5027322084586</v>
+        <v>38.8332450584347</v>
       </c>
       <c r="N2" s="14" t="n">
-        <v>38.5027322084586</v>
+        <v>38.8332450584347</v>
       </c>
       <c r="O2" s="15"/>
       <c r="P2" s="16"/>
       <c r="Q2" s="17"/>
       <c r="R2" s="18" t="n">
-        <v>1.00239373941432</v>
+        <v>1.00863357443342</v>
       </c>
       <c r="S2" s="19" t="n">
-        <v>1.04610514957898</v>
+        <v>1.04683737079748</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B3" s="2" t="n">
         <v>39.128</v>
@@ -1495,106 +1550,106 @@
         <v>39.128</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>0.997885756710282</v>
+        <v>1.01013564306276</v>
       </c>
       <c r="G3" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H3" s="8" t="n">
-        <v>38.8346748967453</v>
+        <v>39.2614676525879</v>
       </c>
       <c r="I3" s="9" t="n">
-        <v>37.301210044943</v>
+        <v>37.555113815482</v>
       </c>
       <c r="J3" s="10" t="n">
-        <v>37.6196442078579</v>
+        <v>38.0391454880525</v>
       </c>
       <c r="K3" s="11" t="n">
-        <v>39.2109013851373</v>
+        <v>38.7353918938676</v>
       </c>
       <c r="L3" s="12" t="n">
-        <v>39.2109013851373</v>
+        <v>38.7353918938676</v>
       </c>
       <c r="M3" s="13" t="n">
-        <v>38.8538928640858</v>
+        <v>39.2547224378267</v>
       </c>
       <c r="N3" s="14" t="n">
-        <v>38.8538928640858</v>
+        <v>39.2547224378267</v>
       </c>
       <c r="O3" s="15" t="n">
-        <v>0.0090790689862916</v>
+        <v>0.0107950427165192</v>
       </c>
       <c r="P3" s="16"/>
       <c r="Q3" s="17" t="n">
-        <v>0.0091204087472545</v>
+        <v>0.0108535194202231</v>
       </c>
       <c r="R3" s="18" t="n">
-        <v>1.00049486618316</v>
+        <v>0.999828197590043</v>
       </c>
       <c r="S3" s="19" t="n">
-        <v>1.0416255348626</v>
+        <v>1.04525638321043</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>38.6315</v>
+        <v>41.255</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>38.6315</v>
+        <v>41.255</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>38.6315</v>
+        <v>41.255</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>38.6315</v>
+        <v>41.255</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>0.994500697640079</v>
+        <v>1.01448548243033</v>
       </c>
       <c r="G4" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H4" s="8" t="n">
-        <v>39.3953016702167</v>
+        <v>40.4432576245915</v>
       </c>
       <c r="I4" s="9" t="n">
-        <v>37.7974638709711</v>
+        <v>38.0155677048888</v>
       </c>
       <c r="J4" s="10" t="n">
-        <v>37.8103095039738</v>
+        <v>38.14742302501</v>
       </c>
       <c r="K4" s="11" t="n">
-        <v>38.8451210659494</v>
+        <v>40.6659343228534</v>
       </c>
       <c r="L4" s="12" t="n">
-        <v>38.8451210659494</v>
+        <v>40.6659343228534</v>
       </c>
       <c r="M4" s="13" t="n">
-        <v>39.264993058892</v>
+        <v>40.1995920351714</v>
       </c>
       <c r="N4" s="14" t="n">
-        <v>39.264993058892</v>
+        <v>40.1995920351714</v>
       </c>
       <c r="O4" s="15" t="n">
-        <v>0.0105250858353628</v>
+        <v>0.023785093316432</v>
       </c>
       <c r="P4" s="16"/>
       <c r="Q4" s="17" t="n">
-        <v>0.0105806693873434</v>
+        <v>0.0240702147070626</v>
       </c>
       <c r="R4" s="18" t="n">
-        <v>0.996692280404004</v>
+        <v>0.993975124563854</v>
       </c>
       <c r="S4" s="19" t="n">
-        <v>1.0388261284654</v>
+        <v>1.05745078824646</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B5" s="2" t="n">
         <v>38.135</v>
@@ -1609,49 +1664,49 @@
         <v>38.135</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>0.949604388795387</v>
+        <v>0.93626228811317</v>
       </c>
       <c r="G5" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H5" s="8" t="n">
-        <v>39.8360081709157</v>
+        <v>40.4466375430071</v>
       </c>
       <c r="I5" s="9" t="n">
-        <v>38.2965898192352</v>
+        <v>38.4789922621167</v>
       </c>
       <c r="J5" s="10" t="n">
-        <v>38.0160919686466</v>
+        <v>38.268647502351</v>
       </c>
       <c r="K5" s="11" t="n">
-        <v>40.1588287185318</v>
+        <v>40.7311076011111</v>
       </c>
       <c r="L5" s="12" t="n">
-        <v>40.1588287185318</v>
+        <v>40.7311076011111</v>
       </c>
       <c r="M5" s="13" t="n">
-        <v>39.4823472633203</v>
+        <v>40.0372536211082</v>
       </c>
       <c r="N5" s="14" t="n">
-        <v>39.4823472633203</v>
+        <v>40.0372536211082</v>
       </c>
       <c r="O5" s="15" t="n">
-        <v>0.00552030723846504</v>
+        <v>-0.00404648598151536</v>
       </c>
       <c r="P5" s="16"/>
       <c r="Q5" s="17" t="n">
-        <v>0.00553557221065426</v>
+        <v>-0.00403830998884702</v>
       </c>
       <c r="R5" s="18" t="n">
-        <v>0.991122079650199</v>
+        <v>0.989878418905313</v>
       </c>
       <c r="S5" s="19" t="n">
-        <v>1.03096248124656</v>
+        <v>1.04049641810723</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B6" s="2" t="n">
         <v>39.451</v>
@@ -1666,51 +1721,51 @@
         <v>39.451</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>1.01765409562552</v>
+        <v>1.03761447936999</v>
       </c>
       <c r="G6" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H6" s="8" t="n">
-        <v>38.2044535171428</v>
+        <v>38.0991948039387</v>
       </c>
       <c r="I6" s="9" t="n">
-        <v>38.8012755151437</v>
+        <v>38.9488981371118</v>
       </c>
       <c r="J6" s="10" t="n">
-        <v>38.2537023869077</v>
+        <v>38.4236255627712</v>
       </c>
       <c r="K6" s="11" t="n">
-        <v>38.7666105502683</v>
+        <v>38.0208649593571</v>
       </c>
       <c r="L6" s="12" t="n">
-        <v>38.7666105502683</v>
+        <v>38.0208649593571</v>
       </c>
       <c r="M6" s="13" t="n">
-        <v>38.0929027495003</v>
+        <v>38.0680521039114</v>
       </c>
       <c r="N6" s="14" t="n">
-        <v>38.0929027495003</v>
+        <v>38.0680521039114</v>
       </c>
       <c r="O6" s="15" t="n">
-        <v>-0.0358256820495371</v>
+        <v>-0.0504349582976838</v>
       </c>
       <c r="P6" s="16" t="n">
-        <v>-0.0106441656332195</v>
+        <v>-0.0197045843933955</v>
       </c>
       <c r="Q6" s="17" t="n">
-        <v>-0.0351915377409907</v>
+        <v>-0.0491842306625792</v>
       </c>
       <c r="R6" s="18" t="n">
-        <v>0.997080163243469</v>
+        <v>0.999182589023533</v>
       </c>
       <c r="S6" s="19" t="n">
-        <v>0.981743570121374</v>
+        <v>0.977384571186081</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B7" s="2" t="n">
         <v>36.088</v>
@@ -1725,51 +1780,51 @@
         <v>36.088</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>1.04061293664589</v>
+        <v>1.01658139536915</v>
       </c>
       <c r="G7" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H7" s="8" t="n">
-        <v>35.5452838781985</v>
+        <v>35.6315654305241</v>
       </c>
       <c r="I7" s="9" t="n">
-        <v>39.3153724834175</v>
+        <v>39.4302035519074</v>
       </c>
       <c r="J7" s="10" t="n">
-        <v>38.5505652275379</v>
+        <v>38.6454761494596</v>
       </c>
       <c r="K7" s="11" t="n">
-        <v>34.6795611789327</v>
+        <v>35.4993708958203</v>
       </c>
       <c r="L7" s="12" t="n">
-        <v>34.6795611789327</v>
+        <v>35.4993708958203</v>
       </c>
       <c r="M7" s="13" t="n">
-        <v>35.9226378834876</v>
+        <v>36.0209046940948</v>
       </c>
       <c r="N7" s="14" t="n">
-        <v>35.9226378834876</v>
+        <v>36.0209046940948</v>
       </c>
       <c r="O7" s="15" t="n">
-        <v>-0.058660306765918</v>
+        <v>-0.0552759470451173</v>
       </c>
       <c r="P7" s="16" t="n">
-        <v>-0.0754430190779584</v>
+        <v>-0.0823803492396061</v>
       </c>
       <c r="Q7" s="17" t="n">
-        <v>-0.0569729453353642</v>
+        <v>-0.0537759957937615</v>
       </c>
       <c r="R7" s="18" t="n">
-        <v>1.01061614830767</v>
+        <v>1.01092680770172</v>
       </c>
       <c r="S7" s="19" t="n">
-        <v>0.913704630386985</v>
+        <v>0.913535854479562</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B8" s="2" t="n">
         <v>35.364</v>
@@ -1784,51 +1839,51 @@
         <v>35.364</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>0.99435344721058</v>
+        <v>1.00855543782045</v>
       </c>
       <c r="G8" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H8" s="8" t="n">
-        <v>35.358968634526</v>
+        <v>35.2416118052889</v>
       </c>
       <c r="I8" s="9" t="n">
-        <v>39.8427105831742</v>
+        <v>39.9272467078003</v>
       </c>
       <c r="J8" s="10" t="n">
-        <v>38.9366695001352</v>
+        <v>38.9653044025888</v>
       </c>
       <c r="K8" s="11" t="n">
-        <v>35.5648186258168</v>
+        <v>35.0640120253813</v>
       </c>
       <c r="L8" s="12" t="n">
-        <v>35.5648186258168</v>
+        <v>35.0640120253813</v>
       </c>
       <c r="M8" s="13" t="n">
-        <v>35.7040002548848</v>
+        <v>35.5371007904587</v>
       </c>
       <c r="N8" s="14" t="n">
-        <v>35.7040002548848</v>
+        <v>35.5371007904587</v>
       </c>
       <c r="O8" s="15" t="n">
-        <v>-0.00610494400807274</v>
+        <v>-0.0135222124291669</v>
       </c>
       <c r="P8" s="16" t="n">
-        <v>-0.0906912882593951</v>
+        <v>-0.115983546316424</v>
       </c>
       <c r="Q8" s="17" t="n">
-        <v>-0.00608634670181873</v>
+        <v>-0.0134311980152841</v>
       </c>
       <c r="R8" s="18" t="n">
-        <v>1.00975796618745</v>
+        <v>1.00838466148491</v>
       </c>
       <c r="S8" s="19" t="n">
-        <v>0.896123776025491</v>
+        <v>0.890046364842785</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B9" s="2" t="n">
         <v>38.249</v>
@@ -1843,51 +1898,51 @@
         <v>38.249</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>0.94413482810095</v>
+        <v>0.932898520842405</v>
       </c>
       <c r="G9" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H9" s="8" t="n">
-        <v>37.006802588973</v>
+        <v>36.5210082152518</v>
       </c>
       <c r="I9" s="9" t="n">
-        <v>40.384222291466</v>
+        <v>40.4419090356775</v>
       </c>
       <c r="J9" s="10" t="n">
-        <v>39.422649194054</v>
+        <v>39.3984849360626</v>
       </c>
       <c r="K9" s="11" t="n">
-        <v>40.512222260601</v>
+        <v>41.0001722003603</v>
       </c>
       <c r="L9" s="12" t="n">
-        <v>37.006802588973</v>
+        <v>36.5210082152518</v>
       </c>
       <c r="M9" s="13" t="n">
-        <v>37.1534635535895</v>
+        <v>36.7099858907332</v>
       </c>
       <c r="N9" s="14" t="n">
-        <v>37.1534635535895</v>
+        <v>36.7099858907332</v>
       </c>
       <c r="O9" s="15" t="n">
-        <v>0.0397942639427373</v>
+        <v>0.0324715697235334</v>
       </c>
       <c r="P9" s="16" t="n">
-        <v>-0.0589854421318665</v>
+        <v>-0.0831042948615429</v>
       </c>
       <c r="Q9" s="17" t="n">
-        <v>0.0405966639132069</v>
+        <v>0.0330045241222778</v>
       </c>
       <c r="R9" s="18" t="n">
-        <v>1.00396308122713</v>
+        <v>1.00517449229133</v>
       </c>
       <c r="S9" s="19" t="n">
-        <v>0.919999481120148</v>
+        <v>0.907721390163554</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B10" s="2" t="n">
         <v>35.512</v>
@@ -1902,51 +1957,51 @@
         <v>35.512</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>1.0546626209824</v>
+        <v>1.04099002413683</v>
       </c>
       <c r="G10" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H10" s="8" t="n">
-        <v>39.035430410595</v>
+        <v>38.7339151070479</v>
       </c>
       <c r="I10" s="9" t="n">
-        <v>40.9381664028721</v>
+        <v>40.9730324447496</v>
       </c>
       <c r="J10" s="10" t="n">
-        <v>40.0022790442775</v>
+        <v>39.9408859018992</v>
       </c>
       <c r="K10" s="11" t="n">
-        <v>33.6714313122439</v>
+        <v>34.1136794557142</v>
       </c>
       <c r="L10" s="12" t="n">
-        <v>39.035430410595</v>
+        <v>38.7339151070479</v>
       </c>
       <c r="M10" s="13" t="n">
-        <v>39.2741042562901</v>
+        <v>38.8798290343308</v>
       </c>
       <c r="N10" s="14" t="n">
-        <v>39.2741042562901</v>
+        <v>38.8798290343308</v>
       </c>
       <c r="O10" s="15" t="n">
-        <v>0.0555083785040022</v>
+        <v>0.0574267691527083</v>
       </c>
       <c r="P10" s="16" t="n">
-        <v>0.0310084404582511</v>
+        <v>0.021324362176546</v>
       </c>
       <c r="Q10" s="17" t="n">
-        <v>0.0570778737665159</v>
+        <v>0.0591077084599305</v>
       </c>
       <c r="R10" s="18" t="n">
-        <v>1.00611428753788</v>
+        <v>1.00376708439825</v>
       </c>
       <c r="S10" s="19" t="n">
-        <v>0.959351815364519</v>
+        <v>0.948912655824502</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B11" s="2" t="n">
         <v>42.694</v>
@@ -1961,51 +2016,51 @@
         <v>42.694</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>1.01607011933742</v>
+        <v>1.02801610663392</v>
       </c>
       <c r="G11" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H11" s="8" t="n">
-        <v>41.9447193973843</v>
+        <v>41.5289152260651</v>
       </c>
       <c r="I11" s="9" t="n">
-        <v>41.5006908246572</v>
+        <v>41.5170082812142</v>
       </c>
       <c r="J11" s="10" t="n">
-        <v>40.6572545527635</v>
+        <v>40.5739880685124</v>
       </c>
       <c r="K11" s="11" t="n">
-        <v>42.0187536149974</v>
+        <v>41.5304777079757</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>42.0187536149974</v>
+        <v>41.5304777079757</v>
       </c>
       <c r="M11" s="13" t="n">
-        <v>41.7419958422861</v>
+        <v>41.3282008842687</v>
       </c>
       <c r="N11" s="14" t="n">
-        <v>41.7419958422861</v>
+        <v>41.3282008842687</v>
       </c>
       <c r="O11" s="15" t="n">
-        <v>0.0609423396519676</v>
+        <v>0.0610695147547215</v>
       </c>
       <c r="P11" s="16" t="n">
-        <v>0.161996955169972</v>
+        <v>0.147339336289464</v>
       </c>
       <c r="Q11" s="17" t="n">
-        <v>0.0628376288327643</v>
+        <v>0.062972803912692</v>
       </c>
       <c r="R11" s="18" t="n">
-        <v>0.995166887321916</v>
+        <v>0.995166877326225</v>
       </c>
       <c r="S11" s="19" t="n">
-        <v>1.00581448194799</v>
+        <v>0.995452287995643</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B12" s="2" t="n">
         <v>43.215</v>
@@ -2020,51 +2075,51 @@
         <v>43.215</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>0.984507460528457</v>
+        <v>0.993038892403791</v>
       </c>
       <c r="G12" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H12" s="8" t="n">
-        <v>43.1927679386013</v>
+        <v>42.9271225952887</v>
       </c>
       <c r="I12" s="9" t="n">
-        <v>42.0667542540913</v>
+        <v>42.0688284429329</v>
       </c>
       <c r="J12" s="10" t="n">
-        <v>41.3644369783011</v>
+        <v>41.273237350342</v>
       </c>
       <c r="K12" s="11" t="n">
-        <v>43.8950457285548</v>
+        <v>43.5179330140756</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>43.8950457285548</v>
+        <v>43.5179330140756</v>
       </c>
       <c r="M12" s="13" t="n">
-        <v>42.8094071247736</v>
+        <v>42.5872212512656</v>
       </c>
       <c r="N12" s="14" t="n">
-        <v>42.8094071247736</v>
+        <v>42.5872212512656</v>
       </c>
       <c r="O12" s="15" t="n">
-        <v>0.0252501545072778</v>
+        <v>0.0300091405754306</v>
       </c>
       <c r="P12" s="16" t="n">
-        <v>0.199008705443772</v>
+        <v>0.198387609118068</v>
       </c>
       <c r="Q12" s="17" t="n">
-        <v>0.0255716398065977</v>
+        <v>0.0304639529439596</v>
       </c>
       <c r="R12" s="18" t="n">
-        <v>0.991124421237077</v>
+        <v>0.992081897796234</v>
       </c>
       <c r="S12" s="19" t="n">
-        <v>1.01765415192711</v>
+        <v>1.01232249215202</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B13" s="2" t="n">
         <v>38.854</v>
@@ -2079,51 +2134,51 @@
         <v>38.854</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>0.937850373242917</v>
+        <v>0.929909929362942</v>
       </c>
       <c r="G13" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H13" s="8" t="n">
-        <v>41.9514355052867</v>
+        <v>42.2042601099554</v>
       </c>
       <c r="I13" s="9" t="n">
-        <v>42.6316391776879</v>
+        <v>42.623493246159</v>
       </c>
       <c r="J13" s="10" t="n">
-        <v>42.1074950749909</v>
+        <v>42.018862110025</v>
       </c>
       <c r="K13" s="11" t="n">
-        <v>41.4287834269873</v>
+        <v>41.7825412689355</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>41.4287834269873</v>
+        <v>41.7825412689355</v>
       </c>
       <c r="M13" s="13" t="n">
-        <v>42.0434572034751</v>
+        <v>42.2131791978093</v>
       </c>
       <c r="N13" s="14" t="n">
-        <v>42.0434572034751</v>
+        <v>42.2131791978093</v>
       </c>
       <c r="O13" s="15" t="n">
-        <v>-0.0180540923958234</v>
+        <v>-0.00882176209649332</v>
       </c>
       <c r="P13" s="16" t="n">
-        <v>0.131616091265151</v>
+        <v>0.149909981536257</v>
       </c>
       <c r="Q13" s="17" t="n">
-        <v>-0.0178920936481545</v>
+        <v>-0.00878296452472094</v>
       </c>
       <c r="R13" s="18" t="n">
-        <v>1.00219352918631</v>
+        <v>1.00021133145874</v>
       </c>
       <c r="S13" s="19" t="n">
-        <v>0.986203158368807</v>
+        <v>0.99037352368141</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B14" s="2" t="n">
         <v>44.001</v>
@@ -2138,51 +2193,51 @@
         <v>44.001</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>1.06228170013692</v>
+        <v>1.05341907398204</v>
       </c>
       <c r="G14" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H14" s="8" t="n">
-        <v>41.6128126071716</v>
+        <v>41.8424865378819</v>
       </c>
       <c r="I14" s="9" t="n">
-        <v>43.1917707641323</v>
+        <v>43.1769086975029</v>
       </c>
       <c r="J14" s="10" t="n">
-        <v>42.8827506406845</v>
+        <v>42.8023141885171</v>
       </c>
       <c r="K14" s="11" t="n">
-        <v>41.4212162313712</v>
+        <v>41.7697012392906</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>41.4212162313712</v>
+        <v>41.7697012392906</v>
       </c>
       <c r="M14" s="13" t="n">
-        <v>41.9566965024896</v>
+        <v>42.1258366154231</v>
       </c>
       <c r="N14" s="14" t="n">
-        <v>41.9566965024896</v>
+        <v>42.1258366154231</v>
       </c>
       <c r="O14" s="15" t="n">
-        <v>-0.00206572793048836</v>
+        <v>-0.00207122676898359</v>
       </c>
       <c r="P14" s="16" t="n">
-        <v>0.0683043521169524</v>
+        <v>0.0834882164277531</v>
       </c>
       <c r="Q14" s="17" t="n">
-        <v>-0.00206359578294524</v>
+        <v>-0.00206908325897315</v>
       </c>
       <c r="R14" s="18" t="n">
-        <v>1.00826389455008</v>
+        <v>1.00677182693922</v>
       </c>
       <c r="S14" s="19" t="n">
-        <v>0.971404870886461</v>
+        <v>0.975656615682154</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B15" s="2" t="n">
         <v>44.777</v>
@@ -2197,51 +2252,51 @@
         <v>44.777</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>1.02804302357654</v>
+        <v>1.03695102950652</v>
       </c>
       <c r="G15" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H15" s="8" t="n">
-        <v>43.3951934586551</v>
+        <v>43.1972721268951</v>
       </c>
       <c r="I15" s="9" t="n">
-        <v>43.7428223972657</v>
+        <v>43.7244552085891</v>
       </c>
       <c r="J15" s="10" t="n">
-        <v>43.6831319149936</v>
+        <v>43.6138638225686</v>
       </c>
       <c r="K15" s="11" t="n">
-        <v>43.5555701202288</v>
+        <v>43.1814027141756</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>43.5555701202288</v>
+        <v>43.1814027141756</v>
       </c>
       <c r="M15" s="13" t="n">
-        <v>43.3595168445624</v>
+        <v>43.2152189256961</v>
       </c>
       <c r="N15" s="14" t="n">
-        <v>43.3595168445624</v>
+        <v>43.2152189256961</v>
       </c>
       <c r="O15" s="15" t="n">
-        <v>0.0328881634401262</v>
+        <v>0.0255314743751081</v>
       </c>
       <c r="P15" s="16" t="n">
-        <v>0.0387504471129685</v>
+        <v>0.0456593319102265</v>
       </c>
       <c r="Q15" s="17" t="n">
-        <v>0.0334349569678234</v>
+        <v>0.0258601940708794</v>
       </c>
       <c r="R15" s="18" t="n">
-        <v>0.999177867149579</v>
+        <v>1.00041546139183</v>
       </c>
       <c r="S15" s="19" t="n">
-        <v>0.99123729261861</v>
+        <v>0.988353513372237</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B16" s="2" t="n">
         <v>43.288</v>
@@ -2256,51 +2311,51 @@
         <v>43.288</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>0.963975385897087</v>
+        <v>0.967797416578932</v>
       </c>
       <c r="G16" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H16" s="8" t="n">
-        <v>44.7024675270108</v>
+        <v>44.4963152968718</v>
       </c>
       <c r="I16" s="9" t="n">
-        <v>44.2793608643462</v>
+        <v>44.2606336863807</v>
       </c>
       <c r="J16" s="10" t="n">
-        <v>44.4942594654835</v>
+        <v>44.4386181841835</v>
       </c>
       <c r="K16" s="11" t="n">
-        <v>44.9057109064208</v>
+        <v>44.7283690351425</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>44.9057109064208</v>
+        <v>44.7283690351425</v>
       </c>
       <c r="M16" s="13" t="n">
-        <v>44.5241684317088</v>
+        <v>44.3858345101726</v>
       </c>
       <c r="N16" s="14" t="n">
-        <v>44.5241684317088</v>
+        <v>44.3858345101726</v>
       </c>
       <c r="O16" s="15" t="n">
-        <v>0.0265059383802069</v>
+        <v>0.0267276528123919</v>
       </c>
       <c r="P16" s="16" t="n">
-        <v>0.040055712566571</v>
+        <v>0.042233637369649</v>
       </c>
       <c r="Q16" s="17" t="n">
-        <v>0.0268603451307252</v>
+        <v>0.0270880401297802</v>
       </c>
       <c r="R16" s="18" t="n">
-        <v>0.996011426098699</v>
+        <v>0.99751708010063</v>
       </c>
       <c r="S16" s="19" t="n">
-        <v>1.00552870598364</v>
+        <v>1.00282871738075</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B17" s="2" t="n">
         <v>42.023</v>
@@ -2315,51 +2370,51 @@
         <v>42.023</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>0.939488015894129</v>
+        <v>0.935815953779607</v>
       </c>
       <c r="G17" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H17" s="8" t="n">
-        <v>44.8659694622458</v>
+        <v>45.0342620110024</v>
       </c>
       <c r="I17" s="9" t="n">
-        <v>44.7958359199586</v>
+        <v>44.779605630032</v>
       </c>
       <c r="J17" s="10" t="n">
-        <v>45.3011160507453</v>
+        <v>45.2595221398241</v>
       </c>
       <c r="K17" s="11" t="n">
-        <v>44.729681793765</v>
+        <v>44.9051972562297</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>44.729681793765</v>
+        <v>44.9051972562297</v>
       </c>
       <c r="M17" s="13" t="n">
-        <v>44.8546454356178</v>
+        <v>44.976399722691</v>
       </c>
       <c r="N17" s="14" t="n">
-        <v>44.8546454356178</v>
+        <v>44.976399722691</v>
       </c>
       <c r="O17" s="15" t="n">
-        <v>0.00739500773507225</v>
+        <v>0.0132175256215397</v>
       </c>
       <c r="P17" s="16" t="n">
-        <v>0.0668638694134385</v>
+        <v>0.0654587163864953</v>
       </c>
       <c r="Q17" s="17" t="n">
-        <v>0.00742241833030222</v>
+        <v>0.013305263245261</v>
       </c>
       <c r="R17" s="18" t="n">
-        <v>0.999747603210992</v>
+        <v>0.998715149627693</v>
       </c>
       <c r="S17" s="19" t="n">
-        <v>1.00131283442872</v>
+        <v>1.00439472590011</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B18" s="2" t="n">
         <v>48.478</v>
@@ -2374,51 +2429,51 @@
         <v>48.478</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>1.076009459876</v>
+        <v>1.06857795200623</v>
       </c>
       <c r="G18" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H18" s="8" t="n">
-        <v>45.267122157544</v>
+        <v>45.4851778270968</v>
       </c>
       <c r="I18" s="9" t="n">
-        <v>45.2870887874642</v>
+        <v>45.2758248732899</v>
       </c>
       <c r="J18" s="10" t="n">
-        <v>46.0907416865751</v>
+        <v>46.0609693102072</v>
       </c>
       <c r="K18" s="11" t="n">
-        <v>45.0535072485205</v>
+        <v>45.3668353431621</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>45.0535072485205</v>
+        <v>45.3668353431621</v>
       </c>
       <c r="M18" s="13" t="n">
-        <v>45.0325185044196</v>
+        <v>45.2578370786992</v>
       </c>
       <c r="N18" s="14" t="n">
-        <v>45.0325185044196</v>
+        <v>45.2578370786992</v>
       </c>
       <c r="O18" s="15" t="n">
-        <v>0.00395770192716748</v>
+        <v>0.00623794866763585</v>
       </c>
       <c r="P18" s="16" t="n">
-        <v>0.073309441837192</v>
+        <v>0.0743486827779556</v>
       </c>
       <c r="Q18" s="17" t="n">
-        <v>0.00396554397151805</v>
+        <v>0.00625744518777416</v>
       </c>
       <c r="R18" s="18" t="n">
-        <v>0.994817349945333</v>
+        <v>0.99500187183478</v>
       </c>
       <c r="S18" s="19" t="n">
-        <v>0.99437874480651</v>
+        <v>0.99960270641913</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B19" s="2" t="n">
         <v>51.223</v>
@@ -2433,51 +2488,51 @@
         <v>51.223</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>1.0287220158442</v>
+        <v>1.03586264242117</v>
       </c>
       <c r="G19" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H19" s="8" t="n">
-        <v>45.2933777268724</v>
+        <v>45.3924803722427</v>
       </c>
       <c r="I19" s="9" t="n">
-        <v>45.7479193438954</v>
+        <v>45.7438237446681</v>
       </c>
       <c r="J19" s="10" t="n">
-        <v>46.847319217484</v>
+        <v>46.8255816916318</v>
       </c>
       <c r="K19" s="11" t="n">
-        <v>49.7928490020357</v>
+        <v>49.449606446154</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>45.2933777268724</v>
+        <v>45.3924803722427</v>
       </c>
       <c r="M19" s="13" t="n">
-        <v>45.1272228346717</v>
+        <v>45.2793955207148</v>
       </c>
       <c r="N19" s="14" t="n">
-        <v>45.1272228346717</v>
+        <v>45.2793955207148</v>
       </c>
       <c r="O19" s="15" t="n">
-        <v>0.00210081270589943</v>
+        <v>0.00047623373951512</v>
       </c>
       <c r="P19" s="16" t="n">
-        <v>0.0407685813577279</v>
+        <v>0.0477650384825736</v>
       </c>
       <c r="Q19" s="17" t="n">
-        <v>0.00210302095901671</v>
+        <v>0.000476347156806112</v>
       </c>
       <c r="R19" s="18" t="n">
-        <v>0.996331585310271</v>
+        <v>0.997508731609276</v>
       </c>
       <c r="S19" s="19" t="n">
-        <v>0.986432246140906</v>
+        <v>0.989847192780699</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B20" s="2" t="n">
         <v>42.247</v>
@@ -2492,51 +2547,51 @@
         <v>42.247</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>0.944438590458225</v>
+        <v>0.946262559880257</v>
       </c>
       <c r="G20" s="7" t="n">
-        <v>0.888219935024077</v>
+        <v>0.761085381439816</v>
       </c>
       <c r="H20" s="8" t="n">
-        <v>45.9511607362054</v>
+        <v>45.9839503491358</v>
       </c>
       <c r="I20" s="9" t="n">
-        <v>46.1729814778227</v>
+        <v>46.1781914542237</v>
       </c>
       <c r="J20" s="10" t="n">
-        <v>47.5498453157928</v>
+        <v>47.5325106105617</v>
       </c>
       <c r="K20" s="11" t="n">
-        <v>44.7323949135777</v>
+        <v>44.64617093732</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>44.8686286364215</v>
+        <v>44.9657859952117</v>
       </c>
       <c r="M20" s="13" t="n">
-        <v>46.0955021994268</v>
+        <v>46.1816588752487</v>
       </c>
       <c r="N20" s="14" t="n">
-        <v>46.0955021994268</v>
+        <v>46.1816588752487</v>
       </c>
       <c r="O20" s="15" t="n">
-        <v>0.0212297041358145</v>
+        <v>0.0197306412241781</v>
       </c>
       <c r="P20" s="16" t="n">
-        <v>0.0352917038782681</v>
+        <v>0.040459402980574</v>
       </c>
       <c r="Q20" s="17" t="n">
-        <v>0.0214566575103128</v>
+        <v>0.0199265768493122</v>
       </c>
       <c r="R20" s="18" t="n">
-        <v>1.00314119297334</v>
+        <v>1.00429951156027</v>
       </c>
       <c r="S20" s="19" t="n">
-        <v>0.998321978007136</v>
+        <v>1.00007508784809</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B21" s="2" t="n">
         <v>46.849</v>
@@ -2551,51 +2606,51 @@
         <v>46.849</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>0.949294748951978</v>
+        <v>0.948310736481559</v>
       </c>
       <c r="G21" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H21" s="8" t="n">
-        <v>49.1955381046652</v>
+        <v>49.4364508696474</v>
       </c>
       <c r="I21" s="9" t="n">
-        <v>46.5566449893061</v>
+        <v>46.5732976224062</v>
       </c>
       <c r="J21" s="10" t="n">
-        <v>48.1695469463692</v>
+        <v>48.1537418868636</v>
       </c>
       <c r="K21" s="11" t="n">
-        <v>49.351373797992</v>
+        <v>49.4025831383288</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>49.351373797992</v>
+        <v>49.4025831383288</v>
       </c>
       <c r="M21" s="13" t="n">
-        <v>49.2345260644284</v>
+        <v>49.3957305710901</v>
       </c>
       <c r="N21" s="14" t="n">
-        <v>49.2345260644284</v>
+        <v>49.3957305710901</v>
       </c>
       <c r="O21" s="15" t="n">
-        <v>0.0658797475946099</v>
+        <v>0.0672812695500669</v>
       </c>
       <c r="P21" s="16" t="n">
-        <v>0.0976460874068716</v>
+        <v>0.0982588841180529</v>
       </c>
       <c r="Q21" s="17" t="n">
-        <v>0.0680982680570641</v>
+        <v>0.0695962807339521</v>
       </c>
       <c r="R21" s="18" t="n">
-        <v>1.00079251007846</v>
+        <v>0.999176310235849</v>
       </c>
       <c r="S21" s="19" t="n">
-        <v>1.05751877257774</v>
+        <v>1.06060195633058</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B22" s="2" t="n">
         <v>58.259</v>
@@ -2610,51 +2665,51 @@
         <v>58.259</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>1.09167269862173</v>
+        <v>1.08264016326621</v>
       </c>
       <c r="G22" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H22" s="8" t="n">
-        <v>53.0125380187339</v>
+        <v>53.1229417225135</v>
       </c>
       <c r="I22" s="9" t="n">
-        <v>46.8924644578795</v>
+        <v>46.922754116253</v>
       </c>
       <c r="J22" s="10" t="n">
-        <v>48.6642449906843</v>
+        <v>48.6484277173277</v>
       </c>
       <c r="K22" s="11" t="n">
-        <v>53.3667280253081</v>
+        <v>53.8119700124913</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>53.3667280253081</v>
+        <v>53.8119700124913</v>
       </c>
       <c r="M22" s="13" t="n">
-        <v>52.350837469462</v>
+        <v>52.4684563679512</v>
       </c>
       <c r="N22" s="14" t="n">
-        <v>52.350837469462</v>
+        <v>52.4684563679512</v>
       </c>
       <c r="O22" s="15" t="n">
-        <v>0.0613728080306542</v>
+        <v>0.0603481631670784</v>
       </c>
       <c r="P22" s="16" t="n">
-        <v>0.162511873821229</v>
+        <v>0.159323108541699</v>
       </c>
       <c r="Q22" s="17" t="n">
-        <v>0.0632952453113005</v>
+        <v>0.062206303284428</v>
       </c>
       <c r="R22" s="18" t="n">
-        <v>0.987518036788994</v>
+        <v>0.987679798344359</v>
       </c>
       <c r="S22" s="19" t="n">
-        <v>1.11640192245569</v>
+        <v>1.11818791023985</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B23" s="2" t="n">
         <v>53.977</v>
@@ -2669,51 +2724,51 @@
         <v>53.977</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>1.01234992963794</v>
+        <v>1.02137663877168</v>
       </c>
       <c r="G23" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H23" s="8" t="n">
-        <v>52.9487769054538</v>
+        <v>52.8318666282636</v>
       </c>
       <c r="I23" s="9" t="n">
-        <v>47.1757411685824</v>
+        <v>47.2219411062491</v>
       </c>
       <c r="J23" s="10" t="n">
-        <v>48.9976694644669</v>
+        <v>48.9819645050012</v>
       </c>
       <c r="K23" s="11" t="n">
-        <v>53.3185200292398</v>
+        <v>52.8473023084936</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>53.3185200292398</v>
+        <v>52.8473023084936</v>
       </c>
       <c r="M23" s="13" t="n">
-        <v>52.5838876717847</v>
+        <v>52.4741351363153</v>
       </c>
       <c r="N23" s="14" t="n">
-        <v>52.5838876717847</v>
+        <v>52.4741351363153</v>
       </c>
       <c r="O23" s="15" t="n">
-        <v>0.00444182009678353</v>
+        <v>0.000108226188970767</v>
       </c>
       <c r="P23" s="16" t="n">
-        <v>0.165236510663004</v>
+        <v>0.158896547377913</v>
       </c>
       <c r="Q23" s="17" t="n">
-        <v>0.00445169960191505</v>
+        <v>0.000108232045636036</v>
       </c>
       <c r="R23" s="18" t="n">
-        <v>0.9931086371585</v>
+        <v>0.993228868961505</v>
       </c>
       <c r="S23" s="19" t="n">
-        <v>1.1146382943699</v>
+        <v>1.11122359452037</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B24" s="2" t="n">
         <v>47.06</v>
@@ -2728,51 +2783,51 @@
         <v>47.06</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>0.934995693891174</v>
+        <v>0.933916091125201</v>
       </c>
       <c r="G24" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H24" s="8" t="n">
-        <v>50.9967318699341</v>
+        <v>50.950466193853</v>
       </c>
       <c r="I24" s="9" t="n">
-        <v>47.4058228211838</v>
+        <v>47.4705445228147</v>
       </c>
       <c r="J24" s="10" t="n">
-        <v>49.1570627986193</v>
+        <v>49.1455663644075</v>
       </c>
       <c r="K24" s="11" t="n">
-        <v>50.3317826033511</v>
+        <v>50.3899659157828</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>50.3317826033511</v>
+        <v>50.3899659157828</v>
       </c>
       <c r="M24" s="13" t="n">
-        <v>51.137295746701</v>
+        <v>51.0397000319876</v>
       </c>
       <c r="N24" s="14" t="n">
-        <v>51.137295746701</v>
+        <v>51.0397000319876</v>
       </c>
       <c r="O24" s="15" t="n">
-        <v>-0.0278956657422433</v>
+        <v>-0.0277166222255422</v>
       </c>
       <c r="P24" s="16" t="n">
-        <v>0.109377125895309</v>
+        <v>0.105194167447775</v>
       </c>
       <c r="Q24" s="17" t="n">
-        <v>-0.027510174487534</v>
+        <v>-0.0273360409009386</v>
       </c>
       <c r="R24" s="18" t="n">
-        <v>1.00275633107481</v>
+        <v>1.00175138413445</v>
       </c>
       <c r="S24" s="19" t="n">
-        <v>1.07871338800705</v>
+        <v>1.07518674043138</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B25" s="2" t="n">
         <v>49.032</v>
@@ -2787,51 +2842,51 @@
         <v>49.032</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>0.969642359970405</v>
+        <v>0.970324173443376</v>
       </c>
       <c r="G25" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H25" s="8" t="n">
-        <v>50.5017922434309</v>
+        <v>50.03521377785</v>
       </c>
       <c r="I25" s="9" t="n">
-        <v>47.5858963522409</v>
+        <v>47.6717661471212</v>
       </c>
       <c r="J25" s="10" t="n">
-        <v>49.1512716768674</v>
+        <v>49.1497740990871</v>
       </c>
       <c r="K25" s="11" t="n">
-        <v>50.567097750862</v>
+        <v>50.5315659878913</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>50.567097750862</v>
+        <v>50.5315659878913</v>
       </c>
       <c r="M25" s="13" t="n">
-        <v>50.6487624635554</v>
+        <v>50.2958313980974</v>
       </c>
       <c r="N25" s="14" t="n">
-        <v>50.6487624635554</v>
+        <v>50.2958313980974</v>
       </c>
       <c r="O25" s="15" t="n">
-        <v>-0.00959929175197531</v>
+        <v>-0.0146815630209618</v>
       </c>
       <c r="P25" s="16" t="n">
-        <v>0.0287244848721879</v>
+        <v>0.0182222393838645</v>
       </c>
       <c r="Q25" s="17" t="n">
-        <v>-0.00955336562116005</v>
+        <v>-0.0145743143753593</v>
       </c>
       <c r="R25" s="18" t="n">
-        <v>1.00291019810576</v>
+        <v>1.00520868405608</v>
       </c>
       <c r="S25" s="19" t="n">
-        <v>1.06436499774308</v>
+        <v>1.0550444311813</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B26" s="2" t="n">
         <v>54.016</v>
@@ -2846,51 +2901,51 @@
         <v>54.016</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>1.05646353732017</v>
+        <v>1.08618042782669</v>
       </c>
       <c r="G26" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H26" s="8" t="n">
-        <v>50.6250970318121</v>
+        <v>50.1470486008719</v>
       </c>
       <c r="I26" s="9" t="n">
-        <v>47.7209774231743</v>
+        <v>47.8306323987107</v>
       </c>
       <c r="J26" s="10" t="n">
-        <v>48.9950163819609</v>
+        <v>49.0113505103376</v>
       </c>
       <c r="K26" s="11" t="n">
-        <v>51.1290717491464</v>
+        <v>49.7302277008243</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>51.1290717491464</v>
+        <v>49.7302277008243</v>
       </c>
       <c r="M26" s="13" t="n">
-        <v>50.7092377350558</v>
+        <v>50.2989855011246</v>
       </c>
       <c r="N26" s="14" t="n">
-        <v>50.7092377350558</v>
+        <v>50.2989855011246</v>
       </c>
       <c r="O26" s="15" t="n">
-        <v>0.00119330054969804</v>
+        <v>0.00006270905650003</v>
       </c>
       <c r="P26" s="16" t="n">
-        <v>-0.031357659471327</v>
+        <v>-0.0413480978287701</v>
       </c>
       <c r="Q26" s="17" t="n">
-        <v>0.00119401281608678</v>
+        <v>0.000062711022754014</v>
       </c>
       <c r="R26" s="18" t="n">
-        <v>1.00166203539701</v>
+        <v>1.00302982736755</v>
       </c>
       <c r="S26" s="19" t="n">
-        <v>1.06261942804278</v>
+        <v>1.05160611471406</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B27" s="2" t="n">
         <v>51.252</v>
@@ -2905,51 +2960,51 @@
         <v>51.252</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>1.02479999817229</v>
+        <v>1.00093897858726</v>
       </c>
       <c r="G27" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H27" s="8" t="n">
-        <v>51.1488272415311</v>
+        <v>51.5307076960085</v>
       </c>
       <c r="I27" s="9" t="n">
-        <v>47.8179449462792</v>
+        <v>47.953957072026</v>
       </c>
       <c r="J27" s="10" t="n">
-        <v>48.7100963270194</v>
+        <v>48.7539673589005</v>
       </c>
       <c r="K27" s="11" t="n">
-        <v>50.0117096910684</v>
+        <v>51.2039206149588</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>50.0117096910684</v>
+        <v>51.2039206149588</v>
       </c>
       <c r="M27" s="13" t="n">
-        <v>50.8062908687371</v>
+        <v>51.1579948837623</v>
       </c>
       <c r="N27" s="14" t="n">
-        <v>50.8062908687371</v>
+        <v>51.1579948837623</v>
       </c>
       <c r="O27" s="15" t="n">
-        <v>0.00191208506886558</v>
+        <v>0.0169338749579167</v>
       </c>
       <c r="P27" s="16" t="n">
-        <v>-0.0338049710995687</v>
+        <v>-0.0250816949938101</v>
       </c>
       <c r="Q27" s="17" t="n">
-        <v>0.00191391426919729</v>
+        <v>0.0170780657716929</v>
       </c>
       <c r="R27" s="18" t="n">
-        <v>0.993303143175179</v>
+        <v>0.992767170704409</v>
       </c>
       <c r="S27" s="19" t="n">
-        <v>1.06249423570618</v>
+        <v>1.0668148784244</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B28" s="2" t="n">
         <v>48.855</v>
@@ -2964,51 +3019,51 @@
         <v>48.855</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>0.938208042744009</v>
+        <v>0.93067937666643</v>
       </c>
       <c r="G28" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H28" s="8" t="n">
-        <v>50.5308644848923</v>
+        <v>51.2156899742843</v>
       </c>
       <c r="I28" s="9" t="n">
-        <v>47.8858078928042</v>
+        <v>48.0497412085734</v>
       </c>
       <c r="J28" s="10" t="n">
-        <v>48.3289812019985</v>
+        <v>48.4048907914699</v>
       </c>
       <c r="K28" s="11" t="n">
-        <v>52.072672343665</v>
+        <v>52.4939106043073</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>52.072672343665</v>
+        <v>52.4939106043073</v>
       </c>
       <c r="M28" s="13" t="n">
-        <v>50.2100541960417</v>
+        <v>50.7206691370872</v>
       </c>
       <c r="N28" s="14" t="n">
-        <v>50.2100541960417</v>
+        <v>50.7206691370872</v>
       </c>
       <c r="O28" s="15" t="n">
-        <v>-0.0118048934827143</v>
+        <v>-0.00858528008862692</v>
       </c>
       <c r="P28" s="16" t="n">
-        <v>-0.0181323931412454</v>
+        <v>-0.00625064204335923</v>
       </c>
       <c r="Q28" s="17" t="n">
-        <v>-0.0117354890998792</v>
+        <v>-0.00854853181147353</v>
       </c>
       <c r="R28" s="18" t="n">
-        <v>0.99365120125846</v>
+        <v>0.990334586189396</v>
       </c>
       <c r="S28" s="19" t="n">
-        <v>1.04853726825369</v>
+        <v>1.05558672869683</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B29" s="2" t="n">
         <v>46.384</v>
@@ -3023,51 +3078,51 @@
         <v>46.384</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>0.993591642246338</v>
+        <v>0.99342624587439</v>
       </c>
       <c r="G29" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H29" s="8" t="n">
-        <v>47.4803728017591</v>
+        <v>47.5756137689542</v>
       </c>
       <c r="I29" s="9" t="n">
-        <v>47.9349463369636</v>
+        <v>48.1280170770737</v>
       </c>
       <c r="J29" s="10" t="n">
-        <v>47.8906487636741</v>
+        <v>48.0036367210199</v>
       </c>
       <c r="K29" s="11" t="n">
-        <v>46.6831624057685</v>
+        <v>46.6909347247756</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>46.6831624057685</v>
+        <v>46.6909347247756</v>
       </c>
       <c r="M29" s="13" t="n">
-        <v>47.4128335948651</v>
+        <v>47.542414428515</v>
       </c>
       <c r="N29" s="14" t="n">
-        <v>47.4128335948651</v>
+        <v>47.542414428515</v>
       </c>
       <c r="O29" s="15" t="n">
-        <v>-0.0573223464323093</v>
+        <v>-0.0647112548597042</v>
       </c>
       <c r="P29" s="16" t="n">
-        <v>-0.0638895939662635</v>
+        <v>-0.054744436925375</v>
       </c>
       <c r="Q29" s="17" t="n">
-        <v>-0.0557103680919171</v>
+        <v>-0.06266192387924</v>
       </c>
       <c r="R29" s="18" t="n">
-        <v>0.998577534191318</v>
+        <v>0.999302177359172</v>
       </c>
       <c r="S29" s="19" t="n">
-        <v>0.989107889295875</v>
+        <v>0.987832396094338</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B30" s="2" t="n">
         <v>48.182</v>
@@ -3082,51 +3137,51 @@
         <v>48.182</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>1.08978631361663</v>
+        <v>1.08778013001314</v>
       </c>
       <c r="G30" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H30" s="8" t="n">
-        <v>44.3670395604517</v>
+        <v>44.2266169425907</v>
       </c>
       <c r="I30" s="9" t="n">
-        <v>47.9783571432534</v>
+        <v>48.2015945521201</v>
       </c>
       <c r="J30" s="10" t="n">
-        <v>47.4527952245302</v>
+        <v>47.6101661595891</v>
       </c>
       <c r="K30" s="11" t="n">
-        <v>44.2123372242585</v>
+        <v>44.2938776602014</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>44.2123372242585</v>
+        <v>44.2938776602014</v>
       </c>
       <c r="M30" s="13" t="n">
-        <v>44.8199861637259</v>
+        <v>44.7579570273399</v>
       </c>
       <c r="N30" s="14" t="n">
-        <v>44.8199861637259</v>
+        <v>44.7579570273399</v>
       </c>
       <c r="O30" s="15" t="n">
-        <v>-0.0562387833359842</v>
+        <v>-0.0603530083669239</v>
       </c>
       <c r="P30" s="16" t="n">
-        <v>-0.116137647386851</v>
+        <v>-0.110161833654893</v>
       </c>
       <c r="Q30" s="17" t="n">
-        <v>-0.0546866161447905</v>
+        <v>-0.0585678585037329</v>
       </c>
       <c r="R30" s="18" t="n">
-        <v>1.01020907880628</v>
+        <v>1.01201403411522</v>
       </c>
       <c r="S30" s="19" t="n">
-        <v>0.934170922732989</v>
+        <v>0.928557601532111</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B31" s="2" t="n">
         <v>42.801</v>
@@ -3141,51 +3196,51 @@
         <v>42.801</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>0.968959873800751</v>
+        <v>0.978238405145149</v>
       </c>
       <c r="G31" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H31" s="8" t="n">
-        <v>43.8254850572815</v>
+        <v>43.7460054592149</v>
       </c>
       <c r="I31" s="9" t="n">
-        <v>48.0282548112125</v>
+        <v>48.2823853318353</v>
       </c>
       <c r="J31" s="10" t="n">
-        <v>47.0670793652615</v>
+        <v>47.2778766092347</v>
       </c>
       <c r="K31" s="11" t="n">
-        <v>44.172107800618</v>
+        <v>43.7531380641811</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>44.172107800618</v>
+        <v>43.7531380641811</v>
       </c>
       <c r="M31" s="13" t="n">
-        <v>44.1310098696079</v>
+        <v>44.0588238237268</v>
       </c>
       <c r="N31" s="14" t="n">
-        <v>44.1310098696079</v>
+        <v>44.0588238237268</v>
       </c>
       <c r="O31" s="15" t="n">
-        <v>-0.0154914526752564</v>
+        <v>-0.0157435934401829</v>
       </c>
       <c r="P31" s="16" t="n">
-        <v>-0.131386898846354</v>
+        <v>-0.138769533015626</v>
       </c>
       <c r="Q31" s="17" t="n">
-        <v>-0.0153720773496273</v>
+        <v>-0.0156203108909997</v>
       </c>
       <c r="R31" s="18" t="n">
-        <v>1.0069713960251</v>
+        <v>1.00715078693993</v>
       </c>
       <c r="S31" s="19" t="n">
-        <v>0.918855162301362</v>
+        <v>0.912523760392515</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B32" s="2" t="n">
         <v>41.173</v>
@@ -3200,51 +3255,51 @@
         <v>41.173</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>0.93644197415705</v>
+        <v>0.926586449468649</v>
       </c>
       <c r="G32" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H32" s="8" t="n">
-        <v>44.4037356212335</v>
+        <v>44.5768633984829</v>
       </c>
       <c r="I32" s="9" t="n">
-        <v>48.0945000779307</v>
+        <v>48.379858791285</v>
       </c>
       <c r="J32" s="10" t="n">
-        <v>46.7689576765611</v>
+        <v>47.043584129517</v>
       </c>
       <c r="K32" s="11" t="n">
-        <v>43.9674866529369</v>
+        <v>44.4351415063437</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>43.9674866529369</v>
+        <v>44.4351415063437</v>
       </c>
       <c r="M32" s="13" t="n">
-        <v>44.4578097632855</v>
+        <v>44.6067184799674</v>
       </c>
       <c r="N32" s="14" t="n">
-        <v>44.4578097632855</v>
+        <v>44.6067184799674</v>
       </c>
       <c r="O32" s="15" t="n">
-        <v>0.00737793724870002</v>
+        <v>0.0123588401044096</v>
       </c>
       <c r="P32" s="16" t="n">
-        <v>-0.114563597368307</v>
+        <v>-0.120541600912147</v>
       </c>
       <c r="Q32" s="17" t="n">
-        <v>0.0074052212864204</v>
+        <v>0.0124355261600411</v>
       </c>
       <c r="R32" s="18" t="n">
-        <v>1.00121778362328</v>
+        <v>1.00066974388076</v>
       </c>
       <c r="S32" s="19" t="n">
-        <v>0.924384486609645</v>
+        <v>0.922010100781913</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B33" s="2" t="n">
         <v>46.762</v>
@@ -3259,51 +3314,51 @@
         <v>46.762</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>1.02269789319162</v>
+        <v>1.02092739951908</v>
       </c>
       <c r="G33" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H33" s="8" t="n">
-        <v>45.2617654683857</v>
+        <v>45.4226223620389</v>
       </c>
       <c r="I33" s="9" t="n">
-        <v>48.184543588616</v>
+        <v>48.5006535259922</v>
       </c>
       <c r="J33" s="10" t="n">
-        <v>46.5794117912993</v>
+        <v>46.9264810872711</v>
       </c>
       <c r="K33" s="11" t="n">
-        <v>45.7241579466502</v>
+        <v>45.8034528430012</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>45.7241579466502</v>
+        <v>45.8034528430012</v>
       </c>
       <c r="M33" s="13" t="n">
-        <v>45.2605782301099</v>
+        <v>45.3583917312767</v>
       </c>
       <c r="N33" s="14" t="n">
-        <v>45.2605782301099</v>
+        <v>45.3583917312767</v>
       </c>
       <c r="O33" s="15" t="n">
-        <v>0.0178957716277897</v>
+        <v>0.0167107168857844</v>
       </c>
       <c r="P33" s="16" t="n">
-        <v>-0.0453939408714925</v>
+        <v>-0.0459384051796985</v>
       </c>
       <c r="Q33" s="17" t="n">
-        <v>0.0180568604503617</v>
+        <v>0.0168511219144458</v>
       </c>
       <c r="R33" s="18" t="n">
-        <v>0.999973769510236</v>
+        <v>0.998585933012624</v>
       </c>
       <c r="S33" s="19" t="n">
-        <v>0.939317359037995</v>
+        <v>0.935211970019506</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B34" s="2" t="n">
         <v>49.253</v>
@@ -3318,51 +3373,51 @@
         <v>49.253</v>
       </c>
       <c r="F34" s="6" t="n">
-        <v>1.07948207294521</v>
+        <v>1.08507052176207</v>
       </c>
       <c r="G34" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H34" s="8" t="n">
-        <v>45.8115440754185</v>
+        <v>45.7056925424763</v>
       </c>
       <c r="I34" s="9" t="n">
-        <v>48.3032566050856</v>
+        <v>48.6489426831771</v>
       </c>
       <c r="J34" s="10" t="n">
-        <v>46.5054159872277</v>
+        <v>46.932717636216</v>
       </c>
       <c r="K34" s="11" t="n">
-        <v>45.6265103742023</v>
+        <v>45.3915197327607</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>45.6265103742023</v>
+        <v>45.3915197327607</v>
       </c>
       <c r="M34" s="13" t="n">
-        <v>45.7833641258168</v>
+        <v>45.626457649441</v>
       </c>
       <c r="N34" s="14" t="n">
-        <v>45.7833641258168</v>
+        <v>45.626457649441</v>
       </c>
       <c r="O34" s="15" t="n">
-        <v>0.0114843805762854</v>
+        <v>0.00589255674196677</v>
       </c>
       <c r="P34" s="16" t="n">
-        <v>0.021494383299713</v>
+        <v>0.0194043848241463</v>
       </c>
       <c r="Q34" s="17" t="n">
-        <v>0.0115505792490997</v>
+        <v>0.00590995200518618</v>
       </c>
       <c r="R34" s="18" t="n">
-        <v>0.999384872303032</v>
+        <v>0.998266410842332</v>
       </c>
       <c r="S34" s="19" t="n">
-        <v>0.947831830473239</v>
+        <v>0.937871516480432</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B35" s="2" t="n">
         <v>43.98</v>
@@ -3377,228 +3432,228 @@
         <v>43.98</v>
       </c>
       <c r="F35" s="6" t="n">
-        <v>0.952849798303592</v>
+        <v>0.957766414728681</v>
       </c>
       <c r="G35" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H35" s="8" t="n">
-        <v>46.3403492652154</v>
+        <v>45.5719511617111</v>
       </c>
       <c r="I35" s="9" t="n">
-        <v>48.4539726481309</v>
+        <v>48.8272136596329</v>
       </c>
       <c r="J35" s="10" t="n">
-        <v>46.5496682728753</v>
+        <v>47.0628287888497</v>
       </c>
       <c r="K35" s="11" t="n">
-        <v>46.1562778082127</v>
+        <v>45.9193382892412</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>46.1562778082127</v>
+        <v>45.9193382892412</v>
       </c>
       <c r="M35" s="13" t="n">
-        <v>46.3035693309845</v>
+        <v>45.7602744429794</v>
       </c>
       <c r="N35" s="14" t="n">
-        <v>46.3035693309845</v>
+        <v>45.7602744429794</v>
       </c>
       <c r="O35" s="15" t="n">
-        <v>0.011298253060091</v>
+        <v>0.00292858462307786</v>
       </c>
       <c r="P35" s="16" t="n">
-        <v>0.049229769900933</v>
+        <v>0.0386177040508358</v>
       </c>
       <c r="Q35" s="17" t="n">
-        <v>0.0113623193729941</v>
+        <v>0.00293287711631218</v>
       </c>
       <c r="R35" s="18" t="n">
-        <v>0.999206308652953</v>
+        <v>1.00413243840713</v>
       </c>
       <c r="S35" s="19" t="n">
-        <v>0.955619669562236</v>
+        <v>0.937187912502386</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B36" s="2" t="n">
-        <v>44.315</v>
+        <v>42.412</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>44.315</v>
+        <v>42.412</v>
       </c>
       <c r="D36" s="4" t="n">
-        <v>44.315</v>
+        <v>42.412</v>
       </c>
       <c r="E36" s="5" t="n">
-        <v>44.315</v>
+        <v>42.412</v>
       </c>
       <c r="F36" s="6" t="n">
-        <v>0.937383435212177</v>
+        <v>0.926465125320817</v>
       </c>
       <c r="G36" s="7" t="n">
-        <v>1</v>
+        <v>0.947651554892939</v>
       </c>
       <c r="H36" s="8" t="n">
-        <v>47.0092547669152</v>
+        <v>46.4010476586104</v>
       </c>
       <c r="I36" s="9" t="n">
-        <v>48.6383522721487</v>
+        <v>49.0359179628088</v>
       </c>
       <c r="J36" s="10" t="n">
-        <v>46.7104721287054</v>
+        <v>47.3096435681527</v>
       </c>
       <c r="K36" s="11" t="n">
-        <v>47.2752113333102</v>
+        <v>45.7783016768316</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>47.2752113333102</v>
+        <v>45.8109014606744</v>
       </c>
       <c r="M36" s="13" t="n">
-        <v>46.832072212308</v>
+        <v>46.4578750187511</v>
       </c>
       <c r="N36" s="14" t="n">
-        <v>46.832072212308</v>
+        <v>46.4578750187511</v>
       </c>
       <c r="O36" s="15" t="n">
-        <v>0.0113492223893012</v>
+        <v>0.0151296439340826</v>
       </c>
       <c r="P36" s="16" t="n">
-        <v>0.0534048452153675</v>
+        <v>0.0414995005654815</v>
       </c>
       <c r="Q36" s="17" t="n">
-        <v>0.0114138691457186</v>
+        <v>0.0152446763981047</v>
       </c>
       <c r="R36" s="18" t="n">
-        <v>0.996230900585732</v>
+        <v>1.00122469993692</v>
       </c>
       <c r="S36" s="19" t="n">
-        <v>0.962863049929532</v>
+        <v>0.947425416895161</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B37" s="2" t="n">
-        <v>50.540389454254</v>
+        <v>50.32</v>
       </c>
       <c r="C37" s="3" t="n">
-        <v>50.540389454254</v>
+        <v>50.32</v>
       </c>
       <c r="D37" s="4" t="n">
-        <v>50.540389454254</v>
+        <v>50.32</v>
       </c>
       <c r="E37" s="5" t="n">
-        <v>50.540389454254</v>
+        <v>50.32</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>1.04355575761558</v>
+        <v>1.04202994517569</v>
       </c>
       <c r="G37" s="7" t="n">
-        <v>0.168630031990409</v>
+        <v>1</v>
       </c>
       <c r="H37" s="8" t="n">
-        <v>46.2545898700299</v>
+        <v>47.9173176787396</v>
       </c>
       <c r="I37" s="9" t="n">
-        <v>48.8566199722608</v>
+        <v>49.2736896780475</v>
       </c>
       <c r="J37" s="10" t="n">
-        <v>46.9841640828583</v>
+        <v>47.6602735446075</v>
       </c>
       <c r="K37" s="11" t="n">
-        <v>48.4309430381887</v>
+        <v>48.2903588644143</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>46.6215883743989</v>
+        <v>48.2903588644143</v>
       </c>
       <c r="M37" s="13" t="n">
-        <v>46.3039041293688</v>
+        <v>47.7669553134026</v>
       </c>
       <c r="N37" s="14" t="n">
-        <v>46.3039041293688</v>
+        <v>47.7669553134026</v>
       </c>
       <c r="O37" s="15" t="n">
-        <v>-0.0113419919062353</v>
+        <v>0.0277881005660096</v>
       </c>
       <c r="P37" s="16" t="n">
-        <v>0.0230515371225375</v>
+        <v>0.0531007271244377</v>
       </c>
       <c r="Q37" s="17" t="n">
-        <v>-0.0112779140018588</v>
+        <v>0.0281777910445349</v>
       </c>
       <c r="R37" s="18" t="n">
-        <v>1.00106614845094</v>
+        <v>0.996862045443672</v>
       </c>
       <c r="S37" s="19" t="n">
-        <v>0.947750870929233</v>
+        <v>0.969421117547926</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B38" s="2" t="n">
-        <v>44.56625</v>
+        <v>52.582</v>
       </c>
       <c r="C38" s="3" t="n">
-        <v>44.56625</v>
+        <v>52.582</v>
       </c>
       <c r="D38" s="4" t="n">
-        <v>44.56625</v>
+        <v>52.582</v>
       </c>
       <c r="E38" s="5" t="n">
-        <v>44.56625</v>
+        <v>52.582</v>
       </c>
       <c r="F38" s="6" t="n">
-        <v>1.03267159516006</v>
+        <v>1.08024040024217</v>
       </c>
       <c r="G38" s="7" t="n">
-        <v>0.246442264979199</v>
+        <v>1</v>
       </c>
       <c r="H38" s="8" t="n">
-        <v>45.201182236689</v>
+        <v>48.4096154233053</v>
       </c>
       <c r="I38" s="9" t="n">
-        <v>49.1081482805025</v>
+        <v>49.537147255378</v>
       </c>
       <c r="J38" s="10" t="n">
-        <v>47.3699043594973</v>
+        <v>48.0943365781591</v>
       </c>
       <c r="K38" s="11" t="n">
-        <v>43.1562659502534</v>
+        <v>48.6762020641073</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>44.697228435367</v>
+        <v>48.6762020641073</v>
       </c>
       <c r="M38" s="13" t="n">
-        <v>45.4301160595692</v>
+        <v>48.2698065311614</v>
       </c>
       <c r="N38" s="14" t="n">
-        <v>45.4301160595692</v>
+        <v>48.2698065311614</v>
       </c>
       <c r="O38" s="15" t="n">
-        <v>-0.0190510455277166</v>
+        <v>0.0104721526124951</v>
       </c>
       <c r="P38" s="16" t="n">
-        <v>-0.00771564241712108</v>
+        <v>0.0579345629246497</v>
       </c>
       <c r="Q38" s="17" t="n">
-        <v>-0.0188707212972431</v>
+        <v>0.0105271775113061</v>
       </c>
       <c r="R38" s="18" t="n">
-        <v>1.00506477511321</v>
+        <v>0.997111960280589</v>
       </c>
       <c r="S38" s="19" t="n">
-        <v>0.925103422757367</v>
+        <v>0.97441635632179</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B39" s="2" t="n">
         <v>44.65</v>
@@ -3613,51 +3668,51 @@
         <v>44.65</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>0.976929605137261</v>
+        <v>0.941259045298932</v>
       </c>
       <c r="G39" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H39" s="8" t="n">
-        <v>45.1856671516557</v>
+        <v>47.8315250424776</v>
       </c>
       <c r="I39" s="9" t="n">
-        <v>49.3909128341602</v>
+        <v>49.8222945630705</v>
       </c>
       <c r="J39" s="10" t="n">
-        <v>47.8650403042433</v>
+        <v>48.5946009553518</v>
       </c>
       <c r="K39" s="11" t="n">
-        <v>45.7044189931439</v>
+        <v>47.4364631320167</v>
       </c>
       <c r="L39" s="12" t="n">
-        <v>45.7044189931439</v>
+        <v>47.4364631320167</v>
       </c>
       <c r="M39" s="13" t="n">
-        <v>45.6360904547007</v>
+        <v>48.0670300534628</v>
       </c>
       <c r="N39" s="14" t="n">
-        <v>45.6360904547007</v>
+        <v>48.0670300534628</v>
       </c>
       <c r="O39" s="15" t="n">
-        <v>0.00452362636496342</v>
+        <v>-0.00420974539654223</v>
       </c>
       <c r="P39" s="16" t="n">
-        <v>-0.014415279122707</v>
+        <v>0.0504095667817248</v>
       </c>
       <c r="Q39" s="17" t="n">
-        <v>0.00453387340814682</v>
+        <v>-0.00420089683946923</v>
       </c>
       <c r="R39" s="18" t="n">
-        <v>1.00996827824923</v>
+        <v>1.00492363584009</v>
       </c>
       <c r="S39" s="19" t="n">
-        <v>0.92397746540812</v>
+        <v>0.964769496768447</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B40" s="2" t="n">
         <v>43.651</v>
@@ -3672,51 +3727,51 @@
         <v>43.651</v>
       </c>
       <c r="F40" s="6" t="n">
-        <v>0.93997851615115</v>
+        <v>0.933965567824869</v>
       </c>
       <c r="G40" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H40" s="8" t="n">
-        <v>47.2694295995685</v>
+        <v>48.7189918857107</v>
       </c>
       <c r="I40" s="9" t="n">
-        <v>49.7001324456172</v>
+        <v>50.1245973786509</v>
       </c>
       <c r="J40" s="10" t="n">
-        <v>48.4535558830967</v>
+        <v>49.1467442901595</v>
       </c>
       <c r="K40" s="11" t="n">
-        <v>46.438295397148</v>
+        <v>46.7372690212335</v>
       </c>
       <c r="L40" s="12" t="n">
-        <v>46.438295397148</v>
+        <v>48.7189918857107</v>
       </c>
       <c r="M40" s="13" t="n">
-        <v>47.40574422295</v>
+        <v>48.9749992199099</v>
       </c>
       <c r="N40" s="14" t="n">
-        <v>47.40574422295</v>
+        <v>48.9749992199099</v>
       </c>
       <c r="O40" s="15" t="n">
-        <v>0.0380445466737033</v>
+        <v>0.0187134516899369</v>
       </c>
       <c r="P40" s="16" t="n">
-        <v>0.0122495542806931</v>
+        <v>0.0541807863606085</v>
       </c>
       <c r="Q40" s="17" t="n">
-        <v>0.0387775059304418</v>
+        <v>0.0188896456768219</v>
       </c>
       <c r="R40" s="18" t="n">
-        <v>1.0028837797396</v>
+        <v>1.0052547748689</v>
       </c>
       <c r="S40" s="19" t="n">
-        <v>0.953835370053033</v>
+        <v>0.977065189171362</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B41" s="2" t="n">
         <v>53.878</v>
@@ -3731,51 +3786,51 @@
         <v>53.878</v>
       </c>
       <c r="F41" s="6" t="n">
-        <v>1.05556276641614</v>
+        <v>1.05590238665</v>
       </c>
       <c r="G41" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H41" s="8" t="n">
-        <v>50.4343463378374</v>
+        <v>50.9779376295802</v>
       </c>
       <c r="I41" s="9" t="n">
-        <v>50.0287218686061</v>
+        <v>50.4380303350006</v>
       </c>
       <c r="J41" s="10" t="n">
-        <v>49.1086319555022</v>
+        <v>49.7306535074392</v>
       </c>
       <c r="K41" s="11" t="n">
-        <v>51.0419671043601</v>
+        <v>51.0255499762015</v>
       </c>
       <c r="L41" s="12" t="n">
-        <v>51.0419671043601</v>
+        <v>51.0255499762015</v>
       </c>
       <c r="M41" s="13" t="n">
-        <v>50.209150236926</v>
+        <v>50.7804638205262</v>
       </c>
       <c r="N41" s="14" t="n">
-        <v>50.209150236926</v>
+        <v>50.7804638205262</v>
       </c>
       <c r="O41" s="15" t="n">
-        <v>0.0574538782267041</v>
+        <v>0.0362017622538983</v>
       </c>
       <c r="P41" s="16" t="n">
-        <v>0.0843394564882982</v>
+        <v>0.0630877242929089</v>
       </c>
       <c r="Q41" s="17" t="n">
-        <v>0.0591364202783424</v>
+        <v>0.0368650256125445</v>
       </c>
       <c r="R41" s="18" t="n">
-        <v>0.995534866271431</v>
+        <v>0.996126288778316</v>
       </c>
       <c r="S41" s="19" t="n">
-        <v>1.00360649566051</v>
+        <v>1.00678919226725</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B42" s="2" t="n">
         <v>55.911</v>
@@ -3790,51 +3845,51 @@
         <v>55.911</v>
       </c>
       <c r="F42" s="6" t="n">
-        <v>1.06875029874034</v>
+        <v>1.06798694679725</v>
       </c>
       <c r="G42" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H42" s="8" t="n">
-        <v>52.2300151530954</v>
+        <v>51.993428323103</v>
       </c>
       <c r="I42" s="9" t="n">
-        <v>50.3675572087043</v>
+        <v>50.7556895615679</v>
       </c>
       <c r="J42" s="10" t="n">
-        <v>49.7933730784749</v>
+        <v>50.324076770026</v>
       </c>
       <c r="K42" s="11" t="n">
-        <v>52.3143713418357</v>
+        <v>52.3517634439912</v>
       </c>
       <c r="L42" s="12" t="n">
-        <v>52.3143713418357</v>
+        <v>52.3517634439912</v>
       </c>
       <c r="M42" s="13" t="n">
-        <v>51.7500928195642</v>
+        <v>51.7012622035349</v>
       </c>
       <c r="N42" s="14" t="n">
-        <v>51.7500928195642</v>
+        <v>51.7012622035349</v>
       </c>
       <c r="O42" s="15" t="n">
-        <v>0.0302289400351621</v>
+        <v>0.0179704850550695</v>
       </c>
       <c r="P42" s="16" t="n">
-        <v>0.139114255215814</v>
+        <v>0.0710890703520488</v>
       </c>
       <c r="Q42" s="17" t="n">
-        <v>0.0306904732576989</v>
+        <v>0.0181329258090881</v>
       </c>
       <c r="R42" s="18" t="n">
-        <v>0.990811369054278</v>
+        <v>0.994380710620725</v>
       </c>
       <c r="S42" s="19" t="n">
-        <v>1.02744893116677</v>
+        <v>1.01862988465204</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B43" s="2" t="n">
         <v>47.518</v>
@@ -3849,51 +3904,51 @@
         <v>47.518</v>
       </c>
       <c r="F43" s="6" t="n">
-        <v>0.925741542422777</v>
+        <v>0.930339613440115</v>
       </c>
       <c r="G43" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H43" s="8" t="n">
-        <v>51.4404698633937</v>
+        <v>51.386023029653</v>
       </c>
       <c r="I43" s="9" t="n">
-        <v>50.7081478497614</v>
+        <v>51.0710383875769</v>
       </c>
       <c r="J43" s="10" t="n">
-        <v>50.4805504847741</v>
+        <v>50.9112367230987</v>
       </c>
       <c r="K43" s="11" t="n">
-        <v>51.3296614902251</v>
+        <v>51.0759719499558</v>
       </c>
       <c r="L43" s="12" t="n">
-        <v>51.3296614902251</v>
+        <v>51.0759719499558</v>
       </c>
       <c r="M43" s="13" t="n">
-        <v>51.32113405097</v>
+        <v>51.256708968177</v>
       </c>
       <c r="N43" s="14" t="n">
-        <v>51.32113405097</v>
+        <v>51.256708968177</v>
       </c>
       <c r="O43" s="15" t="n">
-        <v>-0.008323588613689</v>
+        <v>-0.00863567906411826</v>
       </c>
       <c r="P43" s="16" t="n">
-        <v>0.124573414147131</v>
+        <v>0.0663589764369976</v>
       </c>
       <c r="Q43" s="17" t="n">
-        <v>-0.00828904346297044</v>
+        <v>-0.00859849869056928</v>
       </c>
       <c r="R43" s="18" t="n">
-        <v>0.997680118149376</v>
+        <v>0.997483477921587</v>
       </c>
       <c r="S43" s="19" t="n">
-        <v>1.0120885149074</v>
+        <v>1.00363553564725</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B44" s="2" t="n">
         <v>48.053</v>
@@ -3908,51 +3963,51 @@
         <v>48.053</v>
       </c>
       <c r="F44" s="6" t="n">
-        <v>0.955122160608879</v>
+        <v>0.951108955428263</v>
       </c>
       <c r="G44" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H44" s="8" t="n">
-        <v>50.1771862951008</v>
+        <v>50.2708594150605</v>
       </c>
       <c r="I44" s="9" t="n">
-        <v>51.0432199344603</v>
+        <v>51.3785376884282</v>
       </c>
       <c r="J44" s="10" t="n">
-        <v>51.1555403984761</v>
+        <v>51.4864944452059</v>
       </c>
       <c r="K44" s="11" t="n">
-        <v>50.3108418815943</v>
+        <v>50.5231285288054</v>
       </c>
       <c r="L44" s="12" t="n">
-        <v>50.3108418815943</v>
+        <v>50.5231285288054</v>
       </c>
       <c r="M44" s="13" t="n">
-        <v>50.480789397663</v>
+        <v>50.479453701021</v>
       </c>
       <c r="N44" s="14" t="n">
-        <v>50.480789397663</v>
+        <v>50.479453701021</v>
       </c>
       <c r="O44" s="15" t="n">
-        <v>-0.016509781204169</v>
+        <v>-0.015280120060262</v>
       </c>
       <c r="P44" s="16" t="n">
-        <v>0.0648665098527077</v>
+        <v>0.0307188260352129</v>
       </c>
       <c r="Q44" s="17" t="n">
-        <v>-0.0163742417007483</v>
+        <v>-0.0151639713669208</v>
       </c>
       <c r="R44" s="18" t="n">
-        <v>1.00605062031132</v>
+        <v>1.00414940759692</v>
       </c>
       <c r="S44" s="19" t="n">
-        <v>0.988981288062949</v>
+        <v>0.982500786751474</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B45" s="2" t="n">
         <v>52.985</v>
@@ -3967,51 +4022,51 @@
         <v>52.985</v>
       </c>
       <c r="F45" s="6" t="n">
-        <v>1.060297746306</v>
+        <v>1.06405013923354</v>
       </c>
       <c r="G45" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H45" s="8" t="n">
-        <v>50.552490978167</v>
+        <v>50.0104403245052</v>
       </c>
       <c r="I45" s="9" t="n">
-        <v>51.3658880515093</v>
+        <v>51.6726514229989</v>
       </c>
       <c r="J45" s="10" t="n">
-        <v>51.8079645986842</v>
+        <v>52.0450346910305</v>
       </c>
       <c r="K45" s="11" t="n">
-        <v>49.9718123372382</v>
+        <v>49.7955857965174</v>
       </c>
       <c r="L45" s="12" t="n">
-        <v>49.9718123372382</v>
+        <v>49.7955857965174</v>
       </c>
       <c r="M45" s="13" t="n">
-        <v>50.7753002578821</v>
+        <v>50.3864153909538</v>
       </c>
       <c r="N45" s="14" t="n">
-        <v>50.7753002578821</v>
+        <v>50.3864153909538</v>
       </c>
       <c r="O45" s="15" t="n">
-        <v>0.00581716500660116</v>
+        <v>-0.001844793234637</v>
       </c>
       <c r="P45" s="16" t="n">
-        <v>0.0112758335539342</v>
+        <v>-0.00775984305628019</v>
       </c>
       <c r="Q45" s="17" t="n">
-        <v>0.00583411756696384</v>
+        <v>-0.00184309264950111</v>
       </c>
       <c r="R45" s="18" t="n">
-        <v>1.00440748369475</v>
+        <v>1.00751793153608</v>
       </c>
       <c r="S45" s="19" t="n">
-        <v>0.988502334603171</v>
+        <v>0.97510799239784</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B46" s="2" t="n">
         <v>53.805</v>
@@ -4026,51 +4081,51 @@
         <v>53.805</v>
       </c>
       <c r="F46" s="6" t="n">
-        <v>1.01813291841121</v>
+        <v>1.0461515793375</v>
       </c>
       <c r="G46" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H46" s="8" t="n">
-        <v>52.2466479583518</v>
+        <v>51.8140246964331</v>
       </c>
       <c r="I46" s="9" t="n">
-        <v>51.6688090533334</v>
+        <v>51.9473089194412</v>
       </c>
       <c r="J46" s="10" t="n">
-        <v>52.4232213719174</v>
+        <v>52.5772253856732</v>
       </c>
       <c r="K46" s="11" t="n">
-        <v>52.8467344754576</v>
+        <v>51.431361441975</v>
       </c>
       <c r="L46" s="12" t="n">
-        <v>52.8467344754576</v>
+        <v>51.431361441975</v>
       </c>
       <c r="M46" s="13" t="n">
-        <v>52.3066902851334</v>
+        <v>51.9251669466735</v>
       </c>
       <c r="N46" s="14" t="n">
-        <v>52.3066902851334</v>
+        <v>51.9251669466735</v>
       </c>
       <c r="O46" s="15" t="n">
-        <v>0.0297142632641255</v>
+        <v>0.0300819820549736</v>
       </c>
       <c r="P46" s="16" t="n">
-        <v>0.0107554872898474</v>
+        <v>0.00433074036485115</v>
       </c>
       <c r="Q46" s="17" t="n">
-        <v>0.0301601373004903</v>
+        <v>0.0305390161967338</v>
       </c>
       <c r="R46" s="18" t="n">
-        <v>1.00114920916705</v>
+        <v>1.002145022528</v>
       </c>
       <c r="S46" s="19" t="n">
-        <v>1.01234557644132</v>
+        <v>0.999573760927596</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B47" s="2" t="n">
         <v>51.089</v>
@@ -4085,51 +4140,51 @@
         <v>51.089</v>
       </c>
       <c r="F47" s="6" t="n">
-        <v>0.953838470124527</v>
+        <v>0.928176059848799</v>
       </c>
       <c r="G47" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H47" s="8" t="n">
-        <v>54.0229845719617</v>
+        <v>54.4578757503438</v>
       </c>
       <c r="I47" s="9" t="n">
-        <v>51.9437684950365</v>
+        <v>52.195266339891</v>
       </c>
       <c r="J47" s="10" t="n">
-        <v>52.9775282433876</v>
+        <v>53.0621872097626</v>
       </c>
       <c r="K47" s="11" t="n">
-        <v>53.5614798523802</v>
+        <v>55.0423591062265</v>
       </c>
       <c r="L47" s="12" t="n">
-        <v>53.5614798523802</v>
+        <v>55.0423591062265</v>
       </c>
       <c r="M47" s="13" t="n">
-        <v>53.7210552640912</v>
+        <v>54.1362632500557</v>
       </c>
       <c r="N47" s="14" t="n">
-        <v>53.7210552640912</v>
+        <v>54.1362632500557</v>
       </c>
       <c r="O47" s="15" t="n">
-        <v>0.0266807310348682</v>
+        <v>0.0417006767650006</v>
       </c>
       <c r="P47" s="16" t="n">
-        <v>0.0467628250524941</v>
+        <v>0.0561790707957162</v>
       </c>
       <c r="Q47" s="17" t="n">
-        <v>0.0270398484638921</v>
+        <v>0.0425823629157116</v>
       </c>
       <c r="R47" s="18" t="n">
-        <v>0.994411095383515</v>
+        <v>0.994094288551347</v>
       </c>
       <c r="S47" s="19" t="n">
-        <v>1.03421559160122</v>
+        <v>1.03718722110785</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B48" s="2" t="n">
         <v>53.311</v>
@@ -4144,51 +4199,51 @@
         <v>53.311</v>
       </c>
       <c r="F48" s="6" t="n">
-        <v>0.970799586787606</v>
+        <v>0.968780567011508</v>
       </c>
       <c r="G48" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H48" s="8" t="n">
-        <v>54.1545377159373</v>
+        <v>54.896486185342</v>
       </c>
       <c r="I48" s="9" t="n">
-        <v>52.1832881351109</v>
+        <v>52.4089573793106</v>
       </c>
       <c r="J48" s="10" t="n">
-        <v>53.4492203038241</v>
+        <v>53.4733115242084</v>
       </c>
       <c r="K48" s="11" t="n">
-        <v>54.9145268761466</v>
+        <v>55.0289733457945</v>
       </c>
       <c r="L48" s="12" t="n">
-        <v>54.9145268761466</v>
+        <v>55.0289733457945</v>
       </c>
       <c r="M48" s="13" t="n">
-        <v>54.2024082017939</v>
+        <v>54.6849772432173</v>
       </c>
       <c r="N48" s="14" t="n">
-        <v>54.2024082017939</v>
+        <v>54.6849772432173</v>
       </c>
       <c r="O48" s="15" t="n">
-        <v>0.00892032397958071</v>
+        <v>0.0100847709718569</v>
       </c>
       <c r="P48" s="16" t="n">
-        <v>0.0737234668581321</v>
+        <v>0.083311589842171</v>
       </c>
       <c r="Q48" s="17" t="n">
-        <v>0.00896022863542867</v>
+        <v>0.0101357936477282</v>
       </c>
       <c r="R48" s="18" t="n">
-        <v>1.0008839607515</v>
+        <v>0.996147131504727</v>
       </c>
       <c r="S48" s="19" t="n">
-        <v>1.0386928485889</v>
+        <v>1.04342806988954</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B49" s="2" t="n">
         <v>57.045</v>
@@ -4203,51 +4258,51 @@
         <v>57.045</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>1.06787648709224</v>
+        <v>1.07154914728746</v>
       </c>
       <c r="G49" s="7" t="n">
-        <v>1</v>
+        <v>0.656034519706824</v>
       </c>
       <c r="H49" s="8" t="n">
-        <v>54.4216306828909</v>
+        <v>54.4093657120476</v>
       </c>
       <c r="I49" s="9" t="n">
-        <v>52.3809008016477</v>
+        <v>52.5825951656411</v>
       </c>
       <c r="J49" s="10" t="n">
-        <v>53.8195524020015</v>
+        <v>53.7938905494027</v>
       </c>
       <c r="K49" s="11" t="n">
-        <v>53.4190992025023</v>
+        <v>53.2360089543301</v>
       </c>
       <c r="L49" s="12" t="n">
-        <v>53.4190992025023</v>
+        <v>53.6396031750536</v>
       </c>
       <c r="M49" s="13" t="n">
-        <v>54.4392392302909</v>
+        <v>54.3282213475894</v>
       </c>
       <c r="N49" s="14" t="n">
-        <v>54.4392392302909</v>
+        <v>54.3282213475894</v>
       </c>
       <c r="O49" s="15" t="n">
-        <v>0.00435986399770767</v>
+        <v>-0.00654521055891873</v>
       </c>
       <c r="P49" s="16" t="n">
-        <v>0.0721598681603084</v>
+        <v>0.0782315218506955</v>
       </c>
       <c r="Q49" s="17" t="n">
-        <v>0.00436938203216508</v>
+        <v>-0.00652383732448458</v>
       </c>
       <c r="R49" s="18" t="n">
-        <v>1.00032355787908</v>
+        <v>0.99850863241289</v>
       </c>
       <c r="S49" s="19" t="n">
-        <v>1.03929559051376</v>
+        <v>1.03319779437377</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B50" s="2" t="n">
         <v>58.277</v>
@@ -4262,51 +4317,51 @@
         <v>58.277</v>
       </c>
       <c r="F50" s="6" t="n">
-        <v>1.03396155075624</v>
+        <v>1.02098865649231</v>
       </c>
       <c r="G50" s="7" t="n">
-        <v>0.716602114949986</v>
+        <v>0.128165546893455</v>
       </c>
       <c r="H50" s="8" t="n">
-        <v>55.0974748421907</v>
+        <v>54.6997720954991</v>
       </c>
       <c r="I50" s="9" t="n">
-        <v>52.5318463469509</v>
+        <v>52.7120303368032</v>
       </c>
       <c r="J50" s="10" t="n">
-        <v>54.0771059195557</v>
+        <v>54.0149948148456</v>
       </c>
       <c r="K50" s="11" t="n">
-        <v>56.3628308590161</v>
+        <v>57.0789887129749</v>
       </c>
       <c r="L50" s="12" t="n">
-        <v>56.0042316400125</v>
+        <v>55.0047056944559</v>
       </c>
       <c r="M50" s="13" t="n">
-        <v>55.277766787221</v>
+        <v>54.689307632356</v>
       </c>
       <c r="N50" s="14" t="n">
-        <v>55.277766787221</v>
+        <v>54.689307632356</v>
       </c>
       <c r="O50" s="15" t="n">
-        <v>0.0152855772146042</v>
+        <v>0.00662439533522825</v>
       </c>
       <c r="P50" s="16" t="n">
-        <v>0.0568010800509786</v>
+        <v>0.0532331593371906</v>
       </c>
       <c r="Q50" s="17" t="n">
-        <v>0.0154029991746016</v>
+        <v>0.00664638517164695</v>
       </c>
       <c r="R50" s="18" t="n">
-        <v>1.00327223607882</v>
+        <v>0.999808692746931</v>
       </c>
       <c r="S50" s="19" t="n">
-        <v>1.05227153871833</v>
+        <v>1.03751093029274</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B51" s="2" t="n">
         <v>51.191</v>
@@ -4321,51 +4376,51 @@
         <v>51.191</v>
       </c>
       <c r="F51" s="6" t="n">
-        <v>0.919320727147566</v>
+        <v>0.928917750342093</v>
       </c>
       <c r="G51" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H51" s="8" t="n">
-        <v>56.2672441114481</v>
+        <v>55.7725266059572</v>
       </c>
       <c r="I51" s="9" t="n">
-        <v>52.632013497325</v>
+        <v>52.793774160723</v>
       </c>
       <c r="J51" s="10" t="n">
-        <v>54.2084599721254</v>
+        <v>54.1269234131655</v>
       </c>
       <c r="K51" s="11" t="n">
-        <v>55.6835046663568</v>
+        <v>55.1082159654586</v>
       </c>
       <c r="L51" s="12" t="n">
-        <v>55.6835046663568</v>
+        <v>55.1082159654586</v>
       </c>
       <c r="M51" s="13" t="n">
-        <v>56.1729971922931</v>
+        <v>55.645224749079</v>
       </c>
       <c r="N51" s="14" t="n">
-        <v>56.1729971922931</v>
+        <v>55.645224749079</v>
       </c>
       <c r="O51" s="15" t="n">
-        <v>0.0160653839898555</v>
+        <v>0.0173280479775321</v>
       </c>
       <c r="P51" s="16" t="n">
-        <v>0.0456421028244569</v>
+        <v>0.0278733959167703</v>
       </c>
       <c r="Q51" s="17" t="n">
-        <v>0.0161951261258093</v>
+        <v>0.0174790495273598</v>
       </c>
       <c r="R51" s="18" t="n">
-        <v>0.998325012702447</v>
+        <v>0.997717480906367</v>
       </c>
       <c r="S51" s="19" t="n">
-        <v>1.0672781347259</v>
+        <v>1.05401111463778</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B52" s="2" t="n">
         <v>56.535</v>
@@ -4380,51 +4435,51 @@
         <v>56.535</v>
       </c>
       <c r="F52" s="6" t="n">
-        <v>0.986292087478747</v>
+        <v>0.985621255193007</v>
       </c>
       <c r="G52" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H52" s="8" t="n">
-        <v>57.3078540122309</v>
+        <v>57.144354748277</v>
       </c>
       <c r="I52" s="9" t="n">
-        <v>52.6794612198828</v>
+        <v>52.8257708274252</v>
       </c>
       <c r="J52" s="10" t="n">
-        <v>54.2098293039513</v>
+        <v>54.1249239913887</v>
       </c>
       <c r="K52" s="11" t="n">
-        <v>57.3207477964465</v>
+        <v>57.3597613709428</v>
       </c>
       <c r="L52" s="12" t="n">
-        <v>57.3207477964465</v>
+        <v>57.3597613709428</v>
       </c>
       <c r="M52" s="13" t="n">
-        <v>56.9732212861872</v>
+        <v>56.830031543834</v>
       </c>
       <c r="N52" s="14" t="n">
-        <v>56.9732212861872</v>
+        <v>56.830031543834</v>
       </c>
       <c r="O52" s="15" t="n">
-        <v>0.0141451910181791</v>
+        <v>0.0210686449670085</v>
       </c>
       <c r="P52" s="16" t="n">
-        <v>0.0511197412867275</v>
+        <v>0.0392256595641673</v>
       </c>
       <c r="Q52" s="17" t="n">
-        <v>0.0142457076156135</v>
+        <v>0.0212921557976931</v>
       </c>
       <c r="R52" s="18" t="n">
-        <v>0.994160787699846</v>
+        <v>0.994499488080186</v>
       </c>
       <c r="S52" s="19" t="n">
-        <v>1.0815072889296</v>
+        <v>1.07580127376636</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B53" s="2" t="n">
         <v>62.113</v>
@@ -4439,51 +4494,51 @@
         <v>62.113</v>
       </c>
       <c r="F53" s="6" t="n">
-        <v>1.07895226867447</v>
+        <v>1.08036911903477</v>
       </c>
       <c r="G53" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H53" s="8" t="n">
-        <v>56.7930413531031</v>
+        <v>56.9767281299735</v>
       </c>
       <c r="I53" s="9" t="n">
-        <v>52.6741556637177</v>
+        <v>52.8074110530626</v>
       </c>
       <c r="J53" s="10" t="n">
-        <v>54.0848038827455</v>
+        <v>54.0091506593031</v>
       </c>
       <c r="K53" s="11" t="n">
-        <v>57.5678848854991</v>
+        <v>57.4923874679918</v>
       </c>
       <c r="L53" s="12" t="n">
-        <v>57.5678848854991</v>
+        <v>57.4923874679918</v>
       </c>
       <c r="M53" s="13" t="n">
-        <v>56.4436102518425</v>
+        <v>56.5366523793239</v>
       </c>
       <c r="N53" s="14" t="n">
-        <v>56.4436102518425</v>
+        <v>56.5366523793239</v>
       </c>
       <c r="O53" s="15" t="n">
-        <v>-0.00933926431603951</v>
+        <v>-0.00517576785862009</v>
       </c>
       <c r="P53" s="16" t="n">
-        <v>0.0368184980152384</v>
+        <v>0.0406497944706312</v>
       </c>
       <c r="Q53" s="17" t="n">
-        <v>-0.009295788835327</v>
+        <v>-0.00516239665085916</v>
       </c>
       <c r="R53" s="18" t="n">
-        <v>0.993847290214868</v>
+        <v>0.992276219342646</v>
       </c>
       <c r="S53" s="19" t="n">
-        <v>1.0715617467547</v>
+        <v>1.07061965833762</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B54" s="2" t="n">
         <v>53.27</v>
@@ -4498,51 +4553,51 @@
         <v>53.27</v>
       </c>
       <c r="F54" s="6" t="n">
-        <v>0.999101175799183</v>
+        <v>0.990110544471239</v>
       </c>
       <c r="G54" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H54" s="8" t="n">
-        <v>54.2016734337845</v>
+        <v>54.3265157203401</v>
       </c>
       <c r="I54" s="9" t="n">
-        <v>52.6189637820332</v>
+        <v>52.7409192978775</v>
       </c>
       <c r="J54" s="10" t="n">
-        <v>53.8525282686824</v>
+        <v>53.7959317135943</v>
       </c>
       <c r="K54" s="11" t="n">
-        <v>53.3179234399251</v>
+        <v>53.8020732103691</v>
       </c>
       <c r="L54" s="12" t="n">
-        <v>53.3179234399251</v>
+        <v>53.8020732103691</v>
       </c>
       <c r="M54" s="13" t="n">
-        <v>54.0550584241247</v>
+        <v>54.176030130061</v>
       </c>
       <c r="N54" s="14" t="n">
-        <v>54.0550584241247</v>
+        <v>54.176030130061</v>
       </c>
       <c r="O54" s="15" t="n">
-        <v>-0.0432389635587186</v>
+        <v>-0.0426505804042626</v>
       </c>
       <c r="P54" s="16" t="n">
-        <v>-0.0221193516699559</v>
+        <v>-0.00938533553479048</v>
       </c>
       <c r="Q54" s="17" t="n">
-        <v>-0.0423174884997692</v>
+        <v>-0.0417538384378457</v>
       </c>
       <c r="R54" s="18" t="n">
-        <v>0.997295009538055</v>
+        <v>0.997229978983857</v>
       </c>
       <c r="S54" s="19" t="n">
-        <v>1.02729233984995</v>
+        <v>1.02721057674551</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B55" s="2" t="n">
         <v>48.455</v>
@@ -4557,51 +4612,51 @@
         <v>48.455</v>
       </c>
       <c r="F55" s="6" t="n">
-        <v>0.931531306433035</v>
+        <v>0.938912341434918</v>
       </c>
       <c r="G55" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H55" s="8" t="n">
-        <v>51.2970230317646</v>
+        <v>51.2147333907654</v>
       </c>
       <c r="I55" s="9" t="n">
-        <v>52.519811108797</v>
+        <v>52.6314481323718</v>
       </c>
       <c r="J55" s="10" t="n">
-        <v>53.5495624269504</v>
+        <v>53.5190116349915</v>
       </c>
       <c r="K55" s="11" t="n">
-        <v>52.0165019311493</v>
+        <v>51.6075866315138</v>
       </c>
       <c r="L55" s="12" t="n">
-        <v>52.0165019311493</v>
+        <v>51.6075866315138</v>
       </c>
       <c r="M55" s="13" t="n">
-        <v>51.6060882207792</v>
+        <v>51.5256336803783</v>
       </c>
       <c r="N55" s="14" t="n">
-        <v>51.6060882207792</v>
+        <v>51.5256336803783</v>
       </c>
       <c r="O55" s="15" t="n">
-        <v>-0.046363473269363</v>
+        <v>-0.050159136897906</v>
       </c>
       <c r="P55" s="16" t="n">
-        <v>-0.0813007886312416</v>
+        <v>-0.0740331463710886</v>
       </c>
       <c r="Q55" s="17" t="n">
-        <v>-0.0453051069546622</v>
+        <v>-0.0489219391550072</v>
       </c>
       <c r="R55" s="18" t="n">
-        <v>1.00602501218878</v>
+        <v>1.00607052441806</v>
       </c>
       <c r="S55" s="19" t="n">
-        <v>0.98260231960612</v>
+        <v>0.978989473190775</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B56" s="2" t="n">
         <v>49.068</v>
@@ -4616,51 +4671,51 @@
         <v>49.068</v>
       </c>
       <c r="F56" s="6" t="n">
-        <v>0.999889439532114</v>
+        <v>0.999647791655434</v>
       </c>
       <c r="G56" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H56" s="8" t="n">
-        <v>49.6653378621765</v>
+        <v>49.5207176322892</v>
       </c>
       <c r="I56" s="9" t="n">
-        <v>52.3830600277624</v>
+        <v>52.4848133482426</v>
       </c>
       <c r="J56" s="10" t="n">
-        <v>53.2097932985938</v>
+        <v>53.2121656117074</v>
       </c>
       <c r="K56" s="11" t="n">
-        <v>49.073425580893</v>
+        <v>49.0852882481164</v>
       </c>
       <c r="L56" s="12" t="n">
-        <v>49.073425580893</v>
+        <v>49.0852882481164</v>
       </c>
       <c r="M56" s="13" t="n">
-        <v>49.9651175238582</v>
+        <v>49.8849971744161</v>
       </c>
       <c r="N56" s="14" t="n">
-        <v>49.9651175238582</v>
+        <v>49.8849971744161</v>
       </c>
       <c r="O56" s="15" t="n">
-        <v>-0.0323145418675434</v>
+        <v>-0.0323591254806007</v>
       </c>
       <c r="P56" s="16" t="n">
-        <v>-0.123006977736541</v>
+        <v>-0.122207117975311</v>
       </c>
       <c r="Q56" s="17" t="n">
-        <v>-0.031798005884513</v>
+        <v>-0.0318411708653473</v>
       </c>
       <c r="R56" s="18" t="n">
-        <v>1.0060359936041</v>
+        <v>1.00735610386004</v>
       </c>
       <c r="S56" s="19" t="n">
-        <v>0.95384113676019</v>
+        <v>0.950465363064617</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B57" s="2" t="n">
         <v>53.828</v>
@@ -4675,51 +4730,51 @@
         <v>53.828</v>
       </c>
       <c r="F57" s="6" t="n">
-        <v>1.08312117979188</v>
+        <v>1.08171272624171</v>
       </c>
       <c r="G57" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H57" s="8" t="n">
-        <v>49.5833341344467</v>
+        <v>49.7344106161766</v>
       </c>
       <c r="I57" s="9" t="n">
-        <v>52.214758354447</v>
+        <v>52.3061908237488</v>
       </c>
       <c r="J57" s="10" t="n">
-        <v>52.859442522178</v>
+        <v>52.8996117069377</v>
       </c>
       <c r="K57" s="11" t="n">
-        <v>49.6971170024973</v>
+        <v>49.7618255699176</v>
       </c>
       <c r="L57" s="12" t="n">
-        <v>49.6971170024973</v>
+        <v>49.7618255699176</v>
       </c>
       <c r="M57" s="13" t="n">
-        <v>49.8755942125234</v>
+        <v>49.9606629942069</v>
       </c>
       <c r="N57" s="14" t="n">
-        <v>49.8755942125234</v>
+        <v>49.9606629942069</v>
       </c>
       <c r="O57" s="15" t="n">
-        <v>-0.00179332326002414</v>
+        <v>0.00151565594634886</v>
       </c>
       <c r="P57" s="16" t="n">
-        <v>-0.116364208632539</v>
+        <v>-0.116313738227662</v>
       </c>
       <c r="Q57" s="17" t="n">
-        <v>-0.00179171621665963</v>
+        <v>0.00151680513334007</v>
       </c>
       <c r="R57" s="18" t="n">
-        <v>1.00589432080715</v>
+        <v>1.00454921200889</v>
       </c>
       <c r="S57" s="19" t="n">
-        <v>0.955201092265049</v>
+        <v>0.955157739598254</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B58" s="2" t="n">
         <v>49.391</v>
@@ -4734,51 +4789,51 @@
         <v>49.391</v>
       </c>
       <c r="F58" s="6" t="n">
-        <v>0.967792174576058</v>
+        <v>0.964033202050714</v>
       </c>
       <c r="G58" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H58" s="8" t="n">
-        <v>50.8158191145073</v>
+        <v>50.8506083096699</v>
       </c>
       <c r="I58" s="9" t="n">
-        <v>52.0188853828389</v>
+        <v>52.098631733962</v>
       </c>
       <c r="J58" s="10" t="n">
-        <v>52.5040498976801</v>
+        <v>52.5849335970599</v>
       </c>
       <c r="K58" s="11" t="n">
-        <v>51.0347172642058</v>
+        <v>51.2337125888759</v>
       </c>
       <c r="L58" s="12" t="n">
-        <v>51.0347172642058</v>
+        <v>51.2337125888759</v>
       </c>
       <c r="M58" s="13" t="n">
-        <v>50.8873833158463</v>
+        <v>50.9250199012729</v>
       </c>
       <c r="N58" s="14" t="n">
-        <v>50.8873833158463</v>
+        <v>50.9250199012729</v>
       </c>
       <c r="O58" s="15" t="n">
-        <v>0.0200832316692231</v>
+        <v>0.0191183972386668</v>
       </c>
       <c r="P58" s="16" t="n">
-        <v>-0.0586009006488223</v>
+        <v>-0.0600082771104373</v>
       </c>
       <c r="Q58" s="17" t="n">
-        <v>0.0202862566210558</v>
+        <v>0.0193023240539825</v>
       </c>
       <c r="R58" s="18" t="n">
-        <v>1.00140830557464</v>
+        <v>1.0014633372948</v>
       </c>
       <c r="S58" s="19" t="n">
-        <v>0.978248244677577</v>
+        <v>0.97747326957295</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B59" s="2" t="n">
         <v>49.029</v>
@@ -4793,51 +4848,51 @@
         <v>49.029</v>
       </c>
       <c r="F59" s="6" t="n">
-        <v>0.946816856806279</v>
+        <v>0.952558975411371</v>
       </c>
       <c r="G59" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H59" s="8" t="n">
-        <v>52.0386601153223</v>
+        <v>51.9200815433189</v>
       </c>
       <c r="I59" s="9" t="n">
-        <v>51.7978468810815</v>
+        <v>51.8635970256699</v>
       </c>
       <c r="J59" s="10" t="n">
-        <v>52.1333435974786</v>
+        <v>52.2560260277667</v>
       </c>
       <c r="K59" s="11" t="n">
-        <v>51.7829817324761</v>
+        <v>51.4708288574221</v>
       </c>
       <c r="L59" s="12" t="n">
-        <v>51.7829817324761</v>
+        <v>51.4708288574221</v>
       </c>
       <c r="M59" s="13" t="n">
-        <v>52.0551327068476</v>
+        <v>51.9589849133186</v>
       </c>
       <c r="N59" s="14" t="n">
-        <v>52.0551327068476</v>
+        <v>51.9589849133186</v>
       </c>
       <c r="O59" s="15" t="n">
-        <v>0.0226883804379568</v>
+        <v>0.0201003027776864</v>
       </c>
       <c r="P59" s="16" t="n">
-        <v>0.00870138585484992</v>
+        <v>0.00841040084297573</v>
       </c>
       <c r="Q59" s="17" t="n">
-        <v>0.0229477193541947</v>
+        <v>0.0203036741870743</v>
       </c>
       <c r="R59" s="18" t="n">
-        <v>1.00031654526632</v>
+        <v>1.00074929331471</v>
       </c>
       <c r="S59" s="19" t="n">
-        <v>1.00496711429641</v>
+        <v>1.00183920694127</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B60" s="2" t="n">
         <v>54.484</v>
@@ -4852,51 +4907,51 @@
         <v>54.484</v>
       </c>
       <c r="F60" s="6" t="n">
-        <v>1.01611623121259</v>
+        <v>1.01534517170479</v>
       </c>
       <c r="G60" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H60" s="8" t="n">
-        <v>53.5741529257636</v>
+        <v>53.5105847623225</v>
       </c>
       <c r="I60" s="9" t="n">
-        <v>51.5534335122438</v>
+        <v>51.6020070711947</v>
       </c>
       <c r="J60" s="10" t="n">
-        <v>51.7297051307846</v>
+        <v>51.8940276397094</v>
       </c>
       <c r="K60" s="11" t="n">
-        <v>53.6198500982325</v>
+        <v>53.6605693495543</v>
       </c>
       <c r="L60" s="12" t="n">
-        <v>53.6198500982325</v>
+        <v>53.6605693495543</v>
       </c>
       <c r="M60" s="13" t="n">
-        <v>53.4409619775493</v>
+        <v>53.4159757183968</v>
       </c>
       <c r="N60" s="14" t="n">
-        <v>53.4409619775493</v>
+        <v>53.4159757183968</v>
       </c>
       <c r="O60" s="15" t="n">
-        <v>0.0262741288614757</v>
+        <v>0.0276552162937803</v>
       </c>
       <c r="P60" s="16" t="n">
-        <v>0.0695654213568375</v>
+        <v>0.0707823743406288</v>
       </c>
       <c r="Q60" s="17" t="n">
-        <v>0.0266223367156901</v>
+        <v>0.0280411714645474</v>
       </c>
       <c r="R60" s="18" t="n">
-        <v>0.997513895396556</v>
+        <v>0.998231956455981</v>
       </c>
       <c r="S60" s="19" t="n">
-        <v>1.03661305051306</v>
+        <v>1.03515306380815</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B61" s="2" t="n">
         <v>58.759</v>
@@ -4911,51 +4966,51 @@
         <v>58.759</v>
       </c>
       <c r="F61" s="6" t="n">
-        <v>1.0733969389713</v>
+        <v>1.0708388479554</v>
       </c>
       <c r="G61" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H61" s="8" t="n">
-        <v>54.4638075949544</v>
+        <v>54.6166497876217</v>
       </c>
       <c r="I61" s="9" t="n">
-        <v>51.287426648677</v>
+        <v>51.3145367627533</v>
       </c>
       <c r="J61" s="10" t="n">
-        <v>51.2737641974842</v>
+        <v>51.4761510876881</v>
       </c>
       <c r="K61" s="11" t="n">
-        <v>54.741165981256</v>
+        <v>54.8719353170565</v>
       </c>
       <c r="L61" s="12" t="n">
-        <v>54.741165981256</v>
+        <v>54.8719353170565</v>
       </c>
       <c r="M61" s="13" t="n">
-        <v>54.2668267574952</v>
+        <v>54.4052538077534</v>
       </c>
       <c r="N61" s="14" t="n">
-        <v>54.2668267574952</v>
+        <v>54.4052538077534</v>
       </c>
       <c r="O61" s="15" t="n">
-        <v>0.0153355848294033</v>
+        <v>0.0183508545670164</v>
       </c>
       <c r="P61" s="16" t="n">
-        <v>0.0880437138505148</v>
+        <v>0.0889618060925625</v>
       </c>
       <c r="Q61" s="17" t="n">
-        <v>0.0154537783263118</v>
+        <v>0.0185202661947419</v>
       </c>
       <c r="R61" s="18" t="n">
-        <v>0.996383270906724</v>
+        <v>0.996129459044259</v>
       </c>
       <c r="S61" s="19" t="n">
-        <v>1.05809221291658</v>
+        <v>1.0602308281431</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B62" s="2" t="n">
         <v>51.099</v>
@@ -4970,51 +5025,51 @@
         <v>51.099</v>
       </c>
       <c r="F62" s="6" t="n">
-        <v>0.946889310997239</v>
+        <v>0.942497746618571</v>
       </c>
       <c r="G62" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H62" s="8" t="n">
-        <v>54.2968034551587</v>
+        <v>54.6061504908016</v>
       </c>
       <c r="I62" s="9" t="n">
-        <v>51.0028991730985</v>
+        <v>51.0031475939866</v>
       </c>
       <c r="J62" s="10" t="n">
-        <v>50.755601222301</v>
+        <v>50.9884417350517</v>
       </c>
       <c r="K62" s="11" t="n">
-        <v>53.9651249692362</v>
+        <v>54.2165752473462</v>
       </c>
       <c r="L62" s="12" t="n">
-        <v>53.9651249692362</v>
+        <v>54.2165752473462</v>
       </c>
       <c r="M62" s="13" t="n">
-        <v>54.1222393372008</v>
+        <v>54.3303843470095</v>
       </c>
       <c r="N62" s="14" t="n">
-        <v>54.1222393372008</v>
+        <v>54.3303843470095</v>
       </c>
       <c r="O62" s="15" t="n">
-        <v>-0.00266793526813941</v>
+        <v>-0.00137709170325674</v>
       </c>
       <c r="P62" s="16" t="n">
-        <v>0.0635689204390113</v>
+        <v>0.066870164259897</v>
       </c>
       <c r="Q62" s="17" t="n">
-        <v>-0.00266437949173859</v>
+        <v>-0.0013761439475759</v>
       </c>
       <c r="R62" s="18" t="n">
-        <v>0.996785001936585</v>
+        <v>0.994949906900349</v>
       </c>
       <c r="S62" s="19" t="n">
-        <v>1.06116005589242</v>
+        <v>1.0652359101346</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B63" s="2" t="n">
         <v>48.786</v>
@@ -5029,51 +5084,51 @@
         <v>48.786</v>
       </c>
       <c r="F63" s="6" t="n">
-        <v>0.967441025348538</v>
+        <v>0.97991243318643</v>
       </c>
       <c r="G63" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H63" s="8" t="n">
-        <v>53.8175414290746</v>
+        <v>54.0164515762891</v>
       </c>
       <c r="I63" s="9" t="n">
-        <v>50.7050825553087</v>
+        <v>50.6720244326322</v>
       </c>
       <c r="J63" s="10" t="n">
-        <v>50.1826336388771</v>
+        <v>50.4339238662962</v>
       </c>
       <c r="K63" s="11" t="n">
-        <v>50.42788006889</v>
+        <v>49.7860812331569</v>
       </c>
       <c r="L63" s="12" t="n">
-        <v>53.8175414290746</v>
+        <v>54.0164515762891</v>
       </c>
       <c r="M63" s="13" t="n">
-        <v>53.517784433608</v>
+        <v>53.6854379814643</v>
       </c>
       <c r="N63" s="14" t="n">
-        <v>53.517784433608</v>
+        <v>53.6854379814643</v>
       </c>
       <c r="O63" s="15" t="n">
-        <v>-0.011231161721856</v>
+        <v>-0.011941843632656</v>
       </c>
       <c r="P63" s="16" t="n">
-        <v>0.0280981269416294</v>
+        <v>0.0332272285731885</v>
       </c>
       <c r="Q63" s="17" t="n">
-        <v>-0.0111683276781437</v>
+        <v>-0.0118708228056318</v>
       </c>
       <c r="R63" s="18" t="n">
-        <v>0.994430124685988</v>
+        <v>0.993871985568002</v>
       </c>
       <c r="S63" s="19" t="n">
-        <v>1.0554717936852</v>
+        <v>1.05946897884134</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B64" s="2" t="n">
         <v>58.929</v>
@@ -5088,51 +5143,51 @@
         <v>58.929</v>
       </c>
       <c r="F64" s="6" t="n">
-        <v>1.026029004416</v>
+        <v>1.02076488604257</v>
       </c>
       <c r="G64" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H64" s="8" t="n">
-        <v>52.4709299070465</v>
+        <v>52.4922735259327</v>
       </c>
       <c r="I64" s="9" t="n">
-        <v>50.4010596562306</v>
+        <v>50.3273605387106</v>
       </c>
       <c r="J64" s="10" t="n">
-        <v>49.5783264995896</v>
+        <v>49.8317624334789</v>
       </c>
       <c r="K64" s="11" t="n">
-        <v>57.4340488878689</v>
+        <v>57.7302381829212</v>
       </c>
       <c r="L64" s="12" t="n">
-        <v>52.4709299070465</v>
+        <v>52.4922735259327</v>
       </c>
       <c r="M64" s="13" t="n">
-        <v>51.9622442809669</v>
+        <v>52.0852631985742</v>
       </c>
       <c r="N64" s="14" t="n">
-        <v>51.9622442809669</v>
+        <v>52.0852631985742</v>
       </c>
       <c r="O64" s="15" t="n">
-        <v>-0.0294966346387013</v>
+        <v>-0.030259738536534</v>
       </c>
       <c r="P64" s="16" t="n">
-        <v>-0.0276701174878472</v>
+        <v>-0.0249122570902368</v>
       </c>
       <c r="Q64" s="17" t="n">
-        <v>-0.0290658548201082</v>
+        <v>-0.0298064958218749</v>
       </c>
       <c r="R64" s="18" t="n">
-        <v>0.990305381913742</v>
+        <v>0.992246281213989</v>
       </c>
       <c r="S64" s="19" t="n">
-        <v>1.03097523415945</v>
+        <v>1.03492936329358</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B65" s="2" t="n">
         <v>51.654</v>
@@ -5147,51 +5202,51 @@
         <v>51.654</v>
       </c>
       <c r="F65" s="6" t="n">
-        <v>1.05223968782155</v>
+        <v>1.04689791839437</v>
       </c>
       <c r="G65" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H65" s="8" t="n">
-        <v>48.614187101003</v>
+        <v>48.818935300654</v>
       </c>
       <c r="I65" s="9" t="n">
-        <v>50.099858623583</v>
+        <v>49.9774394392075</v>
       </c>
       <c r="J65" s="10" t="n">
-        <v>48.9843193957661</v>
+        <v>49.2190350272073</v>
       </c>
       <c r="K65" s="11" t="n">
-        <v>49.0895758806999</v>
+        <v>49.3400541661425</v>
       </c>
       <c r="L65" s="12" t="n">
-        <v>49.0895758806999</v>
+        <v>49.3400541661425</v>
       </c>
       <c r="M65" s="13" t="n">
-        <v>48.6609530432126</v>
+        <v>48.8593584739484</v>
       </c>
       <c r="N65" s="14" t="n">
-        <v>48.6609530432126</v>
+        <v>48.8593584739484</v>
       </c>
       <c r="O65" s="15" t="n">
-        <v>-0.0656404604177043</v>
+        <v>-0.0639361168135193</v>
       </c>
       <c r="P65" s="16" t="n">
-        <v>-0.103302036423353</v>
+        <v>-0.101936760618781</v>
       </c>
       <c r="Q65" s="17" t="n">
-        <v>-0.0635324990949924</v>
+        <v>-0.0619350758068968</v>
       </c>
       <c r="R65" s="18" t="n">
-        <v>1.00096198136796</v>
+        <v>1.00082802242706</v>
       </c>
       <c r="S65" s="19" t="n">
-        <v>0.971279248686481</v>
+        <v>0.97762828632669</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B66" s="2" t="n">
         <v>41.524</v>
@@ -5206,51 +5261,51 @@
         <v>41.524</v>
       </c>
       <c r="F66" s="6" t="n">
-        <v>0.943861762208214</v>
+        <v>0.938076385062215</v>
       </c>
       <c r="G66" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H66" s="8" t="n">
-        <v>44.8539858173746</v>
+        <v>44.7242290237141</v>
       </c>
       <c r="I66" s="9" t="n">
-        <v>49.8118012739917</v>
+        <v>49.6318977317254</v>
       </c>
       <c r="J66" s="10" t="n">
-        <v>48.4567149357721</v>
+        <v>48.646121793551</v>
       </c>
       <c r="K66" s="11" t="n">
-        <v>43.993730504404</v>
+        <v>44.2650520375759</v>
       </c>
       <c r="L66" s="12" t="n">
-        <v>43.993730504404</v>
+        <v>44.2650520375759</v>
       </c>
       <c r="M66" s="13" t="n">
-        <v>45.3614293818434</v>
+        <v>45.279685438786</v>
       </c>
       <c r="N66" s="14" t="n">
-        <v>45.3614293818434</v>
+        <v>45.279685438786</v>
       </c>
       <c r="O66" s="15" t="n">
-        <v>-0.0702147520578631</v>
+        <v>-0.0760874490135271</v>
       </c>
       <c r="P66" s="16" t="n">
-        <v>-0.161870795862204</v>
+        <v>-0.166586322129003</v>
       </c>
       <c r="Q66" s="17" t="n">
-        <v>-0.0678063920868772</v>
+        <v>-0.0732648390598709</v>
       </c>
       <c r="R66" s="18" t="n">
-        <v>1.01131323237437</v>
+        <v>1.01241958614373</v>
       </c>
       <c r="S66" s="19" t="n">
-        <v>0.910656274651284</v>
+        <v>0.912310177691284</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B67" s="2" t="n">
         <v>43.751</v>
@@ -5265,51 +5320,51 @@
         <v>43.751</v>
       </c>
       <c r="F67" s="6" t="n">
-        <v>0.986078453787996</v>
+        <v>1.01161694662183</v>
       </c>
       <c r="G67" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H67" s="8" t="n">
-        <v>44.2720710641566</v>
+        <v>43.8394081819645</v>
       </c>
       <c r="I67" s="9" t="n">
-        <v>49.5465779973683</v>
+        <v>49.2999736480711</v>
       </c>
       <c r="J67" s="10" t="n">
-        <v>48.0521420103974</v>
+        <v>48.1640079742742</v>
       </c>
       <c r="K67" s="11" t="n">
-        <v>44.3686806378657</v>
+        <v>43.2485835138498</v>
       </c>
       <c r="L67" s="12" t="n">
-        <v>44.3686806378657</v>
+        <v>43.2485835138498</v>
       </c>
       <c r="M67" s="13" t="n">
-        <v>44.5749597392325</v>
+        <v>44.2298235096378</v>
       </c>
       <c r="N67" s="14" t="n">
-        <v>44.5749597392325</v>
+        <v>44.2298235096378</v>
       </c>
       <c r="O67" s="15" t="n">
-        <v>-0.0174899103336888</v>
+        <v>-0.0234591852615268</v>
       </c>
       <c r="P67" s="16" t="n">
-        <v>-0.167100054477584</v>
+        <v>-0.176129967964333</v>
       </c>
       <c r="Q67" s="17" t="n">
-        <v>-0.0173378496517512</v>
+        <v>-0.0231861577432456</v>
       </c>
       <c r="R67" s="18" t="n">
-        <v>1.006841529384</v>
+        <v>1.00890557933749</v>
       </c>
       <c r="S67" s="19" t="n">
-        <v>0.899657686583322</v>
+        <v>0.897157143031624</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B68" s="2" t="n">
         <v>46.819</v>
@@ -5324,51 +5379,51 @@
         <v>46.819</v>
       </c>
       <c r="F68" s="6" t="n">
-        <v>1.02743662928355</v>
+        <v>1.0143407056688</v>
       </c>
       <c r="G68" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H68" s="8" t="n">
-        <v>44.9045383868031</v>
+        <v>45.149356661541</v>
       </c>
       <c r="I68" s="9" t="n">
-        <v>49.3102428893931</v>
+        <v>48.9875511414926</v>
       </c>
       <c r="J68" s="10" t="n">
-        <v>47.8049145882751</v>
+        <v>47.8017734623614</v>
       </c>
       <c r="K68" s="11" t="n">
-        <v>45.5687471767945</v>
+        <v>46.1570749732755</v>
       </c>
       <c r="L68" s="12" t="n">
-        <v>45.5687471767945</v>
+        <v>46.1570749732755</v>
       </c>
       <c r="M68" s="13" t="n">
-        <v>44.9425390982887</v>
+        <v>45.0933042412506</v>
       </c>
       <c r="N68" s="14" t="n">
-        <v>44.9425390982887</v>
+        <v>45.0933042412506</v>
       </c>
       <c r="O68" s="15" t="n">
-        <v>0.00821250436581651</v>
+        <v>0.0193344691833825</v>
       </c>
       <c r="P68" s="16" t="n">
-        <v>-0.135092417192793</v>
+        <v>-0.134240637906865</v>
       </c>
       <c r="Q68" s="17" t="n">
-        <v>0.00824631948534815</v>
+        <v>0.0195225904852352</v>
       </c>
       <c r="R68" s="18" t="n">
-        <v>1.00084625547552</v>
+        <v>0.998758511207357</v>
       </c>
       <c r="S68" s="19" t="n">
-        <v>0.91142400574052</v>
+        <v>0.920505377192788</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B69" s="2" t="n">
         <v>45.535</v>
@@ -5383,51 +5438,51 @@
         <v>45.535</v>
       </c>
       <c r="F69" s="6" t="n">
-        <v>1.02871451139393</v>
+        <v>1.01616845967136</v>
       </c>
       <c r="G69" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H69" s="8" t="n">
-        <v>45.0400546327493</v>
+        <v>45.2120459601409</v>
       </c>
       <c r="I69" s="9" t="n">
-        <v>49.1056138598971</v>
+        <v>48.6967320464042</v>
       </c>
       <c r="J69" s="10" t="n">
-        <v>47.7309293311754</v>
+        <v>47.5639210284949</v>
       </c>
       <c r="K69" s="11" t="n">
-        <v>44.2639814017002</v>
+        <v>44.8104835046017</v>
       </c>
       <c r="L69" s="12" t="n">
-        <v>44.2639814017002</v>
+        <v>44.8104835046017</v>
       </c>
       <c r="M69" s="13" t="n">
-        <v>45.0667589282927</v>
+        <v>45.1327429632889</v>
       </c>
       <c r="N69" s="14" t="n">
-        <v>45.0667589282927</v>
+        <v>45.1327429632889</v>
       </c>
       <c r="O69" s="15" t="n">
-        <v>0.002760157263553</v>
+        <v>0.000874220378083554</v>
       </c>
       <c r="P69" s="16" t="n">
-        <v>-0.0738619753650973</v>
+        <v>-0.0762722972027244</v>
       </c>
       <c r="Q69" s="17" t="n">
-        <v>0.0027639700047275</v>
+        <v>0.000874602620098086</v>
       </c>
       <c r="R69" s="18" t="n">
-        <v>1.00059290104688</v>
+        <v>0.998245976372715</v>
       </c>
       <c r="S69" s="19" t="n">
-        <v>0.917751665967813</v>
+        <v>0.926812561472933</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B70" s="2" t="n">
         <v>42.418</v>
@@ -5442,51 +5497,51 @@
         <v>42.418</v>
       </c>
       <c r="F70" s="6" t="n">
-        <v>0.918728627675766</v>
+        <v>0.947826212106692</v>
       </c>
       <c r="G70" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H70" s="8" t="n">
-        <v>45.7905384524095</v>
+        <v>44.9144035069678</v>
       </c>
       <c r="I70" s="9" t="n">
-        <v>48.9331703838905</v>
+        <v>48.4278491496148</v>
       </c>
       <c r="J70" s="10" t="n">
-        <v>47.8349020638113</v>
+        <v>47.4467299509115</v>
       </c>
       <c r="K70" s="11" t="n">
-        <v>46.1703257329758</v>
+        <v>44.7529298706768</v>
       </c>
       <c r="L70" s="12" t="n">
-        <v>46.1703257329758</v>
+        <v>44.7529298706768</v>
       </c>
       <c r="M70" s="13" t="n">
-        <v>45.7597442922852</v>
+        <v>45.0939949690738</v>
       </c>
       <c r="N70" s="14" t="n">
-        <v>45.7597442922852</v>
+        <v>45.0939949690738</v>
       </c>
       <c r="O70" s="15" t="n">
-        <v>0.0152598368735994</v>
+        <v>-0.000858902748456157</v>
       </c>
       <c r="P70" s="16" t="n">
-        <v>0.00878091620722277</v>
+        <v>-0.0041009664248487</v>
       </c>
       <c r="Q70" s="17" t="n">
-        <v>0.015376862691528</v>
+        <v>-0.00085853399707192</v>
       </c>
       <c r="R70" s="18" t="n">
-        <v>0.999327499497384</v>
+        <v>1.00399852715573</v>
       </c>
       <c r="S70" s="19" t="n">
-        <v>0.935147752195308</v>
+        <v>0.931158326477784</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B71" s="2" t="n">
         <v>48.256</v>
@@ -5501,51 +5556,51 @@
         <v>48.256</v>
       </c>
       <c r="F71" s="6" t="n">
-        <v>1.03923078329013</v>
+        <v>1.04768520835905</v>
       </c>
       <c r="G71" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H71" s="8" t="n">
-        <v>46.0187947510799</v>
+        <v>45.6321314072373</v>
       </c>
       <c r="I71" s="9" t="n">
-        <v>48.7903659160975</v>
+        <v>48.1788063325947</v>
       </c>
       <c r="J71" s="10" t="n">
-        <v>48.1042138712485</v>
+        <v>47.4327123202288</v>
       </c>
       <c r="K71" s="11" t="n">
-        <v>46.434344301489</v>
+        <v>46.0596366303401</v>
       </c>
       <c r="L71" s="12" t="n">
-        <v>46.434344301489</v>
+        <v>46.0596366303401</v>
       </c>
       <c r="M71" s="13" t="n">
-        <v>46.1034891583009</v>
+        <v>45.86972808298</v>
       </c>
       <c r="N71" s="14" t="n">
-        <v>46.1034891583009</v>
+        <v>45.86972808298</v>
       </c>
       <c r="O71" s="15" t="n">
-        <v>0.0074838748318583</v>
+        <v>0.0170562921999201</v>
       </c>
       <c r="P71" s="16" t="n">
-        <v>0.0342912125554447</v>
+        <v>0.0370768961577452</v>
       </c>
       <c r="Q71" s="17" t="n">
-        <v>0.00751194901396346</v>
+        <v>0.0172025812846741</v>
       </c>
       <c r="R71" s="18" t="n">
-        <v>1.00184043079961</v>
+        <v>1.00520678452694</v>
       </c>
       <c r="S71" s="19" t="n">
-        <v>0.944930178174578</v>
+        <v>0.952072738505094</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B72" s="2" t="n">
         <v>46.223</v>
@@ -5560,51 +5615,51 @@
         <v>46.223</v>
       </c>
       <c r="F72" s="6" t="n">
-        <v>1.01869000068793</v>
+        <v>0.991767082311865</v>
       </c>
       <c r="G72" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H72" s="8" t="n">
-        <v>46.0664994739603</v>
+        <v>47.075539137089</v>
       </c>
       <c r="I72" s="9" t="n">
-        <v>48.6729271333352</v>
+        <v>47.9452106522651</v>
       </c>
       <c r="J72" s="10" t="n">
-        <v>48.5179229568984</v>
+        <v>47.4909112266628</v>
       </c>
       <c r="K72" s="11" t="n">
-        <v>45.3749422972496</v>
+        <v>46.6067092005631</v>
       </c>
       <c r="L72" s="12" t="n">
-        <v>45.3749422972496</v>
+        <v>46.6067092005631</v>
       </c>
       <c r="M72" s="13" t="n">
-        <v>46.5386607303382</v>
+        <v>47.341380505153</v>
       </c>
       <c r="N72" s="14" t="n">
-        <v>46.5386607303382</v>
+        <v>47.341380505153</v>
       </c>
       <c r="O72" s="15" t="n">
-        <v>0.00939474684662622</v>
+        <v>0.0315793845562982</v>
       </c>
       <c r="P72" s="16" t="n">
-        <v>0.0355147186623959</v>
+        <v>0.0498538818950824</v>
       </c>
       <c r="Q72" s="17" t="n">
-        <v>0.00943901600469066</v>
+        <v>0.0320833038188215</v>
       </c>
       <c r="R72" s="18" t="n">
-        <v>1.01024955796011</v>
+        <v>1.00564712317558</v>
       </c>
       <c r="S72" s="19" t="n">
-        <v>0.956150851639754</v>
+        <v>0.987405829719019</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B73" s="2" t="n">
         <v>49.692</v>
@@ -5619,51 +5674,51 @@
         <v>49.692</v>
       </c>
       <c r="F73" s="6" t="n">
-        <v>1.01473514139092</v>
+        <v>0.992005444865943</v>
       </c>
       <c r="G73" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H73" s="8" t="n">
-        <v>49.0551476082885</v>
+        <v>50.3312221743726</v>
       </c>
       <c r="I73" s="9" t="n">
-        <v>48.5751081989118</v>
+        <v>47.7213446844831</v>
       </c>
       <c r="J73" s="10" t="n">
-        <v>49.0467381763236</v>
+        <v>47.5835043819804</v>
       </c>
       <c r="K73" s="11" t="n">
-        <v>48.9704140253644</v>
+        <v>50.0924669891457</v>
       </c>
       <c r="L73" s="12" t="n">
-        <v>48.9704140253644</v>
+        <v>50.0924669891457</v>
       </c>
       <c r="M73" s="13" t="n">
-        <v>49.2741185045009</v>
+        <v>50.15546383799</v>
       </c>
       <c r="N73" s="14" t="n">
-        <v>49.2741185045009</v>
+        <v>50.15546383799</v>
       </c>
       <c r="O73" s="15" t="n">
-        <v>0.057115582857695</v>
+        <v>0.0577426932281833</v>
       </c>
       <c r="P73" s="16" t="n">
-        <v>0.0933583793523463</v>
+        <v>0.111287738012878</v>
       </c>
       <c r="Q73" s="17" t="n">
-        <v>0.0587781799311551</v>
+        <v>0.059442358942843</v>
       </c>
       <c r="R73" s="18" t="n">
-        <v>1.00446376999945</v>
+        <v>0.99650796605388</v>
       </c>
       <c r="S73" s="19" t="n">
-        <v>1.01439029847812</v>
+        <v>1.05100692718532</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B74" s="2" t="n">
         <v>51.943</v>
@@ -5678,51 +5733,51 @@
         <v>51.943</v>
       </c>
       <c r="F74" s="6" t="n">
-        <v>0.965829683425104</v>
+        <v>0.964941394489831</v>
       </c>
       <c r="G74" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H74" s="8" t="n">
-        <v>53.2553272379705</v>
+        <v>53.2480756686054</v>
       </c>
       <c r="I74" s="9" t="n">
-        <v>48.4891020356128</v>
+        <v>47.5006544416985</v>
       </c>
       <c r="J74" s="10" t="n">
-        <v>49.6456534817884</v>
+        <v>47.6682484878179</v>
       </c>
       <c r="K74" s="11" t="n">
-        <v>53.7807036700254</v>
+        <v>53.8302121731056</v>
       </c>
       <c r="L74" s="12" t="n">
-        <v>53.7807036700254</v>
+        <v>53.8302121731056</v>
       </c>
       <c r="M74" s="13" t="n">
-        <v>52.9358965200162</v>
+        <v>52.4086300069795</v>
       </c>
       <c r="N74" s="14" t="n">
-        <v>52.9358965200162</v>
+        <v>52.4086300069795</v>
       </c>
       <c r="O74" s="15" t="n">
-        <v>0.0716827183209285</v>
+        <v>0.0439438141725794</v>
       </c>
       <c r="P74" s="16" t="n">
-        <v>0.15682238479949</v>
+        <v>0.16220862762153</v>
       </c>
       <c r="Q74" s="17" t="n">
-        <v>0.074314429697627</v>
+        <v>0.0449236433395883</v>
       </c>
       <c r="R74" s="18" t="n">
-        <v>0.994001901133254</v>
+        <v>0.984235192519439</v>
       </c>
       <c r="S74" s="19" t="n">
-        <v>1.09170709082502</v>
+        <v>1.10332437779999</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B75" s="2" t="n">
         <v>55.609</v>
@@ -5737,130 +5792,182 @@
         <v>55.609</v>
       </c>
       <c r="F75" s="6" t="n">
-        <v>1.0071947579905</v>
+        <v>1.07184376052507</v>
       </c>
       <c r="G75" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H75" s="8" t="n">
-        <v>55.2313750409053</v>
+        <v>51.4455562648867</v>
       </c>
       <c r="I75" s="9" t="n">
-        <v>48.4073486323651</v>
+        <v>47.2780678878016</v>
       </c>
       <c r="J75" s="10" t="n">
-        <v>50.2692812048025</v>
+        <v>47.7154450588474</v>
       </c>
       <c r="K75" s="11" t="n">
-        <v>55.2117647146497</v>
+        <v>51.8816286925611</v>
       </c>
       <c r="L75" s="12" t="n">
-        <v>55.2117647146497</v>
+        <v>51.8816286925611</v>
       </c>
       <c r="M75" s="13" t="n">
-        <v>54.7347443664416</v>
+        <v>50.9575037053582</v>
       </c>
       <c r="N75" s="14" t="n">
-        <v>54.7347443664416</v>
+        <v>50.9575037053582</v>
       </c>
       <c r="O75" s="15" t="n">
-        <v>0.0334170062651723</v>
+        <v>-0.0280792478655594</v>
       </c>
       <c r="P75" s="16" t="n">
-        <v>0.187214793624501</v>
+        <v>0.110917937276066</v>
       </c>
       <c r="Q75" s="17" t="n">
-        <v>0.0339816261682691</v>
+        <v>-0.0276886898479891</v>
       </c>
       <c r="R75" s="18" t="n">
-        <v>0.991008178338926</v>
+        <v>0.990513222230205</v>
       </c>
       <c r="S75" s="19" t="n">
-        <v>1.13071147073414</v>
+        <v>1.07782542692499</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>126</v>
-      </c>
-      <c r="B76" s="2"/>
+        <v>125</v>
+      </c>
+      <c r="B76" s="2" t="n">
+        <v>44.919</v>
+      </c>
       <c r="C76" s="3" t="n">
-        <v>56.4876353575776</v>
+        <v>44.919</v>
       </c>
       <c r="D76" s="4" t="n">
-        <v>66.5212652070646</v>
+        <v>44.919</v>
       </c>
       <c r="E76" s="5" t="n">
-        <v>47.9674122005693</v>
+        <v>44.919</v>
       </c>
       <c r="F76" s="6" t="n">
-        <v>1.01187571699545</v>
-      </c>
-      <c r="G76" s="7"/>
-      <c r="H76" s="8"/>
-      <c r="I76" s="9"/>
-      <c r="J76" s="10"/>
-      <c r="K76" s="11"/>
-      <c r="L76" s="12"/>
-      <c r="M76" s="13"/>
+        <v>0.971504245057564</v>
+      </c>
+      <c r="G76" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H76" s="8" t="n">
+        <v>46.9229707211691</v>
+      </c>
+      <c r="I76" s="9" t="n">
+        <v>47.0524689602646</v>
+      </c>
+      <c r="J76" s="10" t="n">
+        <v>47.7262054281675</v>
+      </c>
+      <c r="K76" s="11" t="n">
+        <v>46.2365452632051</v>
+      </c>
+      <c r="L76" s="12" t="n">
+        <v>46.2365452632051</v>
+      </c>
+      <c r="M76" s="13" t="n">
+        <v>47.2946002443884</v>
+      </c>
       <c r="N76" s="14" t="n">
-        <v>55.8246772887343</v>
-      </c>
-      <c r="O76" s="15"/>
-      <c r="P76" s="16"/>
-      <c r="Q76" s="17"/>
-      <c r="R76" s="18"/>
-      <c r="S76" s="19"/>
+        <v>47.2946002443884</v>
+      </c>
+      <c r="O76" s="15" t="n">
+        <v>-0.0745958954473433</v>
+      </c>
+      <c r="P76" s="16" t="n">
+        <v>-0.000988147372665837</v>
+      </c>
+      <c r="Q76" s="17" t="n">
+        <v>-0.0718815325442367</v>
+      </c>
+      <c r="R76" s="18" t="n">
+        <v>1.00791999137113</v>
+      </c>
+      <c r="S76" s="19" t="n">
+        <v>1.00514598467359</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>127</v>
-      </c>
-      <c r="B77" s="2"/>
+        <v>126</v>
+      </c>
+      <c r="B77" s="2" t="n">
+        <v>43.842</v>
+      </c>
       <c r="C77" s="3" t="n">
-        <v>58.4177336315206</v>
+        <v>43.842</v>
       </c>
       <c r="D77" s="4" t="n">
-        <v>71.7496013502984</v>
+        <v>43.842</v>
       </c>
       <c r="E77" s="5" t="n">
-        <v>47.5630740578198</v>
+        <v>43.842</v>
       </c>
       <c r="F77" s="6" t="n">
-        <v>1.00870758171269</v>
-      </c>
-      <c r="G77" s="7"/>
-      <c r="H77" s="8"/>
-      <c r="I77" s="9"/>
-      <c r="J77" s="10"/>
-      <c r="K77" s="11"/>
-      <c r="L77" s="12"/>
-      <c r="M77" s="13"/>
+        <v>0.978099037828492</v>
+      </c>
+      <c r="G77" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H77" s="8" t="n">
+        <v>45.1194985311692</v>
+      </c>
+      <c r="I77" s="9" t="n">
+        <v>46.8256188220629</v>
+      </c>
+      <c r="J77" s="10" t="n">
+        <v>47.7224718470452</v>
+      </c>
+      <c r="K77" s="11" t="n">
+        <v>44.8236817585824</v>
+      </c>
+      <c r="L77" s="12" t="n">
+        <v>44.8236817585824</v>
+      </c>
+      <c r="M77" s="13" t="n">
+        <v>45.2946362601233</v>
+      </c>
       <c r="N77" s="14" t="n">
-        <v>57.9134475546747</v>
-      </c>
-      <c r="O77" s="15"/>
-      <c r="P77" s="16"/>
-      <c r="Q77" s="17"/>
-      <c r="R77" s="18"/>
-      <c r="S77" s="19"/>
+        <v>45.2946362601233</v>
+      </c>
+      <c r="O77" s="15" t="n">
+        <v>-0.0432075086182897</v>
+      </c>
+      <c r="P77" s="16" t="n">
+        <v>-0.0969152153306347</v>
+      </c>
+      <c r="Q77" s="17" t="n">
+        <v>-0.0422873641796434</v>
+      </c>
+      <c r="R77" s="18" t="n">
+        <v>1.00388164174372</v>
+      </c>
+      <c r="S77" s="19" t="n">
+        <v>0.967304595209787</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B78" s="2"/>
       <c r="C78" s="3" t="n">
-        <v>58.3225134197315</v>
+        <v>45.174846991025</v>
       </c>
       <c r="D78" s="4" t="n">
-        <v>74.2088726833736</v>
+        <v>53.4823964439734</v>
       </c>
       <c r="E78" s="5" t="n">
-        <v>45.8370468192932</v>
+        <v>38.1577292034843</v>
       </c>
       <c r="F78" s="6" t="n">
-        <v>0.973052638550147</v>
+        <v>0.977317713596562</v>
       </c>
       <c r="G78" s="7"/>
       <c r="H78" s="8"/>
@@ -5870,7 +5977,7 @@
       <c r="L78" s="12"/>
       <c r="M78" s="13"/>
       <c r="N78" s="14" t="n">
-        <v>59.9376756293805</v>
+        <v>46.2232970532991</v>
       </c>
       <c r="O78" s="15"/>
       <c r="P78" s="16"/>
@@ -5880,20 +5987,20 @@
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B79" s="2"/>
       <c r="C79" s="3" t="n">
-        <v>61.8575568816728</v>
+        <v>48.779394229133</v>
       </c>
       <c r="D79" s="4" t="n">
-        <v>81.0715885512487</v>
+        <v>60.8343835218166</v>
       </c>
       <c r="E79" s="5" t="n">
-        <v>47.1972661661932</v>
+        <v>39.113231097474</v>
       </c>
       <c r="F79" s="6" t="n">
-        <v>1.00799077452423</v>
+        <v>1.08430201466051</v>
       </c>
       <c r="G79" s="7"/>
       <c r="H79" s="8"/>
@@ -5903,7 +6010,7 @@
       <c r="L79" s="12"/>
       <c r="M79" s="13"/>
       <c r="N79" s="14" t="n">
-        <v>61.3671855388453</v>
+        <v>44.986907309589</v>
       </c>
       <c r="O79" s="15"/>
       <c r="P79" s="16"/>
@@ -5913,13 +6020,21 @@
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B80" s="2"/>
-      <c r="C80" s="3"/>
-      <c r="D80" s="4"/>
-      <c r="E80" s="5"/>
-      <c r="F80" s="6"/>
+      <c r="C80" s="3" t="n">
+        <v>41.1188859496109</v>
+      </c>
+      <c r="D80" s="4" t="n">
+        <v>53.4763814959196</v>
+      </c>
+      <c r="E80" s="5" t="n">
+        <v>31.6170005232333</v>
+      </c>
+      <c r="F80" s="6" t="n">
+        <v>0.958990209941539</v>
+      </c>
       <c r="G80" s="7"/>
       <c r="H80" s="8"/>
       <c r="I80" s="9"/>
@@ -5927,7 +6042,9 @@
       <c r="K80" s="11"/>
       <c r="L80" s="12"/>
       <c r="M80" s="13"/>
-      <c r="N80" s="14"/>
+      <c r="N80" s="14" t="n">
+        <v>42.8772739526898</v>
+      </c>
       <c r="O80" s="15"/>
       <c r="P80" s="16"/>
       <c r="Q80" s="17"/>
@@ -5936,13 +6053,21 @@
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B81" s="2"/>
-      <c r="C81" s="3"/>
-      <c r="D81" s="4"/>
-      <c r="E81" s="5"/>
-      <c r="F81" s="6"/>
+      <c r="C81" s="3" t="n">
+        <v>40.7615352549826</v>
+      </c>
+      <c r="D81" s="4" t="n">
+        <v>54.9603691374794</v>
+      </c>
+      <c r="E81" s="5" t="n">
+        <v>30.2309242535663</v>
+      </c>
+      <c r="F81" s="6" t="n">
+        <v>0.97516304352839</v>
+      </c>
       <c r="G81" s="7"/>
       <c r="H81" s="8"/>
       <c r="I81" s="9"/>
@@ -5950,7 +6075,9 @@
       <c r="K81" s="11"/>
       <c r="L81" s="12"/>
       <c r="M81" s="13"/>
-      <c r="N81" s="14"/>
+      <c r="N81" s="14" t="n">
+        <v>41.7997129049281</v>
+      </c>
       <c r="O81" s="15"/>
       <c r="P81" s="16"/>
       <c r="Q81" s="17"/>
@@ -5959,7 +6086,7 @@
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B82" s="2"/>
       <c r="C82" s="3"/>
@@ -5982,7 +6109,7 @@
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B83" s="2"/>
       <c r="C83" s="3"/>
@@ -6005,7 +6132,7 @@
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B84" s="2"/>
       <c r="C84" s="3"/>
@@ -6028,7 +6155,7 @@
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B85" s="2"/>
       <c r="C85" s="3"/>
@@ -6051,7 +6178,7 @@
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B86" s="2"/>
       <c r="C86" s="3"/>
@@ -6074,7 +6201,7 @@
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B87" s="2"/>
       <c r="C87" s="3"/>
@@ -6097,7 +6224,7 @@
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B88" s="2"/>
       <c r="C88" s="3"/>
@@ -6120,7 +6247,7 @@
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B89" s="2"/>
       <c r="C89" s="3"/>
@@ -6143,7 +6270,7 @@
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B90" s="2"/>
       <c r="C90" s="3"/>
@@ -6166,7 +6293,7 @@
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B91" s="2"/>
       <c r="C91" s="3"/>
@@ -6189,7 +6316,7 @@
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B92" s="2"/>
       <c r="C92" s="3"/>
@@ -6212,7 +6339,7 @@
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B93" s="2"/>
       <c r="C93" s="3"/>
@@ -6235,7 +6362,7 @@
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B94" s="2"/>
       <c r="C94" s="3"/>
@@ -6258,7 +6385,7 @@
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B95" s="2"/>
       <c r="C95" s="3"/>
@@ -6281,7 +6408,7 @@
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B96" s="2"/>
       <c r="C96" s="3"/>
@@ -6304,7 +6431,7 @@
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B97" s="2"/>
       <c r="C97" s="3"/>
@@ -6338,150 +6465,98 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
+        <v>147</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
         <v>148</v>
       </c>
-      <c r="B2" s="1"/>
     </row>
     <row r="3">
-      <c r="A3"/>
-      <c r="B3" s="1"/>
+      <c r="A3" t="s">
+        <v>149</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>149</v>
-      </c>
-      <c r="B4" s="1"/>
+        <v>150</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>150</v>
-      </c>
-      <c r="B5" s="1" t="n">
-        <v>0.245138351461809</v>
+        <v>151</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>151</v>
-      </c>
-      <c r="B6" s="1" t="n">
-        <v>0.0932531607870792</v>
+        <v>152</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>152</v>
-      </c>
-      <c r="B7" s="1" t="n">
-        <v>-0.0689246310431812</v>
+        <v>153</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>153</v>
-      </c>
-      <c r="B8" s="1" t="n">
-        <v>-0.00416283298210178</v>
+        <v>154</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>154</v>
-      </c>
-      <c r="B9" s="1" t="n">
-        <v>0.149943812535485</v>
+        <v>155</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>155</v>
-      </c>
-      <c r="B10" s="1" t="n">
-        <v>0.155867077686469</v>
+        <v>156</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>156</v>
-      </c>
-      <c r="B11" s="1" t="n">
-        <v>0.025585120444721</v>
+        <v>157</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>157</v>
-      </c>
-      <c r="B12" s="1" t="n">
-        <v>-0.102459980217711</v>
+        <v>158</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>158</v>
-      </c>
-      <c r="B13" s="1" t="n">
-        <v>-0.116840089348192</v>
+        <v>159</v>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="1"/>
+      <c r="A14" t="s">
+        <v>160</v>
+      </c>
     </row>
     <row r="15">
-      <c r="B15" s="1"/>
+      <c r="A15" t="s">
+        <v>161</v>
+      </c>
     </row>
     <row r="16">
-      <c r="B16" s="1"/>
+      <c r="A16" t="s">
+        <v>162</v>
+      </c>
     </row>
     <row r="17">
-      <c r="B17" s="1"/>
+      <c r="A17" t="s">
+        <v>163</v>
+      </c>
     </row>
     <row r="18">
-      <c r="B18" s="1"/>
+      <c r="A18" t="s">
+        <v>164</v>
+      </c>
     </row>
     <row r="19">
-      <c r="B19" s="1"/>
-    </row>
-    <row r="20">
-      <c r="B20" s="1"/>
-    </row>
-    <row r="21">
-      <c r="B21" s="1"/>
-    </row>
-    <row r="22">
-      <c r="B22" s="1"/>
-    </row>
-    <row r="23">
-      <c r="B23" s="1"/>
-    </row>
-    <row r="24">
-      <c r="B24" s="1"/>
-    </row>
-    <row r="25">
-      <c r="B25" s="1"/>
-    </row>
-    <row r="26">
-      <c r="B26" s="1"/>
-    </row>
-    <row r="27">
-      <c r="B27" s="1"/>
-    </row>
-    <row r="28">
-      <c r="B28" s="1"/>
-    </row>
-    <row r="29">
-      <c r="B29" s="1"/>
-    </row>
-    <row r="30">
-      <c r="B30" s="1"/>
+      <c r="A19" t="s">
+        <v>165</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6489,235 +6564,160 @@
 </worksheet>
 </file>
 
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100C5B9F2161CEE1040BBC03CB11300495F" ma:contentTypeVersion="12" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="a7cec21613a3259523bdab11a1e26aca">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b5dd4176-d247-4204-85b8-921214f3ccea" xmlns:ns3="359b39ce-e1f9-4933-8424-33b611e6fdcd" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="68943c349d3a016936c8f8cb3335004b" ns2:_="" ns3:_="">
-    <xsd:import namespace="b5dd4176-d247-4204-85b8-921214f3ccea"/>
-    <xsd:import namespace="359b39ce-e1f9-4933-8424-33b611e6fdcd"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="b5dd4176-d247-4204-85b8-921214f3ccea" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="11" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Etiquetas de imagen" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="01529062-7a8b-4d76-943d-e0db5644ee6d" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="15" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="16" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="17" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="18" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="19" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="359b39ce-e1f9-4933-8424-33b611e6fdcd" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="TaxCatchAll" ma:index="14" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{c9b73259-0823-4f05-8927-4a40ee49fbe1}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="359b39ce-e1f9-4933-8424-33b611e6fdcd">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Tipo de contenido"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Título"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="359b39ce-e1f9-4933-8424-33b611e6fdcd" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b5dd4176-d247-4204-85b8-921214f3ccea">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DEBFCC0A-D7D5-47A5-8F28-8F22660A55BA}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E1BAE1AB-6C81-4CAF-BAE1-CC933EB5E755}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{91265EB2-ADEF-4A1F-AB7A-75EF0E30CE37}"/>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>166</v>
+      </c>
+      <c r="B2" s="1"/>
+    </row>
+    <row r="3">
+      <c r="A3"/>
+      <c r="B3" s="1"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>167</v>
+      </c>
+      <c r="B4" s="1"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>168</v>
+      </c>
+      <c r="B5" s="1" t="n">
+        <v>0.275871470742881</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>169</v>
+      </c>
+      <c r="B6" s="1" t="n">
+        <v>0.0970950569594505</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>170</v>
+      </c>
+      <c r="B7" s="1" t="n">
+        <v>-0.0946392673146209</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>171</v>
+      </c>
+      <c r="B8" s="1" t="n">
+        <v>-0.0307821719066232</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>172</v>
+      </c>
+      <c r="B9" s="1" t="n">
+        <v>0.149597073492798</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>173</v>
+      </c>
+      <c r="B10" s="1" t="n">
+        <v>0.1656656969087</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>174</v>
+      </c>
+      <c r="B11" s="1" t="n">
+        <v>-0.0149014000970461</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>175</v>
+      </c>
+      <c r="B12" s="1" t="n">
+        <v>-0.206697253603492</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>176</v>
+      </c>
+      <c r="B13" s="1" t="n">
+        <v>-0.186360528193574</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="1"/>
+    </row>
+    <row r="15">
+      <c r="B15" s="1"/>
+    </row>
+    <row r="16">
+      <c r="B16" s="1"/>
+    </row>
+    <row r="17">
+      <c r="B17" s="1"/>
+    </row>
+    <row r="18">
+      <c r="B18" s="1"/>
+    </row>
+    <row r="19">
+      <c r="B19" s="1"/>
+    </row>
+    <row r="20">
+      <c r="B20" s="1"/>
+    </row>
+    <row r="21">
+      <c r="B21" s="1"/>
+    </row>
+    <row r="22">
+      <c r="B22" s="1"/>
+    </row>
+    <row r="23">
+      <c r="B23" s="1"/>
+    </row>
+    <row r="24">
+      <c r="B24" s="1"/>
+    </row>
+    <row r="25">
+      <c r="B25" s="1"/>
+    </row>
+    <row r="26">
+      <c r="B26" s="1"/>
+    </row>
+    <row r="27">
+      <c r="B27" s="1"/>
+    </row>
+    <row r="28">
+      <c r="B28" s="1"/>
+    </row>
+    <row r="29">
+      <c r="B29" s="1"/>
+    </row>
+    <row r="30">
+      <c r="B30" s="1"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
 </file>
--- a/indicadores/GSF-EPUB_out.xlsx
+++ b/indicadores/GSF-EPUB_out.xlsx
@@ -6720,4 +6720,237 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100C5B9F2161CEE1040BBC03CB11300495F" ma:contentTypeVersion="12" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="a7cec21613a3259523bdab11a1e26aca">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b5dd4176-d247-4204-85b8-921214f3ccea" xmlns:ns3="359b39ce-e1f9-4933-8424-33b611e6fdcd" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="68943c349d3a016936c8f8cb3335004b" ns2:_="" ns3:_="">
+    <xsd:import namespace="b5dd4176-d247-4204-85b8-921214f3ccea"/>
+    <xsd:import namespace="359b39ce-e1f9-4933-8424-33b611e6fdcd"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="b5dd4176-d247-4204-85b8-921214f3ccea" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="11" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Etiquetas de imagen" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="01529062-7a8b-4d76-943d-e0db5644ee6d" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="15" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="16" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="17" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="18" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="19" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="359b39ce-e1f9-4933-8424-33b611e6fdcd" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="TaxCatchAll" ma:index="14" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{c9b73259-0823-4f05-8927-4a40ee49fbe1}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="359b39ce-e1f9-4933-8424-33b611e6fdcd">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Tipo de contenido"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Título"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="359b39ce-e1f9-4933-8424-33b611e6fdcd" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b5dd4176-d247-4204-85b8-921214f3ccea">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ECDC6ACE-C0A2-43B8-AE2D-64130EE5F484}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F44FE9A6-F6BD-4A06-9DEC-297FF880177E}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C22993D0-D0CE-43CC-BA7D-1EB11030C5A8}"/>
 </file>
--- a/indicadores/GSF-EPUB_out.xlsx
+++ b/indicadores/GSF-EPUB_out.xlsx
@@ -110,7 +110,7 @@
     <t xml:space="preserve">Usuario</t>
   </si>
   <si>
-    <t xml:space="preserve">vcorvalan</t>
+    <t xml:space="preserve">pcohan</t>
   </si>
   <si>
     <t xml:space="preserve">fecha</t>
@@ -6944,13 +6944,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ECDC6ACE-C0A2-43B8-AE2D-64130EE5F484}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7F0E3F6F-DDC6-4ABF-B73D-38F14947BDBA}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F44FE9A6-F6BD-4A06-9DEC-297FF880177E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B7FC476B-62D8-4B68-8015-057B88579772}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C22993D0-D0CE-43CC-BA7D-1EB11030C5A8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5B7FA95A-549A-4098-91BC-39EC262178B4}"/>
 </file>
--- a/indicadores/GSF-EPUB_out.xlsx
+++ b/indicadores/GSF-EPUB_out.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="179">
   <si>
     <t xml:space="preserve"/>
   </si>
@@ -23,7 +23,7 @@
     <t xml:space="preserve">Título</t>
   </si>
   <si>
-    <t xml:space="preserve">Ocupados en el sector público del Gran Santa Fe</t>
+    <t xml:space="preserve">Ocupados en el sector público</t>
   </si>
   <si>
     <t xml:space="preserve">Unidad de medida</t>
@@ -71,6 +71,12 @@
     <t xml:space="preserve">Regresores</t>
   </si>
   <si>
+    <t xml:space="preserve">Alcance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aglomerado Gran Santa Fe</t>
+  </si>
+  <si>
     <t xml:space="preserve">Resumen del correlograma</t>
   </si>
   <si>
@@ -104,13 +110,13 @@
     <t xml:space="preserve">Fecha</t>
   </si>
   <si>
-    <t xml:space="preserve">07/05/2026</t>
+    <t xml:space="preserve">17/06/2026</t>
   </si>
   <si>
     <t xml:space="preserve">Usuario</t>
   </si>
   <si>
-    <t xml:space="preserve">pcohan</t>
+    <t xml:space="preserve">focampo</t>
   </si>
   <si>
     <t xml:space="preserve">fecha</t>
@@ -1047,9 +1053,13 @@
       <c r="J6" s="1"/>
     </row>
     <row r="7">
-      <c r="A7"/>
+      <c r="A7" t="s">
+        <v>18</v>
+      </c>
       <c r="B7"/>
-      <c r="C7"/>
+      <c r="C7" t="s">
+        <v>19</v>
+      </c>
       <c r="D7"/>
       <c r="E7"/>
       <c r="F7"/>
@@ -1060,7 +1070,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B8"/>
       <c r="C8"/>
@@ -1074,12 +1084,12 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B9"/>
       <c r="C9"/>
       <c r="D9" t="n">
-        <v>0.275871470742881</v>
+        <v>0.268324339798877</v>
       </c>
       <c r="E9"/>
       <c r="F9"/>
@@ -1090,7 +1100,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B10"/>
       <c r="C10"/>
@@ -1118,7 +1128,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B12"/>
       <c r="C12"/>
@@ -1132,12 +1142,12 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B13"/>
       <c r="C13"/>
       <c r="D13" t="n">
-        <v>0.0223792843976097</v>
+        <v>0.0251878407593091</v>
       </c>
       <c r="E13"/>
       <c r="F13"/>
@@ -1160,7 +1170,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B15"/>
       <c r="C15"/>
@@ -1174,7 +1184,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B16"/>
       <c r="C16"/>
@@ -1188,7 +1198,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B17"/>
       <c r="C17"/>
@@ -1202,12 +1212,12 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B18"/>
       <c r="C18"/>
       <c r="D18" t="n">
-        <v>0.00704157508379751</v>
+        <v>0.00872811059952</v>
       </c>
       <c r="E18"/>
       <c r="F18"/>
@@ -1218,7 +1228,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B19"/>
       <c r="C19"/>
@@ -1232,12 +1242,12 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B20"/>
       <c r="C20"/>
       <c r="D20" t="n">
-        <v>0.79818838924137</v>
+        <v>0.874084652090649</v>
       </c>
       <c r="E20"/>
       <c r="F20"/>
@@ -1380,10 +1390,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C32"/>
       <c r="D32"/>
@@ -1396,10 +1406,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C33"/>
       <c r="D33"/>
@@ -1423,66 +1433,66 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="H1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="K1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="L1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="M1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="N1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="P1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="Q1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="R1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="S1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B2" s="2" t="n">
         <v>40.382</v>
@@ -1535,7 +1545,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B3" s="2" t="n">
         <v>39.128</v>
@@ -1592,7 +1602,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B4" s="2" t="n">
         <v>41.255</v>
@@ -1649,7 +1659,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B5" s="2" t="n">
         <v>38.135</v>
@@ -1706,7 +1716,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B6" s="2" t="n">
         <v>39.451</v>
@@ -1765,7 +1775,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B7" s="2" t="n">
         <v>36.088</v>
@@ -1824,7 +1834,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B8" s="2" t="n">
         <v>35.364</v>
@@ -1883,7 +1893,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B9" s="2" t="n">
         <v>38.249</v>
@@ -1942,7 +1952,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B10" s="2" t="n">
         <v>35.512</v>
@@ -2001,7 +2011,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B11" s="2" t="n">
         <v>42.694</v>
@@ -2060,7 +2070,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B12" s="2" t="n">
         <v>43.215</v>
@@ -2119,7 +2129,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B13" s="2" t="n">
         <v>38.854</v>
@@ -2178,7 +2188,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B14" s="2" t="n">
         <v>44.001</v>
@@ -2237,7 +2247,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B15" s="2" t="n">
         <v>44.777</v>
@@ -2296,7 +2306,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B16" s="2" t="n">
         <v>43.288</v>
@@ -2355,7 +2365,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B17" s="2" t="n">
         <v>42.023</v>
@@ -2414,7 +2424,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B18" s="2" t="n">
         <v>48.478</v>
@@ -2473,7 +2483,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B19" s="2" t="n">
         <v>51.223</v>
@@ -2532,7 +2542,7 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B20" s="2" t="n">
         <v>42.247</v>
@@ -2591,7 +2601,7 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B21" s="2" t="n">
         <v>46.849</v>
@@ -2650,7 +2660,7 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B22" s="2" t="n">
         <v>58.259</v>
@@ -2709,7 +2719,7 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B23" s="2" t="n">
         <v>53.977</v>
@@ -2768,7 +2778,7 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B24" s="2" t="n">
         <v>47.06</v>
@@ -2827,7 +2837,7 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B25" s="2" t="n">
         <v>49.032</v>
@@ -2886,7 +2896,7 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B26" s="2" t="n">
         <v>54.016</v>
@@ -2945,7 +2955,7 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B27" s="2" t="n">
         <v>51.252</v>
@@ -3004,7 +3014,7 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B28" s="2" t="n">
         <v>48.855</v>
@@ -3063,7 +3073,7 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B29" s="2" t="n">
         <v>46.384</v>
@@ -3122,7 +3132,7 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B30" s="2" t="n">
         <v>48.182</v>
@@ -3181,7 +3191,7 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B31" s="2" t="n">
         <v>42.801</v>
@@ -3240,7 +3250,7 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B32" s="2" t="n">
         <v>41.173</v>
@@ -3299,7 +3309,7 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B33" s="2" t="n">
         <v>46.762</v>
@@ -3358,7 +3368,7 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B34" s="2" t="n">
         <v>49.253</v>
@@ -3417,7 +3427,7 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B35" s="2" t="n">
         <v>43.98</v>
@@ -3476,7 +3486,7 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B36" s="2" t="n">
         <v>42.412</v>
@@ -3535,7 +3545,7 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B37" s="2" t="n">
         <v>50.32</v>
@@ -3594,7 +3604,7 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B38" s="2" t="n">
         <v>52.582</v>
@@ -3653,7 +3663,7 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B39" s="2" t="n">
         <v>44.65</v>
@@ -3712,7 +3722,7 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B40" s="2" t="n">
         <v>43.651</v>
@@ -3771,7 +3781,7 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B41" s="2" t="n">
         <v>53.878</v>
@@ -3830,7 +3840,7 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B42" s="2" t="n">
         <v>55.911</v>
@@ -3889,7 +3899,7 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B43" s="2" t="n">
         <v>47.518</v>
@@ -3948,7 +3958,7 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B44" s="2" t="n">
         <v>48.053</v>
@@ -4007,7 +4017,7 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B45" s="2" t="n">
         <v>52.985</v>
@@ -4066,7 +4076,7 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B46" s="2" t="n">
         <v>53.805</v>
@@ -4125,7 +4135,7 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B47" s="2" t="n">
         <v>51.089</v>
@@ -4184,7 +4194,7 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B48" s="2" t="n">
         <v>53.311</v>
@@ -4243,7 +4253,7 @@
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B49" s="2" t="n">
         <v>57.045</v>
@@ -4302,7 +4312,7 @@
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B50" s="2" t="n">
         <v>58.277</v>
@@ -4361,7 +4371,7 @@
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B51" s="2" t="n">
         <v>51.191</v>
@@ -4420,7 +4430,7 @@
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B52" s="2" t="n">
         <v>56.535</v>
@@ -4479,7 +4489,7 @@
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B53" s="2" t="n">
         <v>62.113</v>
@@ -4538,7 +4548,7 @@
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B54" s="2" t="n">
         <v>53.27</v>
@@ -4597,7 +4607,7 @@
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B55" s="2" t="n">
         <v>48.455</v>
@@ -4656,7 +4666,7 @@
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B56" s="2" t="n">
         <v>49.068</v>
@@ -4715,7 +4725,7 @@
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B57" s="2" t="n">
         <v>53.828</v>
@@ -4774,7 +4784,7 @@
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B58" s="2" t="n">
         <v>49.391</v>
@@ -4833,7 +4843,7 @@
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B59" s="2" t="n">
         <v>49.029</v>
@@ -4892,7 +4902,7 @@
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B60" s="2" t="n">
         <v>54.484</v>
@@ -4951,7 +4961,7 @@
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B61" s="2" t="n">
         <v>58.759</v>
@@ -5010,7 +5020,7 @@
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B62" s="2" t="n">
         <v>51.099</v>
@@ -5069,7 +5079,7 @@
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B63" s="2" t="n">
         <v>48.786</v>
@@ -5128,7 +5138,7 @@
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B64" s="2" t="n">
         <v>58.929</v>
@@ -5187,7 +5197,7 @@
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B65" s="2" t="n">
         <v>51.654</v>
@@ -5246,7 +5256,7 @@
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B66" s="2" t="n">
         <v>41.524</v>
@@ -5305,7 +5315,7 @@
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B67" s="2" t="n">
         <v>43.751</v>
@@ -5364,7 +5374,7 @@
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B68" s="2" t="n">
         <v>46.819</v>
@@ -5423,7 +5433,7 @@
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B69" s="2" t="n">
         <v>45.535</v>
@@ -5482,7 +5492,7 @@
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B70" s="2" t="n">
         <v>42.418</v>
@@ -5541,7 +5551,7 @@
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B71" s="2" t="n">
         <v>48.256</v>
@@ -5600,7 +5610,7 @@
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B72" s="2" t="n">
         <v>46.223</v>
@@ -5659,7 +5669,7 @@
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B73" s="2" t="n">
         <v>49.692</v>
@@ -5718,7 +5728,7 @@
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B74" s="2" t="n">
         <v>51.943</v>
@@ -5777,7 +5787,7 @@
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B75" s="2" t="n">
         <v>55.609</v>
@@ -5836,7 +5846,7 @@
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B76" s="2" t="n">
         <v>44.919</v>
@@ -5895,7 +5905,7 @@
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B77" s="2" t="n">
         <v>43.842</v>
@@ -5954,7 +5964,7 @@
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B78" s="2"/>
       <c r="C78" s="3" t="n">
@@ -5987,7 +5997,7 @@
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B79" s="2"/>
       <c r="C79" s="3" t="n">
@@ -6020,7 +6030,7 @@
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B80" s="2"/>
       <c r="C80" s="3" t="n">
@@ -6053,7 +6063,7 @@
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B81" s="2"/>
       <c r="C81" s="3" t="n">
@@ -6086,7 +6096,7 @@
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B82" s="2"/>
       <c r="C82" s="3"/>
@@ -6109,7 +6119,7 @@
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B83" s="2"/>
       <c r="C83" s="3"/>
@@ -6132,7 +6142,7 @@
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B84" s="2"/>
       <c r="C84" s="3"/>
@@ -6155,7 +6165,7 @@
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B85" s="2"/>
       <c r="C85" s="3"/>
@@ -6178,7 +6188,7 @@
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B86" s="2"/>
       <c r="C86" s="3"/>
@@ -6201,7 +6211,7 @@
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B87" s="2"/>
       <c r="C87" s="3"/>
@@ -6224,7 +6234,7 @@
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B88" s="2"/>
       <c r="C88" s="3"/>
@@ -6247,7 +6257,7 @@
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B89" s="2"/>
       <c r="C89" s="3"/>
@@ -6270,7 +6280,7 @@
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B90" s="2"/>
       <c r="C90" s="3"/>
@@ -6293,7 +6303,7 @@
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B91" s="2"/>
       <c r="C91" s="3"/>
@@ -6316,7 +6326,7 @@
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B92" s="2"/>
       <c r="C92" s="3"/>
@@ -6339,7 +6349,7 @@
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B93" s="2"/>
       <c r="C93" s="3"/>
@@ -6362,7 +6372,7 @@
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B94" s="2"/>
       <c r="C94" s="3"/>
@@ -6385,7 +6395,7 @@
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B95" s="2"/>
       <c r="C95" s="3"/>
@@ -6408,7 +6418,7 @@
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B96" s="2"/>
       <c r="C96" s="3"/>
@@ -6431,7 +6441,7 @@
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B97" s="2"/>
       <c r="C97" s="3"/>
@@ -6465,97 +6475,97 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
   </sheetData>
@@ -6579,7 +6589,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B2" s="1"/>
     </row>
@@ -6589,80 +6599,80 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B4" s="1"/>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B5" s="1" t="n">
-        <v>0.275871470742881</v>
+        <v>0.268324339798877</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B6" s="1" t="n">
-        <v>0.0970950569594505</v>
+        <v>0.0923100736222232</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B7" s="1" t="n">
-        <v>-0.0946392673146209</v>
+        <v>-0.0904329959563043</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B8" s="1" t="n">
-        <v>-0.0307821719066232</v>
+        <v>-0.021206475320898</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B9" s="1" t="n">
-        <v>0.149597073492798</v>
+        <v>0.158706776034639</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B10" s="1" t="n">
-        <v>0.1656656969087</v>
+        <v>0.165413094411826</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B11" s="1" t="n">
-        <v>-0.0149014000970461</v>
+        <v>-0.0237510641572777</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B12" s="1" t="n">
-        <v>-0.206697253603492</v>
+        <v>-0.208647825294298</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B13" s="1" t="n">
-        <v>-0.186360528193574</v>
+        <v>-0.178440807103116</v>
       </c>
     </row>
     <row r="14">
@@ -6720,237 +6730,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100C5B9F2161CEE1040BBC03CB11300495F" ma:contentTypeVersion="12" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="a7cec21613a3259523bdab11a1e26aca">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b5dd4176-d247-4204-85b8-921214f3ccea" xmlns:ns3="359b39ce-e1f9-4933-8424-33b611e6fdcd" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="68943c349d3a016936c8f8cb3335004b" ns2:_="" ns3:_="">
-    <xsd:import namespace="b5dd4176-d247-4204-85b8-921214f3ccea"/>
-    <xsd:import namespace="359b39ce-e1f9-4933-8424-33b611e6fdcd"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="b5dd4176-d247-4204-85b8-921214f3ccea" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="11" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Etiquetas de imagen" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="01529062-7a8b-4d76-943d-e0db5644ee6d" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="15" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="16" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="17" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="18" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="19" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="359b39ce-e1f9-4933-8424-33b611e6fdcd" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="TaxCatchAll" ma:index="14" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{c9b73259-0823-4f05-8927-4a40ee49fbe1}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="359b39ce-e1f9-4933-8424-33b611e6fdcd">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Tipo de contenido"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Título"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="359b39ce-e1f9-4933-8424-33b611e6fdcd" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b5dd4176-d247-4204-85b8-921214f3ccea">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7F0E3F6F-DDC6-4ABF-B73D-38F14947BDBA}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B7FC476B-62D8-4B68-8015-057B88579772}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5B7FA95A-549A-4098-91BC-39EC262178B4}"/>
 </file>
--- a/indicadores/GSF-EPUB_out.xlsx
+++ b/indicadores/GSF-EPUB_out.xlsx
@@ -110,13 +110,13 @@
     <t xml:space="preserve">Fecha</t>
   </si>
   <si>
-    <t xml:space="preserve">17/06/2026</t>
+    <t xml:space="preserve">04/08/2026</t>
   </si>
   <si>
     <t xml:space="preserve">Usuario</t>
   </si>
   <si>
-    <t xml:space="preserve">focampo</t>
+    <t xml:space="preserve">fleiva</t>
   </si>
   <si>
     <t xml:space="preserve">fecha</t>
@@ -1069,9 +1069,7 @@
       <c r="J7" s="1"/>
     </row>
     <row r="8">
-      <c r="A8" t="s">
-        <v>20</v>
-      </c>
+      <c r="A8"/>
       <c r="B8"/>
       <c r="C8"/>
       <c r="D8"/>
@@ -1083,14 +1081,10 @@
       <c r="J8" s="1"/>
     </row>
     <row r="9">
-      <c r="A9" t="s">
-        <v>21</v>
-      </c>
+      <c r="A9"/>
       <c r="B9"/>
       <c r="C9"/>
-      <c r="D9" t="n">
-        <v>0.268324339798877</v>
-      </c>
+      <c r="D9"/>
       <c r="E9"/>
       <c r="F9"/>
       <c r="G9"/>
@@ -1100,13 +1094,11 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B10"/>
       <c r="C10"/>
-      <c r="D10" t="n">
-        <v>-4</v>
-      </c>
+      <c r="D10"/>
       <c r="E10"/>
       <c r="F10"/>
       <c r="G10"/>
@@ -1115,10 +1107,14 @@
       <c r="J10" s="1"/>
     </row>
     <row r="11">
-      <c r="A11"/>
+      <c r="A11" t="s">
+        <v>21</v>
+      </c>
       <c r="B11"/>
       <c r="C11"/>
-      <c r="D11"/>
+      <c r="D11" t="n">
+        <v>0.267073623824962</v>
+      </c>
       <c r="E11"/>
       <c r="F11"/>
       <c r="G11"/>
@@ -1128,11 +1124,13 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B12"/>
       <c r="C12"/>
-      <c r="D12"/>
+      <c r="D12" t="n">
+        <v>-4</v>
+      </c>
       <c r="E12"/>
       <c r="F12"/>
       <c r="G12"/>
@@ -1141,14 +1139,10 @@
       <c r="J12" s="1"/>
     </row>
     <row r="13">
-      <c r="A13" t="s">
-        <v>24</v>
-      </c>
+      <c r="A13"/>
       <c r="B13"/>
       <c r="C13"/>
-      <c r="D13" t="n">
-        <v>0.0251878407593091</v>
-      </c>
+      <c r="D13"/>
       <c r="E13"/>
       <c r="F13"/>
       <c r="G13"/>
@@ -1157,7 +1151,9 @@
       <c r="J13" s="1"/>
     </row>
     <row r="14">
-      <c r="A14"/>
+      <c r="A14" t="s">
+        <v>23</v>
+      </c>
       <c r="B14"/>
       <c r="C14"/>
       <c r="D14"/>
@@ -1170,11 +1166,13 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B15"/>
       <c r="C15"/>
-      <c r="D15"/>
+      <c r="D15" t="n">
+        <v>0.0235828516511249</v>
+      </c>
       <c r="E15"/>
       <c r="F15"/>
       <c r="G15"/>
@@ -1183,9 +1181,7 @@
       <c r="J15" s="1"/>
     </row>
     <row r="16">
-      <c r="A16" t="s">
-        <v>26</v>
-      </c>
+      <c r="A16"/>
       <c r="B16"/>
       <c r="C16"/>
       <c r="D16"/>
@@ -1198,7 +1194,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B17"/>
       <c r="C17"/>
@@ -1212,13 +1208,11 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B18"/>
       <c r="C18"/>
-      <c r="D18" t="n">
-        <v>0.00872811059952</v>
-      </c>
+      <c r="D18"/>
       <c r="E18"/>
       <c r="F18"/>
       <c r="G18"/>
@@ -1228,7 +1222,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B19"/>
       <c r="C19"/>
@@ -1247,7 +1241,7 @@
       <c r="B20"/>
       <c r="C20"/>
       <c r="D20" t="n">
-        <v>0.874084652090649</v>
+        <v>0.0104417960239753</v>
       </c>
       <c r="E20"/>
       <c r="F20"/>
@@ -1257,7 +1251,9 @@
       <c r="J20" s="1"/>
     </row>
     <row r="21">
-      <c r="A21"/>
+      <c r="A21" t="s">
+        <v>29</v>
+      </c>
       <c r="B21"/>
       <c r="C21"/>
       <c r="D21"/>
@@ -1269,10 +1265,14 @@
       <c r="J21" s="1"/>
     </row>
     <row r="22">
-      <c r="A22"/>
+      <c r="A22" t="s">
+        <v>28</v>
+      </c>
       <c r="B22"/>
       <c r="C22"/>
-      <c r="D22"/>
+      <c r="D22" t="n">
+        <v>0.950109602131833</v>
+      </c>
       <c r="E22"/>
       <c r="F22"/>
       <c r="G22"/>
@@ -1507,40 +1507,40 @@
         <v>40.382</v>
       </c>
       <c r="F2" s="6" t="n">
-        <v>1.03857367775495</v>
+        <v>1.03857367964265</v>
       </c>
       <c r="G2" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H2" s="8" t="n">
-        <v>38.5008451461163</v>
+        <v>38.5008450624263</v>
       </c>
       <c r="I2" s="9" t="n">
-        <v>37.0957764230862</v>
+        <v>37.095376717699</v>
       </c>
       <c r="J2" s="10" t="n">
-        <v>37.9356008052722</v>
+        <v>37.9355960845811</v>
       </c>
       <c r="K2" s="11" t="n">
-        <v>38.8821716407183</v>
+        <v>38.8821715700465</v>
       </c>
       <c r="L2" s="12" t="n">
-        <v>38.8821716407183</v>
+        <v>38.8821715700465</v>
       </c>
       <c r="M2" s="13" t="n">
-        <v>38.8332450584347</v>
+        <v>38.833245007136</v>
       </c>
       <c r="N2" s="14" t="n">
-        <v>38.8332450584347</v>
+        <v>38.833245007136</v>
       </c>
       <c r="O2" s="15"/>
       <c r="P2" s="16"/>
       <c r="Q2" s="17"/>
       <c r="R2" s="18" t="n">
-        <v>1.00863357443342</v>
+        <v>1.0086335752935</v>
       </c>
       <c r="S2" s="19" t="n">
-        <v>1.04683737079748</v>
+        <v>1.04684864916355</v>
       </c>
     </row>
     <row r="3">
@@ -1560,44 +1560,44 @@
         <v>39.128</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>1.01013564306276</v>
+        <v>1.0101356433901</v>
       </c>
       <c r="G3" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H3" s="8" t="n">
-        <v>39.2614676525879</v>
+        <v>39.2614676619919</v>
       </c>
       <c r="I3" s="9" t="n">
-        <v>37.555113815482</v>
+        <v>37.5547554522694</v>
       </c>
       <c r="J3" s="10" t="n">
-        <v>38.0391454880525</v>
+        <v>38.0391423018013</v>
       </c>
       <c r="K3" s="11" t="n">
-        <v>38.7353918938676</v>
+        <v>38.7353918813152</v>
       </c>
       <c r="L3" s="12" t="n">
-        <v>38.7353918938676</v>
+        <v>38.7353918813152</v>
       </c>
       <c r="M3" s="13" t="n">
-        <v>39.2547224378267</v>
+        <v>39.2547224430039</v>
       </c>
       <c r="N3" s="14" t="n">
-        <v>39.2547224378267</v>
+        <v>39.2547224430039</v>
       </c>
       <c r="O3" s="15" t="n">
-        <v>0.0107950427165192</v>
+        <v>0.0107950441694051</v>
       </c>
       <c r="P3" s="16"/>
       <c r="Q3" s="17" t="n">
-        <v>0.0108535194202231</v>
+        <v>0.0108535208888778</v>
       </c>
       <c r="R3" s="18" t="n">
-        <v>0.999828197590043</v>
+        <v>0.999828197482426</v>
       </c>
       <c r="S3" s="19" t="n">
-        <v>1.04525638321043</v>
+        <v>1.04526635762267</v>
       </c>
     </row>
     <row r="4">
@@ -1617,44 +1617,44 @@
         <v>41.255</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>1.01448548243033</v>
+        <v>1.01448547952439</v>
       </c>
       <c r="G4" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H4" s="8" t="n">
-        <v>40.4432576245915</v>
+        <v>40.4432577285976</v>
       </c>
       <c r="I4" s="9" t="n">
-        <v>38.0155677048888</v>
+        <v>38.0152509336225</v>
       </c>
       <c r="J4" s="10" t="n">
-        <v>38.14742302501</v>
+        <v>38.1474213964488</v>
       </c>
       <c r="K4" s="11" t="n">
-        <v>40.6659343228534</v>
+        <v>40.6659344393388</v>
       </c>
       <c r="L4" s="12" t="n">
-        <v>40.6659343228534</v>
+        <v>40.6659344393388</v>
       </c>
       <c r="M4" s="13" t="n">
-        <v>40.1995920351714</v>
+        <v>40.1995921085213</v>
       </c>
       <c r="N4" s="14" t="n">
-        <v>40.1995920351714</v>
+        <v>40.1995921085213</v>
       </c>
       <c r="O4" s="15" t="n">
-        <v>0.023785093316432</v>
+        <v>0.0237850950091886</v>
       </c>
       <c r="P4" s="16"/>
       <c r="Q4" s="17" t="n">
-        <v>0.0240702147070626</v>
+        <v>0.0240702164405642</v>
       </c>
       <c r="R4" s="18" t="n">
-        <v>0.993975124563854</v>
+        <v>0.993975123821343</v>
       </c>
       <c r="S4" s="19" t="n">
-        <v>1.05745078824646</v>
+        <v>1.05745960164022</v>
       </c>
     </row>
     <row r="5">
@@ -1674,44 +1674,44 @@
         <v>38.135</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>0.93626228811317</v>
+        <v>0.936262286435591</v>
       </c>
       <c r="G5" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H5" s="8" t="n">
-        <v>40.4466375430071</v>
+        <v>40.4466375573731</v>
       </c>
       <c r="I5" s="9" t="n">
-        <v>38.4789922621167</v>
+        <v>38.4787178063092</v>
       </c>
       <c r="J5" s="10" t="n">
-        <v>38.268647502351</v>
+        <v>38.2686474938486</v>
       </c>
       <c r="K5" s="11" t="n">
-        <v>40.7311076011111</v>
+        <v>40.7311076740924</v>
       </c>
       <c r="L5" s="12" t="n">
-        <v>40.7311076011111</v>
+        <v>40.7311076740924</v>
       </c>
       <c r="M5" s="13" t="n">
-        <v>40.0372536211082</v>
+        <v>40.0372536325776</v>
       </c>
       <c r="N5" s="14" t="n">
-        <v>40.0372536211082</v>
+        <v>40.0372536325776</v>
       </c>
       <c r="O5" s="15" t="n">
-        <v>-0.00404648598151536</v>
+        <v>-0.00404648751968843</v>
       </c>
       <c r="P5" s="16"/>
       <c r="Q5" s="17" t="n">
-        <v>-0.00403830998884702</v>
+        <v>-0.00403831152080847</v>
       </c>
       <c r="R5" s="18" t="n">
-        <v>0.989878418905313</v>
+        <v>0.989878418837295</v>
       </c>
       <c r="S5" s="19" t="n">
-        <v>1.04049641810723</v>
+        <v>1.04050383991779</v>
       </c>
     </row>
     <row r="6">
@@ -1731,46 +1731,46 @@
         <v>39.451</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>1.03761447936999</v>
+        <v>1.03761448528033</v>
       </c>
       <c r="G6" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H6" s="8" t="n">
-        <v>38.0991948039387</v>
+        <v>38.0991946703334</v>
       </c>
       <c r="I6" s="9" t="n">
-        <v>38.9488981371118</v>
+        <v>38.9486673920714</v>
       </c>
       <c r="J6" s="10" t="n">
-        <v>38.4236255627712</v>
+        <v>38.4236272845399</v>
       </c>
       <c r="K6" s="11" t="n">
-        <v>38.0208649593571</v>
+        <v>38.020864742787</v>
       </c>
       <c r="L6" s="12" t="n">
-        <v>38.0208649593571</v>
+        <v>38.020864742787</v>
       </c>
       <c r="M6" s="13" t="n">
-        <v>38.0680521039114</v>
+        <v>38.0680520070242</v>
       </c>
       <c r="N6" s="14" t="n">
-        <v>38.0680521039114</v>
+        <v>38.0680520070242</v>
       </c>
       <c r="O6" s="15" t="n">
-        <v>-0.0504349582976838</v>
+        <v>-0.0504349611292603</v>
       </c>
       <c r="P6" s="16" t="n">
-        <v>-0.0197045843933955</v>
+        <v>-0.0197045855933822</v>
       </c>
       <c r="Q6" s="17" t="n">
-        <v>-0.0491842306625792</v>
+        <v>-0.0491842333548868</v>
       </c>
       <c r="R6" s="18" t="n">
-        <v>0.999182589023533</v>
+        <v>0.999182589984415</v>
       </c>
       <c r="S6" s="19" t="n">
-        <v>0.977384571186081</v>
+        <v>0.977390359054325</v>
       </c>
     </row>
     <row r="7">
@@ -1790,46 +1790,46 @@
         <v>36.088</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>1.01658139536915</v>
+        <v>1.01658139615351</v>
       </c>
       <c r="G7" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H7" s="8" t="n">
-        <v>35.6315654305241</v>
+        <v>35.6315654034808</v>
       </c>
       <c r="I7" s="9" t="n">
-        <v>39.4302035519074</v>
+        <v>39.4300187563185</v>
       </c>
       <c r="J7" s="10" t="n">
-        <v>38.6454761494596</v>
+        <v>38.6454797599633</v>
       </c>
       <c r="K7" s="11" t="n">
-        <v>35.4993708958203</v>
+        <v>35.4993708684302</v>
       </c>
       <c r="L7" s="12" t="n">
-        <v>35.4993708958203</v>
+        <v>35.4993708684302</v>
       </c>
       <c r="M7" s="13" t="n">
-        <v>36.0209046940948</v>
+        <v>36.0209046851068</v>
       </c>
       <c r="N7" s="14" t="n">
-        <v>36.0209046940948</v>
+        <v>36.0209046851068</v>
       </c>
       <c r="O7" s="15" t="n">
-        <v>-0.0552759470451173</v>
+        <v>-0.0552759447495314</v>
       </c>
       <c r="P7" s="16" t="n">
-        <v>-0.0823803492396061</v>
+        <v>-0.0823803495895928</v>
       </c>
       <c r="Q7" s="17" t="n">
-        <v>-0.0537759957937615</v>
+        <v>-0.053775993621623</v>
       </c>
       <c r="R7" s="18" t="n">
-        <v>1.01092680770172</v>
+        <v>1.01092680821674</v>
       </c>
       <c r="S7" s="19" t="n">
-        <v>0.913535854479562</v>
+        <v>0.913540135695082</v>
       </c>
     </row>
     <row r="8">
@@ -1849,46 +1849,46 @@
         <v>35.364</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>1.00855543782045</v>
+        <v>1.00855543104962</v>
       </c>
       <c r="G8" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H8" s="8" t="n">
-        <v>35.2416118052889</v>
+        <v>35.2416120229061</v>
       </c>
       <c r="I8" s="9" t="n">
-        <v>39.9272467078003</v>
+        <v>39.9271110878039</v>
       </c>
       <c r="J8" s="10" t="n">
-        <v>38.9653044025888</v>
+        <v>38.9653100988507</v>
       </c>
       <c r="K8" s="11" t="n">
-        <v>35.0640120253813</v>
+        <v>35.0640122607799</v>
       </c>
       <c r="L8" s="12" t="n">
-        <v>35.0640120253813</v>
+        <v>35.0640122607799</v>
       </c>
       <c r="M8" s="13" t="n">
-        <v>35.5371007904587</v>
+        <v>35.5371009238796</v>
       </c>
       <c r="N8" s="14" t="n">
-        <v>35.5371007904587</v>
+        <v>35.5371009238796</v>
       </c>
       <c r="O8" s="15" t="n">
-        <v>-0.0135222124291669</v>
+        <v>-0.0135222084252348</v>
       </c>
       <c r="P8" s="16" t="n">
-        <v>-0.115983546316424</v>
+        <v>-0.115983544610478</v>
       </c>
       <c r="Q8" s="17" t="n">
-        <v>-0.0134311980152841</v>
+        <v>-0.0134311940651296</v>
       </c>
       <c r="R8" s="18" t="n">
-        <v>1.00838466148491</v>
+        <v>1.00838465904401</v>
       </c>
       <c r="S8" s="19" t="n">
-        <v>0.890046364842785</v>
+        <v>0.89004939139548</v>
       </c>
     </row>
     <row r="9">
@@ -1908,46 +1908,46 @@
         <v>38.249</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>0.932898520842405</v>
+        <v>0.932898516526591</v>
       </c>
       <c r="G9" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H9" s="8" t="n">
-        <v>36.5210082152518</v>
+        <v>36.5210083055285</v>
       </c>
       <c r="I9" s="9" t="n">
-        <v>40.4419090356775</v>
+        <v>40.4418269203512</v>
       </c>
       <c r="J9" s="10" t="n">
-        <v>39.3984849360626</v>
+        <v>39.3984929354761</v>
       </c>
       <c r="K9" s="11" t="n">
-        <v>41.0001722003603</v>
+        <v>41.000172390037</v>
       </c>
       <c r="L9" s="12" t="n">
-        <v>36.5210082152518</v>
+        <v>36.5210083055285</v>
       </c>
       <c r="M9" s="13" t="n">
-        <v>36.7099858907332</v>
+        <v>36.7099858646417</v>
       </c>
       <c r="N9" s="14" t="n">
-        <v>36.7099858907332</v>
+        <v>36.7099858646417</v>
       </c>
       <c r="O9" s="15" t="n">
-        <v>0.0324715697235334</v>
+        <v>0.0324715652583737</v>
       </c>
       <c r="P9" s="16" t="n">
-        <v>-0.0831042948615429</v>
+        <v>-0.083104295775888</v>
       </c>
       <c r="Q9" s="17" t="n">
-        <v>0.0330045241222778</v>
+        <v>0.0330045195097477</v>
       </c>
       <c r="R9" s="18" t="n">
-        <v>1.00517449229133</v>
+        <v>1.0051744890922</v>
       </c>
       <c r="S9" s="19" t="n">
-        <v>0.907721390163554</v>
+        <v>0.9077232326062</v>
       </c>
     </row>
     <row r="10">
@@ -1967,46 +1967,46 @@
         <v>35.512</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>1.04099002413683</v>
+        <v>1.04099003411313</v>
       </c>
       <c r="G10" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H10" s="8" t="n">
-        <v>38.7339151070479</v>
+        <v>38.7339145867298</v>
       </c>
       <c r="I10" s="9" t="n">
-        <v>40.9730324447496</v>
+        <v>40.9730093510172</v>
       </c>
       <c r="J10" s="10" t="n">
-        <v>39.9408859018992</v>
+        <v>39.9408964149234</v>
       </c>
       <c r="K10" s="11" t="n">
-        <v>34.1136794557142</v>
+        <v>34.1136791287867</v>
       </c>
       <c r="L10" s="12" t="n">
-        <v>38.7339151070479</v>
+        <v>38.7339145867298</v>
       </c>
       <c r="M10" s="13" t="n">
-        <v>38.8798290343308</v>
+        <v>38.8798286246814</v>
       </c>
       <c r="N10" s="14" t="n">
-        <v>38.8798290343308</v>
+        <v>38.8798286246814</v>
       </c>
       <c r="O10" s="15" t="n">
-        <v>0.0574267691527083</v>
+        <v>0.0574267593271596</v>
       </c>
       <c r="P10" s="16" t="n">
-        <v>0.021324362176546</v>
+        <v>0.021324354014949</v>
       </c>
       <c r="Q10" s="17" t="n">
-        <v>0.0591077084599305</v>
+        <v>0.0591076980536163</v>
       </c>
       <c r="R10" s="18" t="n">
-        <v>1.00376708439825</v>
+        <v>1.00376708730601</v>
       </c>
       <c r="S10" s="19" t="n">
-        <v>0.948912655824502</v>
+        <v>0.948913180664779</v>
       </c>
     </row>
     <row r="11">
@@ -2026,46 +2026,46 @@
         <v>42.694</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>1.02801610663392</v>
+        <v>1.02801612367008</v>
       </c>
       <c r="G11" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H11" s="8" t="n">
-        <v>41.5289152260651</v>
+        <v>41.5289151911957</v>
       </c>
       <c r="I11" s="9" t="n">
-        <v>41.5170082812142</v>
+        <v>41.5170509652241</v>
       </c>
       <c r="J11" s="10" t="n">
-        <v>40.5739880685124</v>
+        <v>40.5740012591266</v>
       </c>
       <c r="K11" s="11" t="n">
-        <v>41.5304777079757</v>
+        <v>41.5304770197376</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>41.5304777079757</v>
+        <v>41.5304770197376</v>
       </c>
       <c r="M11" s="13" t="n">
-        <v>41.3282008842687</v>
+        <v>41.3282008052307</v>
       </c>
       <c r="N11" s="14" t="n">
-        <v>41.3282008842687</v>
+        <v>41.3282008052307</v>
       </c>
       <c r="O11" s="15" t="n">
-        <v>0.0610695147547215</v>
+        <v>0.061069523378569</v>
       </c>
       <c r="P11" s="16" t="n">
-        <v>0.147339336289464</v>
+        <v>0.147339334381521</v>
       </c>
       <c r="Q11" s="17" t="n">
-        <v>0.062972803912692</v>
+        <v>0.0629728130796074</v>
       </c>
       <c r="R11" s="18" t="n">
-        <v>0.995166877326225</v>
+        <v>0.995166876258603</v>
       </c>
       <c r="S11" s="19" t="n">
-        <v>0.995452287995643</v>
+        <v>0.995451262659488</v>
       </c>
     </row>
     <row r="12">
@@ -2085,46 +2085,46 @@
         <v>43.215</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>0.993038892403791</v>
+        <v>0.993038856335007</v>
       </c>
       <c r="G12" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H12" s="8" t="n">
-        <v>42.9271225952887</v>
+        <v>42.9271232720313</v>
       </c>
       <c r="I12" s="9" t="n">
-        <v>42.0688284429329</v>
+        <v>42.0689449141668</v>
       </c>
       <c r="J12" s="10" t="n">
-        <v>41.273237350342</v>
+        <v>41.2732532808787</v>
       </c>
       <c r="K12" s="11" t="n">
-        <v>43.5179330140756</v>
+        <v>43.5179345947176</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>43.5179330140756</v>
+        <v>43.5179345947176</v>
       </c>
       <c r="M12" s="13" t="n">
-        <v>42.5872212512656</v>
+        <v>42.5872218020612</v>
       </c>
       <c r="N12" s="14" t="n">
-        <v>42.5872212512656</v>
+        <v>42.5872218020612</v>
       </c>
       <c r="O12" s="15" t="n">
-        <v>0.0300091405754306</v>
+        <v>0.0300091554212319</v>
       </c>
       <c r="P12" s="16" t="n">
-        <v>0.198387609118068</v>
+        <v>0.198387620117997</v>
       </c>
       <c r="Q12" s="17" t="n">
-        <v>0.0304639529439596</v>
+        <v>0.0304639682420229</v>
       </c>
       <c r="R12" s="18" t="n">
-        <v>0.992081897796234</v>
+        <v>0.992081894987088</v>
       </c>
       <c r="S12" s="19" t="n">
-        <v>1.01232249215202</v>
+        <v>1.01231970254904</v>
       </c>
     </row>
     <row r="13">
@@ -2144,46 +2144,46 @@
         <v>38.854</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>0.929909929362942</v>
+        <v>0.929909935369013</v>
       </c>
       <c r="G13" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H13" s="8" t="n">
-        <v>42.2042601099554</v>
+        <v>42.2042603999785</v>
       </c>
       <c r="I13" s="9" t="n">
-        <v>42.623493246159</v>
+        <v>42.6236927403241</v>
       </c>
       <c r="J13" s="10" t="n">
-        <v>42.018862110025</v>
+        <v>42.018880671776</v>
       </c>
       <c r="K13" s="11" t="n">
-        <v>41.7825412689355</v>
+        <v>41.7825409990718</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>41.7825412689355</v>
+        <v>41.7825409990718</v>
       </c>
       <c r="M13" s="13" t="n">
-        <v>42.2131791978093</v>
+        <v>42.2131793103886</v>
       </c>
       <c r="N13" s="14" t="n">
-        <v>42.2131791978093</v>
+        <v>42.2131793103886</v>
       </c>
       <c r="O13" s="15" t="n">
-        <v>-0.00882176209649332</v>
+        <v>-0.00882177236292357</v>
       </c>
       <c r="P13" s="16" t="n">
-        <v>0.149909981536257</v>
+        <v>0.149909985420274</v>
       </c>
       <c r="Q13" s="17" t="n">
-        <v>-0.00878296452472094</v>
+        <v>-0.00878297470098144</v>
       </c>
       <c r="R13" s="18" t="n">
-        <v>1.00021133145874</v>
+        <v>1.00021132725288</v>
       </c>
       <c r="S13" s="19" t="n">
-        <v>0.99037352368141</v>
+        <v>0.99036889101945</v>
       </c>
     </row>
     <row r="14">
@@ -2203,46 +2203,46 @@
         <v>44.001</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>1.05341907398204</v>
+        <v>1.05341908887673</v>
       </c>
       <c r="G14" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H14" s="8" t="n">
-        <v>41.8424865378819</v>
+        <v>41.8424853786857</v>
       </c>
       <c r="I14" s="9" t="n">
-        <v>43.1769086975029</v>
+        <v>43.1772016047251</v>
       </c>
       <c r="J14" s="10" t="n">
-        <v>42.8023141885171</v>
+        <v>42.8023350299837</v>
       </c>
       <c r="K14" s="11" t="n">
-        <v>41.7697012392906</v>
+        <v>41.7697006486931</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>41.7697012392906</v>
+        <v>41.7697006486931</v>
       </c>
       <c r="M14" s="13" t="n">
-        <v>42.1258366154231</v>
+        <v>42.1258359132767</v>
       </c>
       <c r="N14" s="14" t="n">
-        <v>42.1258366154231</v>
+        <v>42.1258359132767</v>
       </c>
       <c r="O14" s="15" t="n">
-        <v>-0.00207122676898359</v>
+        <v>-0.0020712461037379</v>
       </c>
       <c r="P14" s="16" t="n">
-        <v>0.0834882164277531</v>
+        <v>0.0834882097843064</v>
       </c>
       <c r="Q14" s="17" t="n">
-        <v>-0.00206908325897315</v>
+        <v>-0.00206910255372206</v>
       </c>
       <c r="R14" s="18" t="n">
-        <v>1.00677182693922</v>
+        <v>1.00677183804993</v>
       </c>
       <c r="S14" s="19" t="n">
-        <v>0.975656615682154</v>
+        <v>0.975649980721925</v>
       </c>
     </row>
     <row r="15">
@@ -2262,46 +2262,46 @@
         <v>44.777</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>1.03695102950652</v>
+        <v>1.03695106210594</v>
       </c>
       <c r="G15" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H15" s="8" t="n">
-        <v>43.1972721268951</v>
+        <v>43.1972721962392</v>
       </c>
       <c r="I15" s="9" t="n">
-        <v>43.7244552085891</v>
+        <v>43.7248529485607</v>
       </c>
       <c r="J15" s="10" t="n">
-        <v>43.6138638225686</v>
+        <v>43.6138862553036</v>
       </c>
       <c r="K15" s="11" t="n">
-        <v>43.1814027141756</v>
+        <v>43.1814013566489</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>43.1814027141756</v>
+        <v>43.1814013566489</v>
       </c>
       <c r="M15" s="13" t="n">
-        <v>43.2152189256961</v>
+        <v>43.2152188985723</v>
       </c>
       <c r="N15" s="14" t="n">
-        <v>43.2152189256961</v>
+        <v>43.2152188985723</v>
       </c>
       <c r="O15" s="15" t="n">
-        <v>0.0255314743751081</v>
+        <v>0.0255314904152959</v>
       </c>
       <c r="P15" s="16" t="n">
-        <v>0.0456593319102265</v>
+        <v>0.0456593332536945</v>
       </c>
       <c r="Q15" s="17" t="n">
-        <v>0.0258601940708794</v>
+        <v>0.0258602105258696</v>
       </c>
       <c r="R15" s="18" t="n">
-        <v>1.00041546139183</v>
+        <v>1.00041545915797</v>
       </c>
       <c r="S15" s="19" t="n">
-        <v>0.988353513372237</v>
+        <v>0.98834452226545</v>
       </c>
     </row>
     <row r="16">
@@ -2321,46 +2321,46 @@
         <v>43.288</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>0.967797416578932</v>
+        <v>0.967797347401385</v>
       </c>
       <c r="G16" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H16" s="8" t="n">
-        <v>44.4963152968718</v>
+        <v>44.4963166735313</v>
       </c>
       <c r="I16" s="9" t="n">
-        <v>44.2606336863807</v>
+        <v>44.2611485249243</v>
       </c>
       <c r="J16" s="10" t="n">
-        <v>44.4386181841835</v>
+        <v>44.4386410756311</v>
       </c>
       <c r="K16" s="11" t="n">
-        <v>44.7283690351425</v>
+        <v>44.7283722322982</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>44.7283690351425</v>
+        <v>44.7283722322982</v>
       </c>
       <c r="M16" s="13" t="n">
-        <v>44.3858345101726</v>
+        <v>44.385835621528</v>
       </c>
       <c r="N16" s="14" t="n">
-        <v>44.3858345101726</v>
+        <v>44.385835621528</v>
       </c>
       <c r="O16" s="15" t="n">
-        <v>0.0267276528123919</v>
+        <v>0.0267276784785522</v>
       </c>
       <c r="P16" s="16" t="n">
-        <v>0.042233637369649</v>
+        <v>0.0422336499860578</v>
       </c>
       <c r="Q16" s="17" t="n">
-        <v>0.0270880401297802</v>
+        <v>0.0270880664911868</v>
       </c>
       <c r="R16" s="18" t="n">
-        <v>0.99751708010063</v>
+        <v>0.997517074215066</v>
       </c>
       <c r="S16" s="19" t="n">
-        <v>1.00282871738075</v>
+        <v>1.00281707774785</v>
       </c>
     </row>
     <row r="17">
@@ -2380,46 +2380,46 @@
         <v>42.023</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>0.935815953779607</v>
+        <v>0.935815966103503</v>
       </c>
       <c r="G17" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H17" s="8" t="n">
-        <v>45.0342620110024</v>
+        <v>45.0342623454701</v>
       </c>
       <c r="I17" s="9" t="n">
-        <v>44.779605630032</v>
+        <v>44.7802504296642</v>
       </c>
       <c r="J17" s="10" t="n">
-        <v>45.2595221398241</v>
+        <v>45.2595437943682</v>
       </c>
       <c r="K17" s="11" t="n">
-        <v>44.9051972562297</v>
+        <v>44.9051966648667</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>44.9051972562297</v>
+        <v>44.9051966648667</v>
       </c>
       <c r="M17" s="13" t="n">
-        <v>44.976399722691</v>
+        <v>44.9763998276809</v>
       </c>
       <c r="N17" s="14" t="n">
-        <v>44.976399722691</v>
+        <v>44.9763998276809</v>
       </c>
       <c r="O17" s="15" t="n">
-        <v>0.0132175256215397</v>
+        <v>0.0132175029173573</v>
       </c>
       <c r="P17" s="16" t="n">
-        <v>0.0654587163864953</v>
+        <v>0.0654587160321358</v>
       </c>
       <c r="Q17" s="17" t="n">
-        <v>0.013305263245261</v>
+        <v>0.0133052402389937</v>
       </c>
       <c r="R17" s="18" t="n">
-        <v>0.998715149627693</v>
+        <v>0.998715144541609</v>
       </c>
       <c r="S17" s="19" t="n">
-        <v>1.00439472590011</v>
+        <v>1.00438026576749</v>
       </c>
     </row>
     <row r="18">
@@ -2439,46 +2439,46 @@
         <v>48.478</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>1.06857795200623</v>
+        <v>1.06857798956264</v>
       </c>
       <c r="G18" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H18" s="8" t="n">
-        <v>45.4851778270968</v>
+        <v>45.48517710477</v>
       </c>
       <c r="I18" s="9" t="n">
-        <v>45.2758248732899</v>
+        <v>45.2766127734461</v>
       </c>
       <c r="J18" s="10" t="n">
-        <v>46.0609693102072</v>
+        <v>46.0609873707004</v>
       </c>
       <c r="K18" s="11" t="n">
-        <v>45.3668353431621</v>
+        <v>45.3668337486922</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>45.3668353431621</v>
+        <v>45.3668337486922</v>
       </c>
       <c r="M18" s="13" t="n">
-        <v>45.2578370786992</v>
+        <v>45.2578348869745</v>
       </c>
       <c r="N18" s="14" t="n">
-        <v>45.2578370786992</v>
+        <v>45.2578348869745</v>
       </c>
       <c r="O18" s="15" t="n">
-        <v>0.00623794866763585</v>
+        <v>0.00623789790578431</v>
       </c>
       <c r="P18" s="16" t="n">
-        <v>0.0743486827779556</v>
+        <v>0.0743486486569795</v>
       </c>
       <c r="Q18" s="17" t="n">
-        <v>0.00625744518777416</v>
+        <v>0.00625739410828441</v>
       </c>
       <c r="R18" s="18" t="n">
-        <v>0.99500187183478</v>
+        <v>0.995001839450425</v>
       </c>
       <c r="S18" s="19" t="n">
-        <v>0.99960270641913</v>
+        <v>0.999585263001773</v>
       </c>
     </row>
     <row r="19">
@@ -2498,46 +2498,46 @@
         <v>51.223</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>1.03586264242117</v>
+        <v>1.03586269363124</v>
       </c>
       <c r="G19" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H19" s="8" t="n">
-        <v>45.3924803722427</v>
+        <v>45.392475385647</v>
       </c>
       <c r="I19" s="9" t="n">
-        <v>45.7438237446681</v>
+        <v>45.7447677583323</v>
       </c>
       <c r="J19" s="10" t="n">
-        <v>46.8255816916318</v>
+        <v>46.8255930281656</v>
       </c>
       <c r="K19" s="11" t="n">
-        <v>49.449606446154</v>
+        <v>49.4496040015078</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>45.3924803722427</v>
+        <v>45.392475385647</v>
       </c>
       <c r="M19" s="13" t="n">
-        <v>45.2793955207148</v>
+        <v>45.2793902516881</v>
       </c>
       <c r="N19" s="14" t="n">
-        <v>45.2793955207148</v>
+        <v>45.2793902516881</v>
       </c>
       <c r="O19" s="15" t="n">
-        <v>0.00047623373951512</v>
+        <v>0.000476165800041647</v>
       </c>
       <c r="P19" s="16" t="n">
-        <v>0.0477650384825736</v>
+        <v>0.047764917214939</v>
       </c>
       <c r="Q19" s="17" t="n">
-        <v>0.000476347156806112</v>
+        <v>0.000476279184972173</v>
       </c>
       <c r="R19" s="18" t="n">
-        <v>0.997508731609276</v>
+        <v>0.997508725113619</v>
       </c>
       <c r="S19" s="19" t="n">
-        <v>0.989847192780699</v>
+        <v>0.989826650577771</v>
       </c>
     </row>
     <row r="20">
@@ -2557,46 +2557,46 @@
         <v>42.247</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>0.946262559880257</v>
+        <v>0.946262424096015</v>
       </c>
       <c r="G20" s="7" t="n">
-        <v>0.761085381439816</v>
+        <v>0.76109489753263</v>
       </c>
       <c r="H20" s="8" t="n">
-        <v>45.9839503491358</v>
+        <v>45.9839434259682</v>
       </c>
       <c r="I20" s="9" t="n">
-        <v>46.1781914542237</v>
+        <v>46.179303974495</v>
       </c>
       <c r="J20" s="10" t="n">
-        <v>47.5325106105617</v>
+        <v>47.5325112221916</v>
       </c>
       <c r="K20" s="11" t="n">
-        <v>44.64617093732</v>
+        <v>44.6461773438372</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>44.9657859952117</v>
+        <v>44.9657764867661</v>
       </c>
       <c r="M20" s="13" t="n">
-        <v>46.1816588752487</v>
+        <v>46.1816529005655</v>
       </c>
       <c r="N20" s="14" t="n">
-        <v>46.1816588752487</v>
+        <v>46.1816529005655</v>
       </c>
       <c r="O20" s="15" t="n">
-        <v>0.0197306412241781</v>
+        <v>0.0197306282176533</v>
       </c>
       <c r="P20" s="16" t="n">
-        <v>0.040459402980574</v>
+        <v>0.0404592423211356</v>
       </c>
       <c r="Q20" s="17" t="n">
-        <v>0.0199265768493122</v>
+        <v>0.0199265635836119</v>
       </c>
       <c r="R20" s="18" t="n">
-        <v>1.00429951156027</v>
+        <v>1.00429953283401</v>
       </c>
       <c r="S20" s="19" t="n">
-        <v>1.00007508784809</v>
+        <v>1.00005086534158</v>
       </c>
     </row>
     <row r="21">
@@ -2616,46 +2616,46 @@
         <v>46.849</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>0.948310736481559</v>
+        <v>0.948310734470745</v>
       </c>
       <c r="G21" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H21" s="8" t="n">
-        <v>49.4364508696474</v>
+        <v>49.4364448959797</v>
       </c>
       <c r="I21" s="9" t="n">
-        <v>46.5732976224062</v>
+        <v>46.5745898293733</v>
       </c>
       <c r="J21" s="10" t="n">
-        <v>48.1537418868636</v>
+        <v>48.1537268199937</v>
       </c>
       <c r="K21" s="11" t="n">
-        <v>49.4025831383288</v>
+        <v>49.4025832430828</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>49.4025831383288</v>
+        <v>49.4025832430828</v>
       </c>
       <c r="M21" s="13" t="n">
-        <v>49.3957305710901</v>
+        <v>49.3957261842572</v>
       </c>
       <c r="N21" s="14" t="n">
-        <v>49.3957305710901</v>
+        <v>49.3957261842572</v>
       </c>
       <c r="O21" s="15" t="n">
-        <v>0.0672812695500669</v>
+        <v>0.067281310113618</v>
       </c>
       <c r="P21" s="16" t="n">
-        <v>0.0982588841180529</v>
+        <v>0.0982587840180218</v>
       </c>
       <c r="Q21" s="17" t="n">
-        <v>0.0695962807339521</v>
+        <v>0.0695963241205764</v>
       </c>
       <c r="R21" s="18" t="n">
-        <v>0.999176310235849</v>
+        <v>0.9991763422348</v>
       </c>
       <c r="S21" s="19" t="n">
-        <v>1.06060195633058</v>
+        <v>1.06057243585438</v>
       </c>
     </row>
     <row r="22">
@@ -2675,46 +2675,46 @@
         <v>58.259</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>1.08264016326621</v>
+        <v>1.08264032921524</v>
       </c>
       <c r="G22" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H22" s="8" t="n">
-        <v>53.1229417225135</v>
+        <v>53.1229365456968</v>
       </c>
       <c r="I22" s="9" t="n">
-        <v>46.922754116253</v>
+        <v>46.9242352757265</v>
       </c>
       <c r="J22" s="10" t="n">
-        <v>48.6484277173277</v>
+        <v>48.6483910151101</v>
       </c>
       <c r="K22" s="11" t="n">
-        <v>53.8119700124913</v>
+        <v>53.8119617640971</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>53.8119700124913</v>
+        <v>53.8119617640971</v>
       </c>
       <c r="M22" s="13" t="n">
-        <v>52.4684563679512</v>
+        <v>52.4684518396372</v>
       </c>
       <c r="N22" s="14" t="n">
-        <v>52.4684563679512</v>
+        <v>52.4684518396372</v>
       </c>
       <c r="O22" s="15" t="n">
-        <v>0.0603481631670784</v>
+        <v>0.0603481656715839</v>
       </c>
       <c r="P22" s="16" t="n">
-        <v>0.159323108541699</v>
+        <v>0.159323064628926</v>
       </c>
       <c r="Q22" s="17" t="n">
-        <v>0.062206303284428</v>
+        <v>0.0622063059447295</v>
       </c>
       <c r="R22" s="18" t="n">
-        <v>0.987679798344359</v>
+        <v>0.987679809351341</v>
       </c>
       <c r="S22" s="19" t="n">
-        <v>1.11818791023985</v>
+        <v>1.11815251823142</v>
       </c>
     </row>
     <row r="23">
@@ -2734,46 +2734,46 @@
         <v>53.977</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>1.02137663877168</v>
+        <v>1.02137667203763</v>
       </c>
       <c r="G23" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H23" s="8" t="n">
-        <v>52.8318666282636</v>
+        <v>52.8318670522314</v>
       </c>
       <c r="I23" s="9" t="n">
-        <v>47.2219411062491</v>
+        <v>47.2236177621974</v>
       </c>
       <c r="J23" s="10" t="n">
-        <v>48.9819645050012</v>
+        <v>48.9818992831943</v>
       </c>
       <c r="K23" s="11" t="n">
-        <v>52.8473023084936</v>
+        <v>52.8473005872718</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>52.8473023084936</v>
+        <v>52.8473005872718</v>
       </c>
       <c r="M23" s="13" t="n">
-        <v>52.4741351363153</v>
+        <v>52.4741357726097</v>
       </c>
       <c r="N23" s="14" t="n">
-        <v>52.4741351363153</v>
+        <v>52.4741357726097</v>
       </c>
       <c r="O23" s="15" t="n">
-        <v>0.000108226188970767</v>
+        <v>0.000108324620297507</v>
       </c>
       <c r="P23" s="16" t="n">
-        <v>0.158896547377913</v>
+        <v>0.158896696287853</v>
       </c>
       <c r="Q23" s="17" t="n">
-        <v>0.000108232045636036</v>
+        <v>0.000108330487621044</v>
       </c>
       <c r="R23" s="18" t="n">
-        <v>0.993228868961505</v>
+        <v>0.993228873034754</v>
       </c>
       <c r="S23" s="19" t="n">
-        <v>1.11122359452037</v>
+        <v>1.1111841544384</v>
       </c>
     </row>
     <row r="24">
@@ -2793,46 +2793,46 @@
         <v>47.06</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>0.933916091125201</v>
+        <v>0.933915827278227</v>
       </c>
       <c r="G24" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H24" s="8" t="n">
-        <v>50.950466193853</v>
+        <v>50.9504772482694</v>
       </c>
       <c r="I24" s="9" t="n">
-        <v>47.4705445228147</v>
+        <v>47.4724195664841</v>
       </c>
       <c r="J24" s="10" t="n">
-        <v>49.1455663644075</v>
+        <v>49.1454649536449</v>
       </c>
       <c r="K24" s="11" t="n">
-        <v>50.3899659157828</v>
+        <v>50.3899801517981</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>50.3899659157828</v>
+        <v>50.3899801517981</v>
       </c>
       <c r="M24" s="13" t="n">
-        <v>51.0397000319876</v>
+        <v>51.0397079590957</v>
       </c>
       <c r="N24" s="14" t="n">
-        <v>51.0397000319876</v>
+        <v>51.0397079590957</v>
       </c>
       <c r="O24" s="15" t="n">
-        <v>-0.0277166222255422</v>
+        <v>-0.0277164790388295</v>
       </c>
       <c r="P24" s="16" t="n">
-        <v>0.105194167447775</v>
+        <v>0.105194482081232</v>
       </c>
       <c r="Q24" s="17" t="n">
-        <v>-0.0273360409009386</v>
+        <v>-0.0273359016283737</v>
       </c>
       <c r="R24" s="18" t="n">
-        <v>1.00175138413445</v>
+        <v>1.00175132237509</v>
       </c>
       <c r="S24" s="19" t="n">
-        <v>1.07518674043138</v>
+        <v>1.07514444018628</v>
       </c>
     </row>
     <row r="25">
@@ -2852,46 +2852,46 @@
         <v>49.032</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>0.970324173443376</v>
+        <v>0.970324078245425</v>
       </c>
       <c r="G25" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H25" s="8" t="n">
-        <v>50.03521377785</v>
+        <v>50.0352155344123</v>
       </c>
       <c r="I25" s="9" t="n">
-        <v>47.6717661471212</v>
+        <v>47.6738377680504</v>
       </c>
       <c r="J25" s="10" t="n">
-        <v>49.1497740990871</v>
+        <v>49.1496283623808</v>
       </c>
       <c r="K25" s="11" t="n">
-        <v>50.5315659878913</v>
+        <v>50.5315709455149</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>50.5315659878913</v>
+        <v>50.5315709455149</v>
       </c>
       <c r="M25" s="13" t="n">
-        <v>50.2958313980974</v>
+        <v>50.2958322129771</v>
       </c>
       <c r="N25" s="14" t="n">
-        <v>50.2958313980974</v>
+        <v>50.2958322129771</v>
       </c>
       <c r="O25" s="15" t="n">
-        <v>-0.0146815630209618</v>
+        <v>-0.014681702131808</v>
       </c>
       <c r="P25" s="16" t="n">
-        <v>0.0182222393838645</v>
+        <v>0.0182223463091173</v>
       </c>
       <c r="Q25" s="17" t="n">
-        <v>-0.0145743143753593</v>
+        <v>-0.0145744514587507</v>
       </c>
       <c r="R25" s="18" t="n">
-        <v>1.00520868405608</v>
+        <v>1.00520866505283</v>
       </c>
       <c r="S25" s="19" t="n">
-        <v>1.0550444311813</v>
+        <v>1.05499860232951</v>
       </c>
     </row>
     <row r="26">
@@ -2911,46 +2911,46 @@
         <v>54.016</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>1.08618042782669</v>
+        <v>1.08618088413292</v>
       </c>
       <c r="G26" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H26" s="8" t="n">
-        <v>50.1470486008719</v>
+        <v>50.1470298367391</v>
       </c>
       <c r="I26" s="9" t="n">
-        <v>47.8306323987107</v>
+        <v>47.8328929217258</v>
       </c>
       <c r="J26" s="10" t="n">
-        <v>49.0113505103376</v>
+        <v>49.0111524213117</v>
       </c>
       <c r="K26" s="11" t="n">
-        <v>49.7302277008243</v>
+        <v>49.7302068090805</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>49.7302277008243</v>
+        <v>49.7302068090805</v>
       </c>
       <c r="M26" s="13" t="n">
-        <v>50.2989855011246</v>
+        <v>50.2989735316516</v>
       </c>
       <c r="N26" s="14" t="n">
-        <v>50.2989855011246</v>
+        <v>50.2989735316516</v>
       </c>
       <c r="O26" s="15" t="n">
-        <v>0.00006270905650003</v>
+        <v>0.0000624548882467139</v>
       </c>
       <c r="P26" s="16" t="n">
-        <v>-0.0413480978287701</v>
+        <v>-0.0413482432189228</v>
       </c>
       <c r="Q26" s="17" t="n">
-        <v>0.000062711022754014</v>
+        <v>0.0000624568385938495</v>
       </c>
       <c r="R26" s="18" t="n">
-        <v>1.00302982736755</v>
+        <v>1.00302996399602</v>
       </c>
       <c r="S26" s="19" t="n">
-        <v>1.05160611471406</v>
+        <v>1.05155616688209</v>
       </c>
     </row>
     <row r="27">
@@ -2970,46 +2970,46 @@
         <v>51.252</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>1.00093897858726</v>
+        <v>1.00093919463338</v>
       </c>
       <c r="G27" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H27" s="8" t="n">
-        <v>51.5307076960085</v>
+        <v>51.5307121057696</v>
       </c>
       <c r="I27" s="9" t="n">
-        <v>47.953957072026</v>
+        <v>47.9563916655758</v>
       </c>
       <c r="J27" s="10" t="n">
-        <v>48.7539673589005</v>
+        <v>48.7537097552628</v>
       </c>
       <c r="K27" s="11" t="n">
-        <v>51.2039206149588</v>
+        <v>51.2039095629304</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>51.2039206149588</v>
+        <v>51.2039095629304</v>
       </c>
       <c r="M27" s="13" t="n">
-        <v>51.1579948837623</v>
+        <v>51.1579985750106</v>
       </c>
       <c r="N27" s="14" t="n">
-        <v>51.1579948837623</v>
+        <v>51.1579985750106</v>
       </c>
       <c r="O27" s="15" t="n">
-        <v>0.0169338749579167</v>
+        <v>0.0169341850783232</v>
       </c>
       <c r="P27" s="16" t="n">
-        <v>-0.0250816949938101</v>
+        <v>-0.0250816364713932</v>
       </c>
       <c r="Q27" s="17" t="n">
-        <v>0.0170780657716929</v>
+        <v>0.017078381188405</v>
       </c>
       <c r="R27" s="18" t="n">
-        <v>0.992767170704409</v>
+        <v>0.992767157379972</v>
       </c>
       <c r="S27" s="19" t="n">
-        <v>1.0668148784244</v>
+        <v>1.0667607965954</v>
       </c>
     </row>
     <row r="28">
@@ -3029,46 +3029,46 @@
         <v>48.855</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>0.93067937666643</v>
+        <v>0.930678352610119</v>
       </c>
       <c r="G28" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H28" s="8" t="n">
-        <v>51.2156899742843</v>
+        <v>51.2157248046306</v>
       </c>
       <c r="I28" s="9" t="n">
-        <v>48.0497412085734</v>
+        <v>48.0523264588456</v>
       </c>
       <c r="J28" s="10" t="n">
-        <v>48.4048907914699</v>
+        <v>48.4045682609985</v>
       </c>
       <c r="K28" s="11" t="n">
-        <v>52.4939106043073</v>
+        <v>52.4939683651011</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>52.4939106043073</v>
+        <v>52.4939683651011</v>
       </c>
       <c r="M28" s="13" t="n">
-        <v>50.7206691370872</v>
+        <v>50.7206948184523</v>
       </c>
       <c r="N28" s="14" t="n">
-        <v>50.7206691370872</v>
+        <v>50.7206948184523</v>
       </c>
       <c r="O28" s="15" t="n">
-        <v>-0.00858528008862692</v>
+        <v>-0.00858484591325969</v>
       </c>
       <c r="P28" s="16" t="n">
-        <v>-0.00625064204335923</v>
+        <v>-0.00625029322070347</v>
       </c>
       <c r="Q28" s="17" t="n">
-        <v>-0.00854853181147353</v>
+        <v>-0.00854810134757478</v>
       </c>
       <c r="R28" s="18" t="n">
-        <v>0.990334586189396</v>
+        <v>0.990334414126391</v>
       </c>
       <c r="S28" s="19" t="n">
-        <v>1.05558672869683</v>
+        <v>1.0555304718054</v>
       </c>
     </row>
     <row r="29">
@@ -3088,46 +3088,46 @@
         <v>46.384</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>0.99342624587439</v>
+        <v>0.993426282982958</v>
       </c>
       <c r="G29" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H29" s="8" t="n">
-        <v>47.5756137689542</v>
+        <v>47.575614057857</v>
       </c>
       <c r="I29" s="9" t="n">
-        <v>48.1280170770737</v>
+        <v>48.1307194594661</v>
       </c>
       <c r="J29" s="10" t="n">
-        <v>48.0036367210199</v>
+        <v>48.0032468343212</v>
       </c>
       <c r="K29" s="11" t="n">
-        <v>46.6909347247756</v>
+        <v>46.6909329806766</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>46.6909347247756</v>
+        <v>46.6909329806766</v>
       </c>
       <c r="M29" s="13" t="n">
-        <v>47.542414428515</v>
+        <v>47.5424118549962</v>
       </c>
       <c r="N29" s="14" t="n">
-        <v>47.542414428515</v>
+        <v>47.5424118549962</v>
       </c>
       <c r="O29" s="15" t="n">
-        <v>-0.0647112548597042</v>
+        <v>-0.0647118153199664</v>
       </c>
       <c r="P29" s="16" t="n">
-        <v>-0.054744436925375</v>
+        <v>-0.0547445034077881</v>
       </c>
       <c r="Q29" s="17" t="n">
-        <v>-0.06266192387924</v>
+        <v>-0.0626624492198367</v>
       </c>
       <c r="R29" s="18" t="n">
-        <v>0.999302177359172</v>
+        <v>0.99930211719768</v>
       </c>
       <c r="S29" s="19" t="n">
-        <v>0.987832396094338</v>
+        <v>0.987776879068569</v>
       </c>
     </row>
     <row r="30">
@@ -3147,46 +3147,46 @@
         <v>48.182</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>1.08778013001314</v>
+        <v>1.08778171565991</v>
       </c>
       <c r="G30" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H30" s="8" t="n">
-        <v>44.2266169425907</v>
+        <v>44.226548446225</v>
       </c>
       <c r="I30" s="9" t="n">
-        <v>48.2015945521201</v>
+        <v>48.2043688515596</v>
       </c>
       <c r="J30" s="10" t="n">
-        <v>47.6101661595891</v>
+        <v>47.609711371554</v>
       </c>
       <c r="K30" s="11" t="n">
-        <v>44.2938776602014</v>
+        <v>44.2938130935305</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>44.2938776602014</v>
+        <v>44.2938130935305</v>
       </c>
       <c r="M30" s="13" t="n">
-        <v>44.7579570273399</v>
+        <v>44.7579159593713</v>
       </c>
       <c r="N30" s="14" t="n">
-        <v>44.7579570273399</v>
+        <v>44.7579159593713</v>
       </c>
       <c r="O30" s="15" t="n">
-        <v>-0.0603530083669239</v>
+        <v>-0.0603538717931547</v>
       </c>
       <c r="P30" s="16" t="n">
-        <v>-0.110161833654893</v>
+        <v>-0.110162438380447</v>
       </c>
       <c r="Q30" s="17" t="n">
-        <v>-0.0585678585037329</v>
+        <v>-0.0585686713605874</v>
       </c>
       <c r="R30" s="18" t="n">
-        <v>1.01201403411522</v>
+        <v>1.01201467290156</v>
       </c>
       <c r="S30" s="19" t="n">
-        <v>0.928557601532111</v>
+        <v>0.928503308428302</v>
       </c>
     </row>
     <row r="31">
@@ -3206,46 +3206,46 @@
         <v>42.801</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>0.978238405145149</v>
+        <v>0.978239151782852</v>
       </c>
       <c r="G31" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H31" s="8" t="n">
-        <v>43.7460054592149</v>
+        <v>43.7460444657787</v>
       </c>
       <c r="I31" s="9" t="n">
-        <v>48.2823853318353</v>
+        <v>48.2851729526992</v>
       </c>
       <c r="J31" s="10" t="n">
-        <v>47.2778766092347</v>
+        <v>47.2773661997517</v>
       </c>
       <c r="K31" s="11" t="n">
-        <v>43.7531380641811</v>
+        <v>43.7531046697474</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>43.7531380641811</v>
+        <v>43.7531046697474</v>
       </c>
       <c r="M31" s="13" t="n">
-        <v>44.0588238237268</v>
+        <v>44.0588516357926</v>
       </c>
       <c r="N31" s="14" t="n">
-        <v>44.0588238237268</v>
+        <v>44.0588516357926</v>
       </c>
       <c r="O31" s="15" t="n">
-        <v>-0.0157435934401829</v>
+        <v>-0.0157420446346585</v>
       </c>
       <c r="P31" s="16" t="n">
-        <v>-0.138769533015626</v>
+        <v>-0.138769051506361</v>
       </c>
       <c r="Q31" s="17" t="n">
-        <v>-0.0156203108909997</v>
+        <v>-0.0156187862771184</v>
       </c>
       <c r="R31" s="18" t="n">
-        <v>1.00715078693993</v>
+        <v>1.00715052466649</v>
       </c>
       <c r="S31" s="19" t="n">
-        <v>0.912523760392515</v>
+        <v>0.912471654165001</v>
       </c>
     </row>
     <row r="32">
@@ -3265,46 +3265,46 @@
         <v>41.173</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>0.926586449468649</v>
+        <v>0.926581390585969</v>
       </c>
       <c r="G32" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H32" s="8" t="n">
-        <v>44.5768633984829</v>
+        <v>44.5769929316379</v>
       </c>
       <c r="I32" s="9" t="n">
-        <v>48.379858791285</v>
+        <v>48.3825859831093</v>
       </c>
       <c r="J32" s="10" t="n">
-        <v>47.043584129517</v>
+        <v>47.043036154579</v>
       </c>
       <c r="K32" s="11" t="n">
-        <v>44.4351415063437</v>
+        <v>44.4353841101452</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>44.4351415063437</v>
+        <v>44.4353841101452</v>
       </c>
       <c r="M32" s="13" t="n">
-        <v>44.6067184799674</v>
+        <v>44.6068134899074</v>
       </c>
       <c r="N32" s="14" t="n">
-        <v>44.6067184799674</v>
+        <v>44.6068134899074</v>
       </c>
       <c r="O32" s="15" t="n">
-        <v>0.0123588401044096</v>
+        <v>0.012360338800716</v>
       </c>
       <c r="P32" s="16" t="n">
-        <v>-0.120541600912147</v>
+        <v>-0.120540173008842</v>
       </c>
       <c r="Q32" s="17" t="n">
-        <v>0.0124355261600411</v>
+        <v>0.0124370434945615</v>
       </c>
       <c r="R32" s="18" t="n">
-        <v>1.00066974388076</v>
+        <v>1.00066896747197</v>
       </c>
       <c r="S32" s="19" t="n">
-        <v>0.922010100781913</v>
+        <v>0.921960093358382</v>
       </c>
     </row>
     <row r="33">
@@ -3324,46 +3324,46 @@
         <v>46.762</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>1.02092739951908</v>
+        <v>1.02092899930142</v>
       </c>
       <c r="G33" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H33" s="8" t="n">
-        <v>45.4226223620389</v>
+        <v>45.4225766397281</v>
       </c>
       <c r="I33" s="9" t="n">
-        <v>48.5006535259922</v>
+        <v>48.5032296203374</v>
       </c>
       <c r="J33" s="10" t="n">
-        <v>46.9264810872711</v>
+        <v>46.9259247640506</v>
       </c>
       <c r="K33" s="11" t="n">
-        <v>45.8034528430012</v>
+        <v>45.8033810695918</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>45.8034528430012</v>
+        <v>45.8033810695918</v>
       </c>
       <c r="M33" s="13" t="n">
-        <v>45.3583917312767</v>
+        <v>45.3583485422744</v>
       </c>
       <c r="N33" s="14" t="n">
-        <v>45.3583917312767</v>
+        <v>45.3583485422744</v>
       </c>
       <c r="O33" s="15" t="n">
-        <v>0.0167107168857844</v>
+        <v>0.0167076347684805</v>
       </c>
       <c r="P33" s="16" t="n">
-        <v>-0.0459384051796985</v>
+        <v>-0.0459392619664138</v>
       </c>
       <c r="Q33" s="17" t="n">
-        <v>0.0168511219144458</v>
+        <v>0.0168479878648373</v>
       </c>
       <c r="R33" s="18" t="n">
-        <v>0.998585933012624</v>
+        <v>0.998585987361239</v>
       </c>
       <c r="S33" s="19" t="n">
-        <v>0.935211970019506</v>
+        <v>0.935161408782884</v>
       </c>
     </row>
     <row r="34">
@@ -3383,46 +3383,46 @@
         <v>49.253</v>
       </c>
       <c r="F34" s="6" t="n">
-        <v>1.08507052176207</v>
+        <v>1.08507701940817</v>
       </c>
       <c r="G34" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H34" s="8" t="n">
-        <v>45.7056925424763</v>
+        <v>45.7054683978162</v>
       </c>
       <c r="I34" s="9" t="n">
-        <v>48.6489426831771</v>
+        <v>48.6512585407603</v>
       </c>
       <c r="J34" s="10" t="n">
-        <v>46.932717636216</v>
+        <v>46.932197295959</v>
       </c>
       <c r="K34" s="11" t="n">
-        <v>45.3915197327607</v>
+        <v>45.3912479197688</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>45.3915197327607</v>
+        <v>45.3912479197688</v>
       </c>
       <c r="M34" s="13" t="n">
-        <v>45.626457649441</v>
+        <v>45.6263019013358</v>
       </c>
       <c r="N34" s="14" t="n">
-        <v>45.626457649441</v>
+        <v>45.6263019013358</v>
       </c>
       <c r="O34" s="15" t="n">
-        <v>0.00589255674196677</v>
+        <v>0.00589009536080919</v>
       </c>
       <c r="P34" s="16" t="n">
-        <v>0.0194043848241463</v>
+        <v>0.0194018403974123</v>
       </c>
       <c r="Q34" s="17" t="n">
-        <v>0.00590995200518618</v>
+        <v>0.00590747608043118</v>
       </c>
       <c r="R34" s="18" t="n">
-        <v>0.998266410842332</v>
+        <v>0.998267898803894</v>
       </c>
       <c r="S34" s="19" t="n">
-        <v>0.937871516480432</v>
+        <v>0.937823671367305</v>
       </c>
     </row>
     <row r="35">
@@ -3442,46 +3442,46 @@
         <v>43.98</v>
       </c>
       <c r="F35" s="6" t="n">
-        <v>0.957766414728681</v>
+        <v>0.95776657310091</v>
       </c>
       <c r="G35" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H35" s="8" t="n">
-        <v>45.5719511617111</v>
+        <v>45.5720148378429</v>
       </c>
       <c r="I35" s="9" t="n">
-        <v>48.8272136596329</v>
+        <v>48.8291400154108</v>
       </c>
       <c r="J35" s="10" t="n">
-        <v>47.0628287888497</v>
+        <v>47.0624062996243</v>
       </c>
       <c r="K35" s="11" t="n">
-        <v>45.9193382892412</v>
+        <v>45.9193306962137</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>45.9193382892412</v>
+        <v>45.9193306962137</v>
       </c>
       <c r="M35" s="13" t="n">
-        <v>45.7602744429794</v>
+        <v>45.7603336723772</v>
       </c>
       <c r="N35" s="14" t="n">
-        <v>45.7602744429794</v>
+        <v>45.7603336723772</v>
       </c>
       <c r="O35" s="15" t="n">
-        <v>0.00292858462307786</v>
+        <v>0.00293329251707363</v>
       </c>
       <c r="P35" s="16" t="n">
-        <v>0.0386177040508358</v>
+        <v>0.0386183927499895</v>
       </c>
       <c r="Q35" s="17" t="n">
-        <v>0.00293287711631218</v>
+        <v>0.00293759882909717</v>
       </c>
       <c r="R35" s="18" t="n">
-        <v>1.00413243840713</v>
+        <v>1.00413233505704</v>
       </c>
       <c r="S35" s="19" t="n">
-        <v>0.937187912502386</v>
+        <v>0.937152152545281</v>
       </c>
     </row>
     <row r="36">
@@ -3501,46 +3501,46 @@
         <v>42.412</v>
       </c>
       <c r="F36" s="6" t="n">
-        <v>0.926465125320817</v>
+        <v>0.926449763757185</v>
       </c>
       <c r="G36" s="7" t="n">
-        <v>0.947651554892939</v>
+        <v>0.947985726064843</v>
       </c>
       <c r="H36" s="8" t="n">
-        <v>46.4010476586104</v>
+        <v>46.4012869606011</v>
       </c>
       <c r="I36" s="9" t="n">
-        <v>49.0359179628088</v>
+        <v>49.0373038086834</v>
       </c>
       <c r="J36" s="10" t="n">
-        <v>47.3096435681527</v>
+        <v>47.309399577486</v>
       </c>
       <c r="K36" s="11" t="n">
-        <v>45.7783016768316</v>
+        <v>45.7790607317979</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>45.8109014606744</v>
+        <v>45.8114253773125</v>
       </c>
       <c r="M36" s="13" t="n">
-        <v>46.4578750187511</v>
+        <v>46.4580715553147</v>
       </c>
       <c r="N36" s="14" t="n">
-        <v>46.4578750187511</v>
+        <v>46.4580715553147</v>
       </c>
       <c r="O36" s="15" t="n">
-        <v>0.0151296439340826</v>
+        <v>0.0151325800101738</v>
       </c>
       <c r="P36" s="16" t="n">
-        <v>0.0414995005654815</v>
+        <v>0.041501688207928</v>
       </c>
       <c r="Q36" s="17" t="n">
-        <v>0.0152446763981047</v>
+        <v>0.0152476572381017</v>
       </c>
       <c r="R36" s="18" t="n">
-        <v>1.00122469993692</v>
+        <v>1.00122377197774</v>
       </c>
       <c r="S36" s="19" t="n">
-        <v>0.947425416895161</v>
+        <v>0.947402649553667</v>
       </c>
     </row>
     <row r="37">
@@ -3560,46 +3560,46 @@
         <v>50.32</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>1.04202994517569</v>
+        <v>1.04203542815304</v>
       </c>
       <c r="G37" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H37" s="8" t="n">
-        <v>47.9173176787396</v>
+        <v>47.9170620513164</v>
       </c>
       <c r="I37" s="9" t="n">
-        <v>49.2736896780475</v>
+        <v>49.2743610541481</v>
       </c>
       <c r="J37" s="10" t="n">
-        <v>47.6602735446075</v>
+        <v>47.6603095539662</v>
       </c>
       <c r="K37" s="11" t="n">
-        <v>48.2903588644143</v>
+        <v>48.2901047704202</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>48.2903588644143</v>
+        <v>48.2901047704202</v>
       </c>
       <c r="M37" s="13" t="n">
-        <v>47.7669553134026</v>
+        <v>47.7667538142871</v>
       </c>
       <c r="N37" s="14" t="n">
-        <v>47.7669553134026</v>
+        <v>47.7667538142871</v>
       </c>
       <c r="O37" s="15" t="n">
-        <v>0.0277881005660096</v>
+        <v>0.0277796517620136</v>
       </c>
       <c r="P37" s="16" t="n">
-        <v>0.0531007271244377</v>
+        <v>0.0530972874765936</v>
       </c>
       <c r="Q37" s="17" t="n">
-        <v>0.0281777910445349</v>
+        <v>0.0281691042086021</v>
       </c>
       <c r="R37" s="18" t="n">
-        <v>0.996862045443672</v>
+        <v>0.996863158328273</v>
       </c>
       <c r="S37" s="19" t="n">
-        <v>0.969421117547926</v>
+        <v>0.969403819600942</v>
       </c>
     </row>
     <row r="38">
@@ -3619,46 +3619,46 @@
         <v>52.582</v>
       </c>
       <c r="F38" s="6" t="n">
-        <v>1.08024040024217</v>
+        <v>1.08025863657967</v>
       </c>
       <c r="G38" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H38" s="8" t="n">
-        <v>48.4096154233053</v>
+        <v>48.4089567759588</v>
       </c>
       <c r="I38" s="9" t="n">
-        <v>49.537147255378</v>
+        <v>49.5369067113554</v>
       </c>
       <c r="J38" s="10" t="n">
-        <v>48.0943365781591</v>
+        <v>48.0947787824862</v>
       </c>
       <c r="K38" s="11" t="n">
-        <v>48.6762020641073</v>
+        <v>48.6753803389954</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>48.6762020641073</v>
+        <v>48.6753803389954</v>
       </c>
       <c r="M38" s="13" t="n">
-        <v>48.2698065311614</v>
+        <v>48.2693202913224</v>
       </c>
       <c r="N38" s="14" t="n">
-        <v>48.2698065311614</v>
+        <v>48.2693202913224</v>
       </c>
       <c r="O38" s="15" t="n">
-        <v>0.0104721526124951</v>
+        <v>0.0104662975750199</v>
       </c>
       <c r="P38" s="16" t="n">
-        <v>0.0579345629246497</v>
+        <v>0.0579275172399896</v>
       </c>
       <c r="Q38" s="17" t="n">
-        <v>0.0105271775113061</v>
+        <v>0.0105212608541332</v>
       </c>
       <c r="R38" s="18" t="n">
-        <v>0.997111960280589</v>
+        <v>0.99711548246572</v>
       </c>
       <c r="S38" s="19" t="n">
-        <v>0.97441635632179</v>
+        <v>0.974411272237503</v>
       </c>
     </row>
     <row r="39">
@@ -3678,46 +3678,46 @@
         <v>44.65</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>0.941259045298932</v>
+        <v>0.941259986135776</v>
       </c>
       <c r="G39" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H39" s="8" t="n">
-        <v>47.8315250424776</v>
+        <v>47.8315819047392</v>
       </c>
       <c r="I39" s="9" t="n">
-        <v>49.8222945630705</v>
+        <v>49.8209205796785</v>
       </c>
       <c r="J39" s="10" t="n">
-        <v>48.5946009553518</v>
+        <v>48.5955987925496</v>
       </c>
       <c r="K39" s="11" t="n">
-        <v>47.4364631320167</v>
+        <v>47.4364157168785</v>
       </c>
       <c r="L39" s="12" t="n">
-        <v>47.4364631320167</v>
+        <v>47.4364157168785</v>
       </c>
       <c r="M39" s="13" t="n">
-        <v>48.0670300534628</v>
+        <v>48.0670406046599</v>
       </c>
       <c r="N39" s="14" t="n">
-        <v>48.0670300534628</v>
+        <v>48.0670406046599</v>
       </c>
       <c r="O39" s="15" t="n">
-        <v>-0.00420974539654223</v>
+        <v>-0.00419945246124549</v>
       </c>
       <c r="P39" s="16" t="n">
-        <v>0.0504095667817248</v>
+        <v>0.0504084377705298</v>
       </c>
       <c r="Q39" s="17" t="n">
-        <v>-0.00420089683946923</v>
+        <v>-0.00419064709098194</v>
       </c>
       <c r="R39" s="18" t="n">
-        <v>1.00492363584009</v>
+        <v>1.00492266177584</v>
       </c>
       <c r="S39" s="19" t="n">
-        <v>0.964769496768447</v>
+        <v>0.964796315390968</v>
       </c>
     </row>
     <row r="40">
@@ -3737,46 +3737,46 @@
         <v>43.651</v>
       </c>
       <c r="F40" s="6" t="n">
-        <v>0.933965567824869</v>
+        <v>0.933927998007314</v>
       </c>
       <c r="G40" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H40" s="8" t="n">
-        <v>48.7189918857107</v>
+        <v>48.719950645887</v>
       </c>
       <c r="I40" s="9" t="n">
-        <v>50.1245973786509</v>
+        <v>50.1218440045077</v>
       </c>
       <c r="J40" s="10" t="n">
-        <v>49.1467442901595</v>
+        <v>49.1484641214427</v>
       </c>
       <c r="K40" s="11" t="n">
-        <v>46.7372690212335</v>
+        <v>46.7391491561838</v>
       </c>
       <c r="L40" s="12" t="n">
-        <v>48.7189918857107</v>
+        <v>48.719950645887</v>
       </c>
       <c r="M40" s="13" t="n">
-        <v>48.9749992199099</v>
+        <v>48.9755063667583</v>
       </c>
       <c r="N40" s="14" t="n">
-        <v>48.9749992199099</v>
+        <v>48.9755063667583</v>
       </c>
       <c r="O40" s="15" t="n">
-        <v>0.0187134516899369</v>
+        <v>0.0187235873453996</v>
       </c>
       <c r="P40" s="16" t="n">
-        <v>0.0541807863606085</v>
+        <v>0.0541872429734025</v>
       </c>
       <c r="Q40" s="17" t="n">
-        <v>0.0188896456768219</v>
+        <v>0.0188999728435613</v>
       </c>
       <c r="R40" s="18" t="n">
-        <v>1.0052547748689</v>
+        <v>1.00524540188328</v>
       </c>
       <c r="S40" s="19" t="n">
-        <v>0.977065189171362</v>
+        <v>0.977128981175427</v>
       </c>
     </row>
     <row r="41">
@@ -3796,46 +3796,46 @@
         <v>53.878</v>
       </c>
       <c r="F41" s="6" t="n">
-        <v>1.05590238665</v>
+        <v>1.05589910709316</v>
       </c>
       <c r="G41" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H41" s="8" t="n">
-        <v>50.9779376295802</v>
+        <v>50.9771929131849</v>
       </c>
       <c r="I41" s="9" t="n">
-        <v>50.4380303350006</v>
+        <v>50.4336280156941</v>
       </c>
       <c r="J41" s="10" t="n">
-        <v>49.7306535074392</v>
+        <v>49.7332733910732</v>
       </c>
       <c r="K41" s="11" t="n">
-        <v>51.0255499762015</v>
+        <v>51.0257084583806</v>
       </c>
       <c r="L41" s="12" t="n">
-        <v>51.0255499762015</v>
+        <v>51.0257084583806</v>
       </c>
       <c r="M41" s="13" t="n">
-        <v>50.7804638205262</v>
+        <v>50.7798953554156</v>
       </c>
       <c r="N41" s="14" t="n">
-        <v>50.7804638205262</v>
+        <v>50.7798953554156</v>
       </c>
       <c r="O41" s="15" t="n">
-        <v>0.0362017622538983</v>
+        <v>0.0361802124625506</v>
       </c>
       <c r="P41" s="16" t="n">
-        <v>0.0630877242929089</v>
+        <v>0.0630803079657316</v>
       </c>
       <c r="Q41" s="17" t="n">
-        <v>0.0368650256125445</v>
+        <v>0.0368426816283418</v>
       </c>
       <c r="R41" s="18" t="n">
-        <v>0.996126288778316</v>
+        <v>0.996129689641693</v>
       </c>
       <c r="S41" s="19" t="n">
-        <v>1.00678919226725</v>
+        <v>1.00686580270636</v>
       </c>
     </row>
     <row r="42">
@@ -3855,46 +3855,46 @@
         <v>55.911</v>
       </c>
       <c r="F42" s="6" t="n">
-        <v>1.06798694679725</v>
+        <v>1.06805936398482</v>
       </c>
       <c r="G42" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H42" s="8" t="n">
-        <v>51.993428323103</v>
+        <v>51.9916305323268</v>
       </c>
       <c r="I42" s="9" t="n">
-        <v>50.7556895615679</v>
+        <v>50.7493474597398</v>
       </c>
       <c r="J42" s="10" t="n">
-        <v>50.324076770026</v>
+        <v>50.3277826559712</v>
       </c>
       <c r="K42" s="11" t="n">
-        <v>52.3517634439912</v>
+        <v>52.3482138590142</v>
       </c>
       <c r="L42" s="12" t="n">
-        <v>52.3517634439912</v>
+        <v>52.3482138590142</v>
       </c>
       <c r="M42" s="13" t="n">
-        <v>51.7012622035349</v>
+        <v>51.6999084923974</v>
       </c>
       <c r="N42" s="14" t="n">
-        <v>51.7012622035349</v>
+        <v>51.6999084923974</v>
       </c>
       <c r="O42" s="15" t="n">
-        <v>0.0179704850550695</v>
+        <v>0.0179554960095179</v>
       </c>
       <c r="P42" s="16" t="n">
-        <v>0.0710890703520488</v>
+        <v>0.0710718149824827</v>
       </c>
       <c r="Q42" s="17" t="n">
-        <v>0.0181329258090881</v>
+        <v>0.0181176650826578</v>
       </c>
       <c r="R42" s="18" t="n">
-        <v>0.994380710620725</v>
+        <v>0.994389057682121</v>
       </c>
       <c r="S42" s="19" t="n">
-        <v>1.01862988465204</v>
+        <v>1.01873050748902</v>
       </c>
     </row>
     <row r="43">
@@ -3914,46 +3914,46 @@
         <v>47.518</v>
       </c>
       <c r="F43" s="6" t="n">
-        <v>0.930339613440115</v>
+        <v>0.930311821311341</v>
       </c>
       <c r="G43" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H43" s="8" t="n">
-        <v>51.386023029653</v>
+        <v>51.386699148739</v>
       </c>
       <c r="I43" s="9" t="n">
-        <v>51.0710383875769</v>
+        <v>51.0624472334235</v>
       </c>
       <c r="J43" s="10" t="n">
-        <v>50.9112367230987</v>
+        <v>50.9162101460032</v>
       </c>
       <c r="K43" s="11" t="n">
-        <v>51.0759719499558</v>
+        <v>51.0774977931808</v>
       </c>
       <c r="L43" s="12" t="n">
-        <v>51.0759719499558</v>
+        <v>51.0774977931808</v>
       </c>
       <c r="M43" s="13" t="n">
-        <v>51.256708968177</v>
+        <v>51.2573583194621</v>
       </c>
       <c r="N43" s="14" t="n">
-        <v>51.256708968177</v>
+        <v>51.2573583194621</v>
       </c>
       <c r="O43" s="15" t="n">
-        <v>-0.00863567906411826</v>
+        <v>-0.00859682686240158</v>
       </c>
       <c r="P43" s="16" t="n">
-        <v>0.0663589764369976</v>
+        <v>0.0663722516441529</v>
       </c>
       <c r="Q43" s="17" t="n">
-        <v>-0.00859849869056928</v>
+        <v>-0.00855997981119139</v>
       </c>
       <c r="R43" s="18" t="n">
-        <v>0.997483477921587</v>
+        <v>0.997482990123523</v>
       </c>
       <c r="S43" s="19" t="n">
-        <v>1.00363553564725</v>
+        <v>1.00381711211661</v>
       </c>
     </row>
     <row r="44">
@@ -3973,46 +3973,46 @@
         <v>48.053</v>
       </c>
       <c r="F44" s="6" t="n">
-        <v>0.951108955428263</v>
+        <v>0.951050689228767</v>
       </c>
       <c r="G44" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H44" s="8" t="n">
-        <v>50.2708594150605</v>
+        <v>50.2739034090622</v>
       </c>
       <c r="I44" s="9" t="n">
-        <v>51.3785376884282</v>
+        <v>51.3673715250234</v>
       </c>
       <c r="J44" s="10" t="n">
-        <v>51.4864944452059</v>
+        <v>51.492876247051</v>
       </c>
       <c r="K44" s="11" t="n">
-        <v>50.5231285288054</v>
+        <v>50.5262238324726</v>
       </c>
       <c r="L44" s="12" t="n">
-        <v>50.5231285288054</v>
+        <v>50.5262238324726</v>
       </c>
       <c r="M44" s="13" t="n">
-        <v>50.479453701021</v>
+        <v>50.4814932553464</v>
       </c>
       <c r="N44" s="14" t="n">
-        <v>50.479453701021</v>
+        <v>50.4814932553464</v>
       </c>
       <c r="O44" s="15" t="n">
-        <v>-0.015280120060262</v>
+        <v>-0.0152523857539025</v>
       </c>
       <c r="P44" s="16" t="n">
-        <v>0.0307188260352129</v>
+        <v>0.030749797200877</v>
       </c>
       <c r="Q44" s="17" t="n">
-        <v>-0.0151639713669208</v>
+        <v>-0.0151366572440215</v>
       </c>
       <c r="R44" s="18" t="n">
-        <v>1.00414940759692</v>
+        <v>1.00412917701248</v>
       </c>
       <c r="S44" s="19" t="n">
-        <v>0.982500786751474</v>
+        <v>0.98275406657229</v>
       </c>
     </row>
     <row r="45">
@@ -4032,46 +4032,46 @@
         <v>52.985</v>
       </c>
       <c r="F45" s="6" t="n">
-        <v>1.06405013923354</v>
+        <v>1.0640406994853</v>
       </c>
       <c r="G45" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H45" s="8" t="n">
-        <v>50.0104403245052</v>
+        <v>50.0093360402502</v>
       </c>
       <c r="I45" s="9" t="n">
-        <v>51.6726514229989</v>
+        <v>51.6585739294175</v>
       </c>
       <c r="J45" s="10" t="n">
-        <v>52.0450346910305</v>
+        <v>52.0529077832322</v>
       </c>
       <c r="K45" s="11" t="n">
-        <v>49.7955857965174</v>
+        <v>49.7960275632596</v>
       </c>
       <c r="L45" s="12" t="n">
-        <v>49.7955857965174</v>
+        <v>49.7960275632596</v>
       </c>
       <c r="M45" s="13" t="n">
-        <v>50.3864153909538</v>
+        <v>50.3857968481468</v>
       </c>
       <c r="N45" s="14" t="n">
-        <v>50.3864153909538</v>
+        <v>50.3857968481468</v>
       </c>
       <c r="O45" s="15" t="n">
-        <v>-0.001844793234637</v>
+        <v>-0.00189747213023164</v>
       </c>
       <c r="P45" s="16" t="n">
-        <v>-0.00775984305628019</v>
+        <v>-0.00776091609701912</v>
       </c>
       <c r="Q45" s="17" t="n">
-        <v>-0.00184309264950111</v>
+        <v>-0.00189567306805916</v>
       </c>
       <c r="R45" s="18" t="n">
-        <v>1.00751793153608</v>
+        <v>1.00752781055908</v>
       </c>
       <c r="S45" s="19" t="n">
-        <v>0.97510799239784</v>
+        <v>0.975361745699567</v>
       </c>
     </row>
     <row r="46">
@@ -4091,46 +4091,46 @@
         <v>53.805</v>
       </c>
       <c r="F46" s="6" t="n">
-        <v>1.0461515793375</v>
+        <v>1.04628285472745</v>
       </c>
       <c r="G46" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H46" s="8" t="n">
-        <v>51.8140246964331</v>
+        <v>51.8109783296764</v>
       </c>
       <c r="I46" s="9" t="n">
-        <v>51.9473089194412</v>
+        <v>51.9299823241762</v>
       </c>
       <c r="J46" s="10" t="n">
-        <v>52.5772253856732</v>
+        <v>52.5865983165917</v>
       </c>
       <c r="K46" s="11" t="n">
-        <v>51.431361441975</v>
+        <v>51.4249084335955</v>
       </c>
       <c r="L46" s="12" t="n">
-        <v>51.431361441975</v>
+        <v>51.4249084335955</v>
       </c>
       <c r="M46" s="13" t="n">
-        <v>51.9251669466735</v>
+        <v>51.9229130040757</v>
       </c>
       <c r="N46" s="14" t="n">
-        <v>51.9251669466735</v>
+        <v>51.9229130040757</v>
       </c>
       <c r="O46" s="15" t="n">
-        <v>0.0300819820549736</v>
+        <v>0.0300508496541564</v>
       </c>
       <c r="P46" s="16" t="n">
-        <v>0.00433074036485115</v>
+        <v>0.00431344112941767</v>
       </c>
       <c r="Q46" s="17" t="n">
-        <v>0.0305390161967338</v>
+        <v>0.0305069335424315</v>
       </c>
       <c r="R46" s="18" t="n">
-        <v>1.002145022528</v>
+        <v>1.00216044317262</v>
       </c>
       <c r="S46" s="19" t="n">
-        <v>0.999573760927596</v>
+        <v>0.999863868235957</v>
       </c>
     </row>
     <row r="47">
@@ -4150,46 +4150,46 @@
         <v>51.089</v>
       </c>
       <c r="F47" s="6" t="n">
-        <v>0.928176059848799</v>
+        <v>0.928117911983017</v>
       </c>
       <c r="G47" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H47" s="8" t="n">
-        <v>54.4578757503438</v>
+        <v>54.4580269680921</v>
       </c>
       <c r="I47" s="9" t="n">
-        <v>52.195266339891</v>
+        <v>52.1743604953907</v>
       </c>
       <c r="J47" s="10" t="n">
-        <v>53.0621872097626</v>
+        <v>53.0729570080744</v>
       </c>
       <c r="K47" s="11" t="n">
-        <v>55.0423591062265</v>
+        <v>55.0458075858521</v>
       </c>
       <c r="L47" s="12" t="n">
-        <v>55.0423591062265</v>
+        <v>55.0458075858521</v>
       </c>
       <c r="M47" s="13" t="n">
-        <v>54.1362632500557</v>
+        <v>54.1375713671732</v>
       </c>
       <c r="N47" s="14" t="n">
-        <v>54.1362632500557</v>
+        <v>54.1375713671732</v>
       </c>
       <c r="O47" s="15" t="n">
-        <v>0.0417006767650006</v>
+        <v>0.0417682483500529</v>
       </c>
       <c r="P47" s="16" t="n">
-        <v>0.0561790707957162</v>
+        <v>0.0561912112161569</v>
       </c>
       <c r="Q47" s="17" t="n">
-        <v>0.0425823629157116</v>
+        <v>0.0426528142387483</v>
       </c>
       <c r="R47" s="18" t="n">
-        <v>0.994094288551347</v>
+        <v>0.99411554882246</v>
       </c>
       <c r="S47" s="19" t="n">
-        <v>1.03718722110785</v>
+        <v>1.037627885673</v>
       </c>
     </row>
     <row r="48">
@@ -4209,46 +4209,46 @@
         <v>53.311</v>
       </c>
       <c r="F48" s="6" t="n">
-        <v>0.968780567011508</v>
+        <v>0.968696272886645</v>
       </c>
       <c r="G48" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H48" s="8" t="n">
-        <v>54.896486185342</v>
+        <v>54.9029075843718</v>
       </c>
       <c r="I48" s="9" t="n">
-        <v>52.4089573793106</v>
+        <v>52.3841565579709</v>
       </c>
       <c r="J48" s="10" t="n">
-        <v>53.4733115242084</v>
+        <v>53.4851845692101</v>
       </c>
       <c r="K48" s="11" t="n">
-        <v>55.0289733457945</v>
+        <v>55.033761863393</v>
       </c>
       <c r="L48" s="12" t="n">
-        <v>55.0289733457945</v>
+        <v>55.033761863393</v>
       </c>
       <c r="M48" s="13" t="n">
-        <v>54.6849772432173</v>
+        <v>54.6928617722894</v>
       </c>
       <c r="N48" s="14" t="n">
-        <v>54.6849772432173</v>
+        <v>54.6928617722894</v>
       </c>
       <c r="O48" s="15" t="n">
-        <v>0.0100847709718569</v>
+        <v>0.0102047783504792</v>
       </c>
       <c r="P48" s="16" t="n">
-        <v>0.083311589842171</v>
+        <v>0.0834240083913722</v>
       </c>
       <c r="Q48" s="17" t="n">
-        <v>0.0101357936477282</v>
+        <v>0.0102570246705396</v>
       </c>
       <c r="R48" s="18" t="n">
-        <v>0.996147131504727</v>
+        <v>0.996174231542116</v>
       </c>
       <c r="S48" s="19" t="n">
-        <v>1.04342806988954</v>
+        <v>1.04407258541547</v>
       </c>
     </row>
     <row r="49">
@@ -4268,46 +4268,46 @@
         <v>57.045</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>1.07154914728746</v>
+        <v>1.07153487018247</v>
       </c>
       <c r="G49" s="7" t="n">
-        <v>0.656034519706824</v>
+        <v>0.647078141523793</v>
       </c>
       <c r="H49" s="8" t="n">
-        <v>54.4093657120476</v>
+        <v>54.4307432266049</v>
       </c>
       <c r="I49" s="9" t="n">
-        <v>52.5825951656411</v>
+        <v>52.5536132812581</v>
       </c>
       <c r="J49" s="10" t="n">
-        <v>53.7938905494027</v>
+        <v>53.8063459644178</v>
       </c>
       <c r="K49" s="11" t="n">
-        <v>53.2360089543301</v>
+        <v>53.2367182696405</v>
       </c>
       <c r="L49" s="12" t="n">
-        <v>53.6396031750536</v>
+        <v>53.6581157765194</v>
       </c>
       <c r="M49" s="13" t="n">
-        <v>54.3282213475894</v>
+        <v>54.3562898925463</v>
       </c>
       <c r="N49" s="14" t="n">
-        <v>54.3282213475894</v>
+        <v>54.3562898925463</v>
       </c>
       <c r="O49" s="15" t="n">
-        <v>-0.00654521055891873</v>
+        <v>-0.00617286688323414</v>
       </c>
       <c r="P49" s="16" t="n">
-        <v>0.0782315218506955</v>
+        <v>0.0788018309279859</v>
       </c>
       <c r="Q49" s="17" t="n">
-        <v>-0.00652383732448458</v>
+        <v>-0.00615385388214607</v>
       </c>
       <c r="R49" s="18" t="n">
-        <v>0.99850863241289</v>
+        <v>0.998632145555157</v>
       </c>
       <c r="S49" s="19" t="n">
-        <v>1.03319779437377</v>
+        <v>1.03430166831043</v>
       </c>
     </row>
     <row r="50">
@@ -4327,46 +4327,46 @@
         <v>58.277</v>
       </c>
       <c r="F50" s="6" t="n">
-        <v>1.02098865649231</v>
+        <v>1.02118735916925</v>
       </c>
       <c r="G50" s="7" t="n">
-        <v>0.128165546893455</v>
+        <v>0.148793666070673</v>
       </c>
       <c r="H50" s="8" t="n">
-        <v>54.6997720954991</v>
+        <v>54.7268328223335</v>
       </c>
       <c r="I50" s="9" t="n">
-        <v>52.7120303368032</v>
+        <v>52.6786294379095</v>
       </c>
       <c r="J50" s="10" t="n">
-        <v>54.0149948148456</v>
+        <v>54.0272490445871</v>
       </c>
       <c r="K50" s="11" t="n">
-        <v>57.0789887129749</v>
+        <v>57.0678822810822</v>
       </c>
       <c r="L50" s="12" t="n">
-        <v>55.0047056944559</v>
+        <v>55.0751661537535</v>
       </c>
       <c r="M50" s="13" t="n">
-        <v>54.689307632356</v>
+        <v>54.7306443515108</v>
       </c>
       <c r="N50" s="14" t="n">
-        <v>54.689307632356</v>
+        <v>54.7306443515108</v>
       </c>
       <c r="O50" s="15" t="n">
-        <v>0.00662439533522825</v>
+        <v>0.0068634420998648</v>
       </c>
       <c r="P50" s="16" t="n">
-        <v>0.0532331593371906</v>
+        <v>0.0540749966631258</v>
       </c>
       <c r="Q50" s="17" t="n">
-        <v>0.00664638517164695</v>
+        <v>0.00688704949702346</v>
       </c>
       <c r="R50" s="18" t="n">
-        <v>0.999808692746931</v>
+        <v>1.00006964644181</v>
       </c>
       <c r="S50" s="19" t="n">
-        <v>1.03751093029274</v>
+        <v>1.03895346054931</v>
       </c>
     </row>
     <row r="51">
@@ -4386,46 +4386,46 @@
         <v>51.191</v>
       </c>
       <c r="F51" s="6" t="n">
-        <v>0.928917750342093</v>
+        <v>0.928818084032586</v>
       </c>
       <c r="G51" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H51" s="8" t="n">
-        <v>55.7725266059572</v>
+        <v>55.7875150069618</v>
       </c>
       <c r="I51" s="9" t="n">
-        <v>52.793774160723</v>
+        <v>52.7557941146418</v>
       </c>
       <c r="J51" s="10" t="n">
-        <v>54.1269234131655</v>
+        <v>54.1379605096683</v>
       </c>
       <c r="K51" s="11" t="n">
-        <v>55.1082159654586</v>
+        <v>55.114129322017</v>
       </c>
       <c r="L51" s="12" t="n">
-        <v>55.1082159654586</v>
+        <v>55.114129322017</v>
       </c>
       <c r="M51" s="13" t="n">
-        <v>55.645224749079</v>
+        <v>55.6673730952911</v>
       </c>
       <c r="N51" s="14" t="n">
-        <v>55.645224749079</v>
+        <v>55.6673730952911</v>
       </c>
       <c r="O51" s="15" t="n">
-        <v>0.0173280479775321</v>
+        <v>0.0169704356380646</v>
       </c>
       <c r="P51" s="16" t="n">
-        <v>0.0278733959167703</v>
+        <v>0.0282576718808174</v>
       </c>
       <c r="Q51" s="17" t="n">
-        <v>0.0174790495273598</v>
+        <v>0.017115251517305</v>
       </c>
       <c r="R51" s="18" t="n">
-        <v>0.997717480906367</v>
+        <v>0.997846437295949</v>
       </c>
       <c r="S51" s="19" t="n">
-        <v>1.05401111463778</v>
+        <v>1.05518974796062</v>
       </c>
     </row>
     <row r="52">
@@ -4445,46 +4445,46 @@
         <v>56.535</v>
       </c>
       <c r="F52" s="6" t="n">
-        <v>0.985621255193007</v>
+        <v>0.985512906524941</v>
       </c>
       <c r="G52" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H52" s="8" t="n">
-        <v>57.144354748277</v>
+        <v>57.1477188684522</v>
       </c>
       <c r="I52" s="9" t="n">
-        <v>52.8257708274252</v>
+        <v>52.7831942336192</v>
       </c>
       <c r="J52" s="10" t="n">
-        <v>54.1249239913887</v>
+        <v>54.1337866451574</v>
       </c>
       <c r="K52" s="11" t="n">
-        <v>57.3597613709428</v>
+        <v>57.3660675833769</v>
       </c>
       <c r="L52" s="12" t="n">
-        <v>57.3597613709428</v>
+        <v>57.3660675833769</v>
       </c>
       <c r="M52" s="13" t="n">
-        <v>56.830031543834</v>
+        <v>56.834659428366</v>
       </c>
       <c r="N52" s="14" t="n">
-        <v>56.830031543834</v>
+        <v>56.834659428366</v>
       </c>
       <c r="O52" s="15" t="n">
-        <v>0.0210686449670085</v>
+        <v>0.0207521268309843</v>
       </c>
       <c r="P52" s="16" t="n">
-        <v>0.0392256595641673</v>
+        <v>0.0391604605550517</v>
       </c>
       <c r="Q52" s="17" t="n">
-        <v>0.0212921557976931</v>
+        <v>0.0209689494612357</v>
       </c>
       <c r="R52" s="18" t="n">
-        <v>0.994499488080186</v>
+        <v>0.994521925874123</v>
       </c>
       <c r="S52" s="19" t="n">
-        <v>1.07580127376636</v>
+        <v>1.07675672633253</v>
       </c>
     </row>
     <row r="53">
@@ -4504,46 +4504,46 @@
         <v>62.113</v>
       </c>
       <c r="F53" s="6" t="n">
-        <v>1.08036911903477</v>
+        <v>1.08036938668801</v>
       </c>
       <c r="G53" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H53" s="8" t="n">
-        <v>56.9767281299735</v>
+        <v>56.9744430795162</v>
       </c>
       <c r="I53" s="9" t="n">
-        <v>52.8074110530626</v>
+        <v>52.7603906765104</v>
       </c>
       <c r="J53" s="10" t="n">
-        <v>54.0091506593031</v>
+        <v>54.0149145806123</v>
       </c>
       <c r="K53" s="11" t="n">
-        <v>57.4923874679918</v>
+        <v>57.4923732246932</v>
       </c>
       <c r="L53" s="12" t="n">
-        <v>57.4923874679918</v>
+        <v>57.4923732246932</v>
       </c>
       <c r="M53" s="13" t="n">
-        <v>56.5366523793239</v>
+        <v>56.5352443873063</v>
       </c>
       <c r="N53" s="14" t="n">
-        <v>56.5366523793239</v>
+        <v>56.5352443873063</v>
       </c>
       <c r="O53" s="15" t="n">
-        <v>-0.00517576785862009</v>
+        <v>-0.00528210269458064</v>
       </c>
       <c r="P53" s="16" t="n">
-        <v>0.0406497944706312</v>
+        <v>0.0400865198685827</v>
       </c>
       <c r="Q53" s="17" t="n">
-        <v>-0.00516239665085916</v>
+        <v>-0.00526817692005521</v>
       </c>
       <c r="R53" s="18" t="n">
-        <v>0.992276219342646</v>
+        <v>0.992291303460449</v>
       </c>
       <c r="S53" s="19" t="n">
-        <v>1.07061965833762</v>
+        <v>1.07154711446207</v>
       </c>
     </row>
     <row r="54">
@@ -4563,46 +4563,46 @@
         <v>53.27</v>
       </c>
       <c r="F54" s="6" t="n">
-        <v>0.990110544471239</v>
+        <v>0.990329765100963</v>
       </c>
       <c r="G54" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H54" s="8" t="n">
-        <v>54.3265157203401</v>
+        <v>54.3191930552151</v>
       </c>
       <c r="I54" s="9" t="n">
-        <v>52.7409192978775</v>
+        <v>52.6898086208278</v>
       </c>
       <c r="J54" s="10" t="n">
-        <v>53.7959317135943</v>
+        <v>53.797692850282</v>
       </c>
       <c r="K54" s="11" t="n">
-        <v>53.8020732103691</v>
+        <v>53.7901635164618</v>
       </c>
       <c r="L54" s="12" t="n">
-        <v>53.8020732103691</v>
+        <v>53.7901635164618</v>
       </c>
       <c r="M54" s="13" t="n">
-        <v>54.176030130061</v>
+        <v>54.1707428243257</v>
       </c>
       <c r="N54" s="14" t="n">
-        <v>54.176030130061</v>
+        <v>54.1707428243257</v>
       </c>
       <c r="O54" s="15" t="n">
-        <v>-0.0426505804042626</v>
+        <v>-0.0427232757273193</v>
       </c>
       <c r="P54" s="16" t="n">
-        <v>-0.00938533553479048</v>
+        <v>-0.0102301285471658</v>
       </c>
       <c r="Q54" s="17" t="n">
-        <v>-0.0417538384378457</v>
+        <v>-0.0418234959202111</v>
       </c>
       <c r="R54" s="18" t="n">
-        <v>0.997229978983857</v>
+        <v>0.997267075916637</v>
       </c>
       <c r="S54" s="19" t="n">
-        <v>1.02721057674551</v>
+        <v>1.02810665368241</v>
       </c>
     </row>
     <row r="55">
@@ -4622,46 +4622,46 @@
         <v>48.455</v>
       </c>
       <c r="F55" s="6" t="n">
-        <v>0.938912341434918</v>
+        <v>0.938863505730098</v>
       </c>
       <c r="G55" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H55" s="8" t="n">
-        <v>51.2147333907654</v>
+        <v>51.216965212365</v>
       </c>
       <c r="I55" s="9" t="n">
-        <v>52.6314481323718</v>
+        <v>52.5768307331764</v>
       </c>
       <c r="J55" s="10" t="n">
-        <v>53.5190116349915</v>
+        <v>53.5158572816356</v>
       </c>
       <c r="K55" s="11" t="n">
-        <v>51.6075866315138</v>
+        <v>51.6102710396858</v>
       </c>
       <c r="L55" s="12" t="n">
-        <v>51.6075866315138</v>
+        <v>51.6102710396858</v>
       </c>
       <c r="M55" s="13" t="n">
-        <v>51.5256336803783</v>
+        <v>51.5273388727594</v>
       </c>
       <c r="N55" s="14" t="n">
-        <v>51.5256336803783</v>
+        <v>51.5273388727594</v>
       </c>
       <c r="O55" s="15" t="n">
-        <v>-0.050159136897906</v>
+        <v>-0.0500284436958703</v>
       </c>
       <c r="P55" s="16" t="n">
-        <v>-0.0740331463710886</v>
+        <v>-0.0743709284690833</v>
       </c>
       <c r="Q55" s="17" t="n">
-        <v>-0.0489219391550072</v>
+        <v>-0.0487976315949499</v>
       </c>
       <c r="R55" s="18" t="n">
-        <v>1.00607052441806</v>
+        <v>1.00605997757008</v>
       </c>
       <c r="S55" s="19" t="n">
-        <v>0.978989473190775</v>
+        <v>0.980038890785506</v>
       </c>
     </row>
     <row r="56">
@@ -4681,46 +4681,46 @@
         <v>49.068</v>
       </c>
       <c r="F56" s="6" t="n">
-        <v>0.999647791655434</v>
+        <v>0.999375748716722</v>
       </c>
       <c r="G56" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H56" s="8" t="n">
-        <v>49.5207176322892</v>
+        <v>49.5296724809904</v>
       </c>
       <c r="I56" s="9" t="n">
-        <v>52.4848133482426</v>
+        <v>52.4275274019708</v>
       </c>
       <c r="J56" s="10" t="n">
-        <v>53.2121656117074</v>
+        <v>53.2031060554735</v>
       </c>
       <c r="K56" s="11" t="n">
-        <v>49.0852882481164</v>
+        <v>49.0986498952043</v>
       </c>
       <c r="L56" s="12" t="n">
-        <v>49.0852882481164</v>
+        <v>49.0986498952043</v>
       </c>
       <c r="M56" s="13" t="n">
-        <v>49.8849971744161</v>
+        <v>49.8913189512704</v>
       </c>
       <c r="N56" s="14" t="n">
-        <v>49.8849971744161</v>
+        <v>49.8913189512704</v>
       </c>
       <c r="O56" s="15" t="n">
-        <v>-0.0323591254806007</v>
+        <v>-0.032265500005199</v>
       </c>
       <c r="P56" s="16" t="n">
-        <v>-0.122207117975311</v>
+        <v>-0.122167363135992</v>
       </c>
       <c r="Q56" s="17" t="n">
-        <v>-0.0318411708653473</v>
+        <v>-0.0317505222912636</v>
       </c>
       <c r="R56" s="18" t="n">
-        <v>1.00735610386004</v>
+        <v>1.00730161239041</v>
       </c>
       <c r="S56" s="19" t="n">
-        <v>0.950465363064617</v>
+        <v>0.951624488577254</v>
       </c>
     </row>
     <row r="57">
@@ -4740,46 +4740,46 @@
         <v>53.828</v>
       </c>
       <c r="F57" s="6" t="n">
-        <v>1.08171272624171</v>
+        <v>1.08180230633746</v>
       </c>
       <c r="G57" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H57" s="8" t="n">
-        <v>49.7344106161766</v>
+        <v>49.7321162824162</v>
       </c>
       <c r="I57" s="9" t="n">
-        <v>52.3061908237488</v>
+        <v>52.2473649158174</v>
       </c>
       <c r="J57" s="10" t="n">
-        <v>52.8996117069377</v>
+        <v>52.8836094213861</v>
       </c>
       <c r="K57" s="11" t="n">
-        <v>49.7618255699176</v>
+        <v>49.7577049749871</v>
       </c>
       <c r="L57" s="12" t="n">
-        <v>49.7618255699176</v>
+        <v>49.7577049749871</v>
       </c>
       <c r="M57" s="13" t="n">
-        <v>49.9606629942069</v>
+        <v>49.9584459738693</v>
       </c>
       <c r="N57" s="14" t="n">
-        <v>49.9606629942069</v>
+        <v>49.9584459738693</v>
       </c>
       <c r="O57" s="15" t="n">
-        <v>0.00151565594634886</v>
+        <v>0.00134456065594553</v>
       </c>
       <c r="P57" s="16" t="n">
-        <v>-0.116313738227662</v>
+        <v>-0.116330945142489</v>
       </c>
       <c r="Q57" s="17" t="n">
-        <v>0.00151680513334007</v>
+        <v>0.00134546498288635</v>
       </c>
       <c r="R57" s="18" t="n">
-        <v>1.00454921200889</v>
+        <v>1.00455097647902</v>
       </c>
       <c r="S57" s="19" t="n">
-        <v>0.955157739598254</v>
+        <v>0.956190729510741</v>
       </c>
     </row>
     <row r="58">
@@ -4799,46 +4799,46 @@
         <v>49.391</v>
       </c>
       <c r="F58" s="6" t="n">
-        <v>0.964033202050714</v>
+        <v>0.964296487647943</v>
       </c>
       <c r="G58" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H58" s="8" t="n">
-        <v>50.8506083096699</v>
+        <v>50.8365546016281</v>
       </c>
       <c r="I58" s="9" t="n">
-        <v>52.098631733962</v>
+        <v>52.0397290148808</v>
       </c>
       <c r="J58" s="10" t="n">
-        <v>52.5849335970599</v>
+        <v>52.5610153481625</v>
       </c>
       <c r="K58" s="11" t="n">
-        <v>51.2337125888759</v>
+        <v>51.2197240502988</v>
       </c>
       <c r="L58" s="12" t="n">
-        <v>51.2337125888759</v>
+        <v>51.2197240502988</v>
       </c>
       <c r="M58" s="13" t="n">
-        <v>50.9250199012729</v>
+        <v>50.9156603976553</v>
       </c>
       <c r="N58" s="14" t="n">
-        <v>50.9250199012729</v>
+        <v>50.9156603976553</v>
       </c>
       <c r="O58" s="15" t="n">
-        <v>0.0191183972386668</v>
+        <v>0.0189789667641412</v>
       </c>
       <c r="P58" s="16" t="n">
-        <v>-0.0600082771104373</v>
+        <v>-0.0600893075663841</v>
       </c>
       <c r="Q58" s="17" t="n">
-        <v>0.0193023240539825</v>
+        <v>0.0191602121548495</v>
       </c>
       <c r="R58" s="18" t="n">
-        <v>1.0014633372948</v>
+        <v>1.00155608098635</v>
       </c>
       <c r="S58" s="19" t="n">
-        <v>0.97747326957295</v>
+        <v>0.978399798797875</v>
       </c>
     </row>
     <row r="59">
@@ -4858,46 +4858,46 @@
         <v>49.029</v>
       </c>
       <c r="F59" s="6" t="n">
-        <v>0.952558975411371</v>
+        <v>0.952657818174125</v>
       </c>
       <c r="G59" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H59" s="8" t="n">
-        <v>51.9200815433189</v>
+        <v>51.923122485803</v>
       </c>
       <c r="I59" s="9" t="n">
-        <v>51.8635970256699</v>
+        <v>51.8064494018625</v>
       </c>
       <c r="J59" s="10" t="n">
-        <v>52.2560260277667</v>
+        <v>52.2233422823599</v>
       </c>
       <c r="K59" s="11" t="n">
-        <v>51.4708288574221</v>
+        <v>51.4654885150363</v>
       </c>
       <c r="L59" s="12" t="n">
-        <v>51.4708288574221</v>
+        <v>51.4654885150363</v>
       </c>
       <c r="M59" s="13" t="n">
-        <v>51.9589849133186</v>
+        <v>51.9612209527695</v>
       </c>
       <c r="N59" s="14" t="n">
-        <v>51.9589849133186</v>
+        <v>51.9612209527695</v>
       </c>
       <c r="O59" s="15" t="n">
-        <v>0.0201003027776864</v>
+        <v>0.0203271433318177</v>
       </c>
       <c r="P59" s="16" t="n">
-        <v>0.00841040084297573</v>
+        <v>0.00842042475900917</v>
       </c>
       <c r="Q59" s="17" t="n">
-        <v>0.0203036741870743</v>
+        <v>0.0205351466905921</v>
       </c>
       <c r="R59" s="18" t="n">
-        <v>1.00074929331471</v>
+        <v>1.00073374760882</v>
       </c>
       <c r="S59" s="19" t="n">
-        <v>1.00183920694127</v>
+        <v>1.00298749581749</v>
       </c>
     </row>
     <row r="60">
@@ -4917,46 +4917,46 @@
         <v>54.484</v>
       </c>
       <c r="F60" s="6" t="n">
-        <v>1.01534517170479</v>
+        <v>1.01470955006904</v>
       </c>
       <c r="G60" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H60" s="8" t="n">
-        <v>53.5105847623225</v>
+        <v>53.5318823554545</v>
       </c>
       <c r="I60" s="9" t="n">
-        <v>51.6020070711947</v>
+        <v>51.5488432763612</v>
       </c>
       <c r="J60" s="10" t="n">
-        <v>51.8940276397094</v>
+        <v>51.8519022140461</v>
       </c>
       <c r="K60" s="11" t="n">
-        <v>53.6605693495543</v>
+        <v>53.6941827307065</v>
       </c>
       <c r="L60" s="12" t="n">
-        <v>53.6605693495543</v>
+        <v>53.6941827307065</v>
       </c>
       <c r="M60" s="13" t="n">
-        <v>53.4159757183968</v>
+        <v>53.4315765488249</v>
       </c>
       <c r="N60" s="14" t="n">
-        <v>53.4159757183968</v>
+        <v>53.4315765488249</v>
       </c>
       <c r="O60" s="15" t="n">
-        <v>0.0276552162937803</v>
+        <v>0.0279042028811242</v>
       </c>
       <c r="P60" s="16" t="n">
-        <v>0.0707823743406288</v>
+        <v>0.0709593907712152</v>
       </c>
       <c r="Q60" s="17" t="n">
-        <v>0.0280411714645474</v>
+        <v>0.0282971717964813</v>
       </c>
       <c r="R60" s="18" t="n">
-        <v>0.998231956455981</v>
+        <v>0.998126241742005</v>
       </c>
       <c r="S60" s="19" t="n">
-        <v>1.03515306380815</v>
+        <v>1.03652328845422</v>
       </c>
     </row>
     <row r="61">
@@ -4976,46 +4976,46 @@
         <v>58.759</v>
       </c>
       <c r="F61" s="6" t="n">
-        <v>1.0708388479554</v>
+        <v>1.07082876058917</v>
       </c>
       <c r="G61" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H61" s="8" t="n">
-        <v>54.6166497876217</v>
+        <v>54.6218094867251</v>
       </c>
       <c r="I61" s="9" t="n">
-        <v>51.3145367627533</v>
+        <v>51.2680147374213</v>
       </c>
       <c r="J61" s="10" t="n">
-        <v>51.4761510876881</v>
+        <v>51.4242178644522</v>
       </c>
       <c r="K61" s="11" t="n">
-        <v>54.8719353170565</v>
+        <v>54.8724522188504</v>
       </c>
       <c r="L61" s="12" t="n">
-        <v>54.8719353170565</v>
+        <v>54.8724522188504</v>
       </c>
       <c r="M61" s="13" t="n">
-        <v>54.4052538077534</v>
+        <v>54.4041015521407</v>
       </c>
       <c r="N61" s="14" t="n">
-        <v>54.4052538077534</v>
+        <v>54.4041015521407</v>
       </c>
       <c r="O61" s="15" t="n">
-        <v>0.0183508545670164</v>
+        <v>0.0180376548550668</v>
       </c>
       <c r="P61" s="16" t="n">
-        <v>0.0889618060925625</v>
+        <v>0.0889870669835615</v>
       </c>
       <c r="Q61" s="17" t="n">
-        <v>0.0185202661947419</v>
+        <v>0.0182013158909338</v>
       </c>
       <c r="R61" s="18" t="n">
-        <v>0.996129459044259</v>
+        <v>0.996014267256428</v>
       </c>
       <c r="S61" s="19" t="n">
-        <v>1.0602308281431</v>
+        <v>1.06117043600735</v>
       </c>
     </row>
     <row r="62">
@@ -5035,46 +5035,46 @@
         <v>51.099</v>
       </c>
       <c r="F62" s="6" t="n">
-        <v>0.942497746618571</v>
+        <v>0.943180668687686</v>
       </c>
       <c r="G62" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H62" s="8" t="n">
-        <v>54.6061504908016</v>
+        <v>54.5611429656043</v>
       </c>
       <c r="I62" s="9" t="n">
-        <v>51.0031475939866</v>
+        <v>50.9664087212463</v>
       </c>
       <c r="J62" s="10" t="n">
-        <v>50.9884417350517</v>
+        <v>50.9270233573928</v>
       </c>
       <c r="K62" s="11" t="n">
-        <v>54.2165752473462</v>
+        <v>54.1773190401555</v>
       </c>
       <c r="L62" s="12" t="n">
-        <v>54.2165752473462</v>
+        <v>54.1773190401555</v>
       </c>
       <c r="M62" s="13" t="n">
-        <v>54.3303843470095</v>
+        <v>54.2920368519768</v>
       </c>
       <c r="N62" s="14" t="n">
-        <v>54.3303843470095</v>
+        <v>54.2920368519768</v>
       </c>
       <c r="O62" s="15" t="n">
-        <v>-0.00137709170325674</v>
+        <v>-0.00206198198970748</v>
       </c>
       <c r="P62" s="16" t="n">
-        <v>0.066870164259897</v>
+        <v>0.0663131230735643</v>
       </c>
       <c r="Q62" s="17" t="n">
-        <v>-0.0013761439475759</v>
+        <v>-0.00205985756527038</v>
       </c>
       <c r="R62" s="18" t="n">
-        <v>0.994949906900349</v>
+        <v>0.995067806519428</v>
       </c>
       <c r="S62" s="19" t="n">
-        <v>1.0652359101346</v>
+        <v>1.06525137270157</v>
       </c>
     </row>
     <row r="63">
@@ -5094,46 +5094,46 @@
         <v>48.786</v>
       </c>
       <c r="F63" s="6" t="n">
-        <v>0.97991243318643</v>
+        <v>0.980554751852713</v>
       </c>
       <c r="G63" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H63" s="8" t="n">
-        <v>54.0164515762891</v>
+        <v>53.9410571087457</v>
       </c>
       <c r="I63" s="9" t="n">
-        <v>50.6720244326322</v>
+        <v>50.6487229374655</v>
       </c>
       <c r="J63" s="10" t="n">
-        <v>50.4339238662962</v>
+        <v>50.3642939884544</v>
       </c>
       <c r="K63" s="11" t="n">
-        <v>49.7860812331569</v>
+        <v>49.7534685419872</v>
       </c>
       <c r="L63" s="12" t="n">
-        <v>54.0164515762891</v>
+        <v>53.9410571087457</v>
       </c>
       <c r="M63" s="13" t="n">
-        <v>53.6854379814643</v>
+        <v>53.628769691213</v>
       </c>
       <c r="N63" s="14" t="n">
-        <v>53.6854379814643</v>
+        <v>53.628769691213</v>
       </c>
       <c r="O63" s="15" t="n">
-        <v>-0.011941843632656</v>
+        <v>-0.0122918931596172</v>
       </c>
       <c r="P63" s="16" t="n">
-        <v>0.0332272285731885</v>
+        <v>0.0320921777407657</v>
       </c>
       <c r="Q63" s="17" t="n">
-        <v>-0.0118708228056318</v>
+        <v>-0.0122166564237067</v>
       </c>
       <c r="R63" s="18" t="n">
-        <v>0.993871985568002</v>
+        <v>0.994210580320976</v>
       </c>
       <c r="S63" s="19" t="n">
-        <v>1.05946897884134</v>
+        <v>1.05883754971328</v>
       </c>
     </row>
     <row r="64">
@@ -5153,46 +5153,46 @@
         <v>58.929</v>
       </c>
       <c r="F64" s="6" t="n">
-        <v>1.02076488604257</v>
+        <v>1.01899709477359</v>
       </c>
       <c r="G64" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H64" s="8" t="n">
-        <v>52.4922735259327</v>
+        <v>52.4556455072049</v>
       </c>
       <c r="I64" s="9" t="n">
-        <v>50.3273605387106</v>
+        <v>50.3216619146573</v>
       </c>
       <c r="J64" s="10" t="n">
-        <v>49.8317624334789</v>
+        <v>49.7562565316371</v>
       </c>
       <c r="K64" s="11" t="n">
-        <v>57.7302381829212</v>
+        <v>57.8303905891836</v>
       </c>
       <c r="L64" s="12" t="n">
-        <v>52.4922735259327</v>
+        <v>52.4556455072049</v>
       </c>
       <c r="M64" s="13" t="n">
-        <v>52.0852631985742</v>
+        <v>52.0543155592045</v>
       </c>
       <c r="N64" s="14" t="n">
-        <v>52.0852631985742</v>
+        <v>52.0543155592045</v>
       </c>
       <c r="O64" s="15" t="n">
-        <v>-0.030259738536534</v>
+        <v>-0.0297979686252175</v>
       </c>
       <c r="P64" s="16" t="n">
-        <v>-0.0249122570902368</v>
+        <v>-0.025776162310351</v>
       </c>
       <c r="Q64" s="17" t="n">
-        <v>-0.0298064958218749</v>
+        <v>-0.029358386199683</v>
       </c>
       <c r="R64" s="18" t="n">
-        <v>0.992246281213989</v>
+        <v>0.992349156242004</v>
       </c>
       <c r="S64" s="19" t="n">
-        <v>1.03492936329358</v>
+        <v>1.03443156641936</v>
       </c>
     </row>
     <row r="65">
@@ -5212,46 +5212,46 @@
         <v>51.654</v>
       </c>
       <c r="F65" s="6" t="n">
-        <v>1.04689791839437</v>
+        <v>1.04637070533673</v>
       </c>
       <c r="G65" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H65" s="8" t="n">
-        <v>48.818935300654</v>
+        <v>48.8026957559934</v>
       </c>
       <c r="I65" s="9" t="n">
-        <v>49.9774394392075</v>
+        <v>49.9939878902575</v>
       </c>
       <c r="J65" s="10" t="n">
-        <v>49.2190350272073</v>
+        <v>49.1410215765429</v>
       </c>
       <c r="K65" s="11" t="n">
-        <v>49.3400541661425</v>
+        <v>49.3649141136624</v>
       </c>
       <c r="L65" s="12" t="n">
-        <v>49.3400541661425</v>
+        <v>49.3649141136624</v>
       </c>
       <c r="M65" s="13" t="n">
-        <v>48.8593584739484</v>
+        <v>48.839533307868</v>
       </c>
       <c r="N65" s="14" t="n">
-        <v>48.8593584739484</v>
+        <v>48.839533307868</v>
       </c>
       <c r="O65" s="15" t="n">
-        <v>-0.0639361168135193</v>
+        <v>-0.0637476097583723</v>
       </c>
       <c r="P65" s="16" t="n">
-        <v>-0.101936760618781</v>
+        <v>-0.102282145748509</v>
       </c>
       <c r="Q65" s="17" t="n">
-        <v>-0.0619350758068968</v>
+        <v>-0.061758227282427</v>
       </c>
       <c r="R65" s="18" t="n">
-        <v>1.00082802242706</v>
+        <v>1.000754826169</v>
       </c>
       <c r="S65" s="19" t="n">
-        <v>0.97762828632669</v>
+        <v>0.976908131735286</v>
       </c>
     </row>
     <row r="66">
@@ -5271,46 +5271,46 @@
         <v>41.524</v>
       </c>
       <c r="F66" s="6" t="n">
-        <v>0.938076385062215</v>
+        <v>0.94003848699385</v>
       </c>
       <c r="G66" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H66" s="8" t="n">
-        <v>44.7242290237141</v>
+        <v>44.6489512854631</v>
       </c>
       <c r="I66" s="9" t="n">
-        <v>49.6318977317254</v>
+        <v>49.6757968414471</v>
       </c>
       <c r="J66" s="10" t="n">
-        <v>48.646121793551</v>
+        <v>48.5701966576513</v>
       </c>
       <c r="K66" s="11" t="n">
-        <v>44.2650520375759</v>
+        <v>44.1726594969421</v>
       </c>
       <c r="L66" s="12" t="n">
-        <v>44.2650520375759</v>
+        <v>44.1726594969421</v>
       </c>
       <c r="M66" s="13" t="n">
-        <v>45.279685438786</v>
+        <v>45.2189139335277</v>
       </c>
       <c r="N66" s="14" t="n">
-        <v>45.279685438786</v>
+        <v>45.2189139335277</v>
       </c>
       <c r="O66" s="15" t="n">
-        <v>-0.0760874490135271</v>
+        <v>-0.0770246444966224</v>
       </c>
       <c r="P66" s="16" t="n">
-        <v>-0.166586322129003</v>
+        <v>-0.16711701097504</v>
       </c>
       <c r="Q66" s="17" t="n">
-        <v>-0.0732648390598709</v>
+        <v>-0.0741329642017067</v>
       </c>
       <c r="R66" s="18" t="n">
-        <v>1.01241958614373</v>
+        <v>1.01276542072445</v>
       </c>
       <c r="S66" s="19" t="n">
-        <v>0.912310177691284</v>
+        <v>0.910280595555525</v>
       </c>
     </row>
     <row r="67">
@@ -5330,46 +5330,46 @@
         <v>43.751</v>
       </c>
       <c r="F67" s="6" t="n">
-        <v>1.01161694662183</v>
+        <v>1.01356588996016</v>
       </c>
       <c r="G67" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H67" s="8" t="n">
-        <v>43.8394081819645</v>
+        <v>43.7893656389056</v>
       </c>
       <c r="I67" s="9" t="n">
-        <v>49.2999736480711</v>
+        <v>49.3767915742967</v>
       </c>
       <c r="J67" s="10" t="n">
-        <v>48.1640079742742</v>
+        <v>48.0965087721275</v>
       </c>
       <c r="K67" s="11" t="n">
-        <v>43.2485835138498</v>
+        <v>43.1654226265642</v>
       </c>
       <c r="L67" s="12" t="n">
-        <v>43.2485835138498</v>
+        <v>43.1654226265642</v>
       </c>
       <c r="M67" s="13" t="n">
-        <v>44.2298235096378</v>
+        <v>44.2001440892951</v>
       </c>
       <c r="N67" s="14" t="n">
-        <v>44.2298235096378</v>
+        <v>44.2001440892951</v>
       </c>
       <c r="O67" s="15" t="n">
-        <v>-0.0234591852615268</v>
+        <v>-0.0227874001521268</v>
       </c>
       <c r="P67" s="16" t="n">
-        <v>-0.176129967964333</v>
+        <v>-0.175812826887632</v>
       </c>
       <c r="Q67" s="17" t="n">
-        <v>-0.0231861577432456</v>
+        <v>-0.0225297282842807</v>
       </c>
       <c r="R67" s="18" t="n">
-        <v>1.00890557933749</v>
+        <v>1.00938078102745</v>
       </c>
       <c r="S67" s="19" t="n">
-        <v>0.897157143031624</v>
+        <v>0.895160310746145</v>
       </c>
     </row>
     <row r="68">
@@ -5389,46 +5389,46 @@
         <v>46.819</v>
       </c>
       <c r="F68" s="6" t="n">
-        <v>1.0143407056688</v>
+        <v>1.01127346449295</v>
       </c>
       <c r="G68" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H68" s="8" t="n">
-        <v>45.149356661541</v>
+        <v>45.301008130631</v>
       </c>
       <c r="I68" s="9" t="n">
-        <v>48.9875511414926</v>
+        <v>49.1032354340365</v>
       </c>
       <c r="J68" s="10" t="n">
-        <v>47.8017734623614</v>
+        <v>47.7506972313332</v>
       </c>
       <c r="K68" s="11" t="n">
-        <v>46.1570749732755</v>
+        <v>46.2970716071097</v>
       </c>
       <c r="L68" s="12" t="n">
-        <v>46.1570749732755</v>
+        <v>46.2970716071097</v>
       </c>
       <c r="M68" s="13" t="n">
-        <v>45.0933042412506</v>
+        <v>45.1958826968235</v>
       </c>
       <c r="N68" s="14" t="n">
-        <v>45.0933042412506</v>
+        <v>45.1958826968235</v>
       </c>
       <c r="O68" s="15" t="n">
-        <v>0.0193344691833825</v>
+        <v>0.0222779428937865</v>
       </c>
       <c r="P68" s="16" t="n">
-        <v>-0.134240637906865</v>
+        <v>-0.131755317281628</v>
       </c>
       <c r="Q68" s="17" t="n">
-        <v>0.0195225904852352</v>
+        <v>0.022527949355025</v>
       </c>
       <c r="R68" s="18" t="n">
-        <v>0.998758511207357</v>
+        <v>0.997679401890917</v>
       </c>
       <c r="S68" s="19" t="n">
-        <v>0.920505377192788</v>
+        <v>0.920425758044762</v>
       </c>
     </row>
     <row r="69">
@@ -5448,46 +5448,46 @@
         <v>45.535</v>
       </c>
       <c r="F69" s="6" t="n">
-        <v>1.01616845967136</v>
+        <v>1.01135028987555</v>
       </c>
       <c r="G69" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H69" s="8" t="n">
-        <v>45.2120459601409</v>
+        <v>45.2738819862328</v>
       </c>
       <c r="I69" s="9" t="n">
-        <v>48.6967320464042</v>
+        <v>48.8575096603047</v>
       </c>
       <c r="J69" s="10" t="n">
-        <v>47.5639210284949</v>
+        <v>47.5388459159021</v>
       </c>
       <c r="K69" s="11" t="n">
-        <v>44.8104835046017</v>
+        <v>45.0239649465105</v>
       </c>
       <c r="L69" s="12" t="n">
-        <v>44.8104835046017</v>
+        <v>45.0239649465105</v>
       </c>
       <c r="M69" s="13" t="n">
-        <v>45.1327429632889</v>
+        <v>45.1782246426462</v>
       </c>
       <c r="N69" s="14" t="n">
-        <v>45.1327429632889</v>
+        <v>45.1782246426462</v>
       </c>
       <c r="O69" s="15" t="n">
-        <v>0.000874220378083554</v>
+        <v>-0.000390776847968801</v>
       </c>
       <c r="P69" s="16" t="n">
-        <v>-0.0762722972027244</v>
+        <v>-0.0749660862265437</v>
       </c>
       <c r="Q69" s="17" t="n">
-        <v>0.000874602620098086</v>
+        <v>-0.000390700504641073</v>
       </c>
       <c r="R69" s="18" t="n">
-        <v>0.998245976372715</v>
+        <v>0.997887140678245</v>
       </c>
       <c r="S69" s="19" t="n">
-        <v>0.926812561472933</v>
+        <v>0.924693562090254</v>
       </c>
     </row>
     <row r="70">
@@ -5507,46 +5507,46 @@
         <v>42.418</v>
       </c>
       <c r="F70" s="6" t="n">
-        <v>0.947826212106692</v>
+        <v>0.956051622925521</v>
       </c>
       <c r="G70" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H70" s="8" t="n">
-        <v>44.9144035069678</v>
+        <v>44.6997781614755</v>
       </c>
       <c r="I70" s="9" t="n">
-        <v>48.4278491496148</v>
+        <v>48.6402416403473</v>
       </c>
       <c r="J70" s="10" t="n">
-        <v>47.4467299509115</v>
+        <v>47.459770578347</v>
       </c>
       <c r="K70" s="11" t="n">
-        <v>44.7529298706768</v>
+        <v>44.367897070454</v>
       </c>
       <c r="L70" s="12" t="n">
-        <v>44.7529298706768</v>
+        <v>44.367897070454</v>
       </c>
       <c r="M70" s="13" t="n">
-        <v>45.0939949690738</v>
+        <v>44.9266973568139</v>
       </c>
       <c r="N70" s="14" t="n">
-        <v>45.0939949690738</v>
+        <v>44.9266973568139</v>
       </c>
       <c r="O70" s="15" t="n">
-        <v>-0.000858902748456157</v>
+        <v>-0.00558300109673275</v>
       </c>
       <c r="P70" s="16" t="n">
-        <v>-0.0041009664248487</v>
+        <v>-0.00646226437776443</v>
       </c>
       <c r="Q70" s="17" t="n">
-        <v>-0.00085853399707192</v>
+        <v>-0.00556744510927187</v>
       </c>
       <c r="R70" s="18" t="n">
-        <v>1.00399852715573</v>
+        <v>1.00507651725963</v>
       </c>
       <c r="S70" s="19" t="n">
-        <v>0.931158326477784</v>
+        <v>0.923652840563747</v>
       </c>
     </row>
     <row r="71">
@@ -5566,46 +5566,46 @@
         <v>48.256</v>
       </c>
       <c r="F71" s="6" t="n">
-        <v>1.04768520835905</v>
+        <v>1.05025285950115</v>
       </c>
       <c r="G71" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H71" s="8" t="n">
-        <v>45.6321314072373</v>
+        <v>45.4643174680573</v>
       </c>
       <c r="I71" s="9" t="n">
-        <v>48.1788063325947</v>
+        <v>48.4496627959644</v>
       </c>
       <c r="J71" s="10" t="n">
-        <v>47.4327123202288</v>
+        <v>47.4997125663336</v>
       </c>
       <c r="K71" s="11" t="n">
-        <v>46.0596366303401</v>
+        <v>45.9470303398371</v>
       </c>
       <c r="L71" s="12" t="n">
-        <v>46.0596366303401</v>
+        <v>45.9470303398371</v>
       </c>
       <c r="M71" s="13" t="n">
-        <v>45.86972808298</v>
+        <v>45.7803951208006</v>
       </c>
       <c r="N71" s="14" t="n">
-        <v>45.86972808298</v>
+        <v>45.7803951208006</v>
       </c>
       <c r="O71" s="15" t="n">
-        <v>0.0170562921999201</v>
+        <v>0.0188237313815995</v>
       </c>
       <c r="P71" s="16" t="n">
-        <v>0.0370768961577452</v>
+        <v>0.0357521692307843</v>
       </c>
       <c r="Q71" s="17" t="n">
-        <v>0.0172025812846741</v>
+        <v>0.0190020147086827</v>
       </c>
       <c r="R71" s="18" t="n">
-        <v>1.00520678452694</v>
+        <v>1.00695221374357</v>
       </c>
       <c r="S71" s="19" t="n">
-        <v>0.952072738505094</v>
+        <v>0.944906372487981</v>
       </c>
     </row>
     <row r="72">
@@ -5625,46 +5625,46 @@
         <v>46.223</v>
       </c>
       <c r="F72" s="6" t="n">
-        <v>0.991767082311865</v>
+        <v>0.986414258247434</v>
       </c>
       <c r="G72" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H72" s="8" t="n">
-        <v>47.075539137089</v>
+        <v>47.4950751949954</v>
       </c>
       <c r="I72" s="9" t="n">
-        <v>47.9452106522651</v>
+        <v>48.2813343335998</v>
       </c>
       <c r="J72" s="10" t="n">
-        <v>47.4909112266628</v>
+        <v>47.6294538599883</v>
       </c>
       <c r="K72" s="11" t="n">
-        <v>46.6067092005631</v>
+        <v>46.8596227330742</v>
       </c>
       <c r="L72" s="12" t="n">
-        <v>46.6067092005631</v>
+        <v>46.8596227330742</v>
       </c>
       <c r="M72" s="13" t="n">
-        <v>47.341380505153</v>
+        <v>47.6110744054156</v>
       </c>
       <c r="N72" s="14" t="n">
-        <v>47.341380505153</v>
+        <v>47.6110744054156</v>
       </c>
       <c r="O72" s="15" t="n">
-        <v>0.0315793845562982</v>
+        <v>0.0392094444053955</v>
       </c>
       <c r="P72" s="16" t="n">
-        <v>0.0498538818950824</v>
+        <v>0.0534383126178404</v>
       </c>
       <c r="Q72" s="17" t="n">
-        <v>0.0320833038188215</v>
+        <v>0.0399882805682306</v>
       </c>
       <c r="R72" s="18" t="n">
-        <v>1.00564712317558</v>
+        <v>1.00244234186269</v>
       </c>
       <c r="S72" s="19" t="n">
-        <v>0.987405829719019</v>
+        <v>0.986117617969027</v>
       </c>
     </row>
     <row r="73">
@@ -5684,46 +5684,46 @@
         <v>49.692</v>
       </c>
       <c r="F73" s="6" t="n">
-        <v>0.992005444865943</v>
+        <v>0.978612364624617</v>
       </c>
       <c r="G73" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H73" s="8" t="n">
-        <v>50.3312221743726</v>
+        <v>50.4782034642476</v>
       </c>
       <c r="I73" s="9" t="n">
-        <v>47.7213446844831</v>
+        <v>48.1292533144122</v>
       </c>
       <c r="J73" s="10" t="n">
-        <v>47.5835043819804</v>
+        <v>47.8120130283048</v>
       </c>
       <c r="K73" s="11" t="n">
-        <v>50.0924669891457</v>
+        <v>50.7780218156769</v>
       </c>
       <c r="L73" s="12" t="n">
-        <v>50.0924669891457</v>
+        <v>50.7780218156769</v>
       </c>
       <c r="M73" s="13" t="n">
-        <v>50.15546383799</v>
+        <v>50.2839960447601</v>
       </c>
       <c r="N73" s="14" t="n">
-        <v>50.15546383799</v>
+        <v>50.2839960447601</v>
       </c>
       <c r="O73" s="15" t="n">
-        <v>0.0577426932281833</v>
+        <v>0.0546214666413395</v>
       </c>
       <c r="P73" s="16" t="n">
-        <v>0.111287738012878</v>
+        <v>0.113013989427426</v>
       </c>
       <c r="Q73" s="17" t="n">
-        <v>0.059442358942843</v>
+        <v>0.0561407544930435</v>
       </c>
       <c r="R73" s="18" t="n">
-        <v>0.99650796605388</v>
+        <v>0.996152647951802</v>
       </c>
       <c r="S73" s="19" t="n">
-        <v>1.05100692718532</v>
+        <v>1.04476991812592</v>
       </c>
     </row>
     <row r="74">
@@ -5743,46 +5743,46 @@
         <v>51.943</v>
       </c>
       <c r="F74" s="6" t="n">
-        <v>0.964941394489831</v>
+        <v>0.985255820775861</v>
       </c>
       <c r="G74" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H74" s="8" t="n">
-        <v>53.2480756686054</v>
+        <v>52.7557320268819</v>
       </c>
       <c r="I74" s="9" t="n">
-        <v>47.5006544416985</v>
+        <v>47.9865282298102</v>
       </c>
       <c r="J74" s="10" t="n">
-        <v>47.6682484878179</v>
+        <v>48.0065594846424</v>
       </c>
       <c r="K74" s="11" t="n">
-        <v>53.8302121731056</v>
+        <v>52.7203178146122</v>
       </c>
       <c r="L74" s="12" t="n">
-        <v>53.8302121731056</v>
+        <v>52.7203178146122</v>
       </c>
       <c r="M74" s="13" t="n">
-        <v>52.4086300069795</v>
+        <v>52.0016247017322</v>
       </c>
       <c r="N74" s="14" t="n">
-        <v>52.4086300069795</v>
+        <v>52.0016247017322</v>
       </c>
       <c r="O74" s="15" t="n">
-        <v>0.0439438141725794</v>
+        <v>0.0335881059628557</v>
       </c>
       <c r="P74" s="16" t="n">
-        <v>0.16220862762153</v>
+        <v>0.157477129661419</v>
       </c>
       <c r="Q74" s="17" t="n">
-        <v>0.0449236433395883</v>
+        <v>0.034158555247741</v>
       </c>
       <c r="R74" s="18" t="n">
-        <v>0.984235192519439</v>
+        <v>0.985705679815694</v>
       </c>
       <c r="S74" s="19" t="n">
-        <v>1.10332437779999</v>
+        <v>1.08367132651676</v>
       </c>
     </row>
     <row r="75">
@@ -5802,46 +5802,46 @@
         <v>55.609</v>
       </c>
       <c r="F75" s="6" t="n">
-        <v>1.07184376052507</v>
+        <v>1.07378486025823</v>
       </c>
       <c r="G75" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H75" s="8" t="n">
-        <v>51.4455562648867</v>
+        <v>51.0397221751725</v>
       </c>
       <c r="I75" s="9" t="n">
-        <v>47.2780678878016</v>
+        <v>47.8479230515154</v>
       </c>
       <c r="J75" s="10" t="n">
-        <v>47.7154450588474</v>
+        <v>48.1870926862971</v>
       </c>
       <c r="K75" s="11" t="n">
-        <v>51.8816286925611</v>
+        <v>51.7878413620274</v>
       </c>
       <c r="L75" s="12" t="n">
-        <v>51.8816286925611</v>
+        <v>51.7878413620274</v>
       </c>
       <c r="M75" s="13" t="n">
-        <v>50.9575037053582</v>
+        <v>50.7239039463611</v>
       </c>
       <c r="N75" s="14" t="n">
-        <v>50.9575037053582</v>
+        <v>50.7239039463611</v>
       </c>
       <c r="O75" s="15" t="n">
-        <v>-0.0280792478655594</v>
+        <v>-0.0248776846392426</v>
       </c>
       <c r="P75" s="16" t="n">
-        <v>0.110917937276066</v>
+        <v>0.107983096531083</v>
       </c>
       <c r="Q75" s="17" t="n">
-        <v>-0.0276886898479891</v>
+        <v>-0.0245707852918009</v>
       </c>
       <c r="R75" s="18" t="n">
-        <v>0.990513222230205</v>
+        <v>0.993812305095873</v>
       </c>
       <c r="S75" s="19" t="n">
-        <v>1.07782542692499</v>
+        <v>1.06010670289177</v>
       </c>
     </row>
     <row r="76">
@@ -5861,46 +5861,46 @@
         <v>44.919</v>
       </c>
       <c r="F76" s="6" t="n">
-        <v>0.971504245057564</v>
+        <v>0.963934997362587</v>
       </c>
       <c r="G76" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H76" s="8" t="n">
-        <v>46.9229707211691</v>
+        <v>47.2468635865499</v>
       </c>
       <c r="I76" s="9" t="n">
-        <v>47.0524689602646</v>
+        <v>47.71116036974</v>
       </c>
       <c r="J76" s="10" t="n">
-        <v>47.7262054281675</v>
+        <v>48.351180882215</v>
       </c>
       <c r="K76" s="11" t="n">
-        <v>46.2365452632051</v>
+        <v>46.5996152467775</v>
       </c>
       <c r="L76" s="12" t="n">
-        <v>46.2365452632051</v>
+        <v>46.5996152467775</v>
       </c>
       <c r="M76" s="13" t="n">
-        <v>47.2946002443884</v>
+        <v>47.7376012359495</v>
       </c>
       <c r="N76" s="14" t="n">
-        <v>47.2946002443884</v>
+        <v>47.7376012359495</v>
       </c>
       <c r="O76" s="15" t="n">
-        <v>-0.0745958954473433</v>
+        <v>-0.0606779044890397</v>
       </c>
       <c r="P76" s="16" t="n">
-        <v>-0.000988147372665837</v>
+        <v>0.00265750840773848</v>
       </c>
       <c r="Q76" s="17" t="n">
-        <v>-0.0718815325442367</v>
+        <v>-0.0588736764735138</v>
       </c>
       <c r="R76" s="18" t="n">
-        <v>1.00791999137113</v>
+        <v>1.01038667145599</v>
       </c>
       <c r="S76" s="19" t="n">
-        <v>1.00514598467359</v>
+        <v>1.0005541861905</v>
       </c>
     </row>
     <row r="77">
@@ -5920,80 +5920,106 @@
         <v>43.842</v>
       </c>
       <c r="F77" s="6" t="n">
-        <v>0.978099037828492</v>
+        <v>0.953847274649465</v>
       </c>
       <c r="G77" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H77" s="8" t="n">
-        <v>45.1194985311692</v>
+        <v>46.6318747844905</v>
       </c>
       <c r="I77" s="9" t="n">
-        <v>46.8256188220629</v>
+        <v>47.5764252236404</v>
       </c>
       <c r="J77" s="10" t="n">
-        <v>47.7224718470452</v>
+        <v>48.5143960647205</v>
       </c>
       <c r="K77" s="11" t="n">
-        <v>44.8236817585824</v>
+        <v>45.9633330882156</v>
       </c>
       <c r="L77" s="12" t="n">
-        <v>44.8236817585824</v>
+        <v>45.9633330882156</v>
       </c>
       <c r="M77" s="13" t="n">
-        <v>45.2946362601233</v>
+        <v>47.0995159920482</v>
       </c>
       <c r="N77" s="14" t="n">
-        <v>45.2946362601233</v>
+        <v>47.0995159920482</v>
       </c>
       <c r="O77" s="15" t="n">
-        <v>-0.0432075086182897</v>
+        <v>-0.0134566484368823</v>
       </c>
       <c r="P77" s="16" t="n">
-        <v>-0.0969152153306347</v>
+        <v>-0.0633298922758089</v>
       </c>
       <c r="Q77" s="17" t="n">
-        <v>-0.0422873641796434</v>
+        <v>-0.0133665125054656</v>
       </c>
       <c r="R77" s="18" t="n">
-        <v>1.00388164174372</v>
+        <v>1.01002835956562</v>
       </c>
       <c r="S77" s="19" t="n">
-        <v>0.967304595209787</v>
+        <v>0.98997593389267</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s">
         <v>129</v>
       </c>
-      <c r="B78" s="2"/>
+      <c r="B78" s="2" t="n">
+        <v>50.478</v>
+      </c>
       <c r="C78" s="3" t="n">
-        <v>45.174846991025</v>
+        <v>50.478</v>
       </c>
       <c r="D78" s="4" t="n">
-        <v>53.4823964439734</v>
+        <v>50.478</v>
       </c>
       <c r="E78" s="5" t="n">
-        <v>38.1577292034843</v>
+        <v>50.478</v>
       </c>
       <c r="F78" s="6" t="n">
-        <v>0.977317713596562</v>
-      </c>
-      <c r="G78" s="7"/>
-      <c r="H78" s="8"/>
-      <c r="I78" s="9"/>
-      <c r="J78" s="10"/>
-      <c r="K78" s="11"/>
-      <c r="L78" s="12"/>
-      <c r="M78" s="13"/>
+        <v>1.01215552009734</v>
+      </c>
+      <c r="G78" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H78" s="8" t="n">
+        <v>48.9975486788071</v>
+      </c>
+      <c r="I78" s="9" t="n">
+        <v>47.4432079366711</v>
+      </c>
+      <c r="J78" s="10" t="n">
+        <v>48.6835523979612</v>
+      </c>
+      <c r="K78" s="11" t="n">
+        <v>49.8717825449843</v>
+      </c>
+      <c r="L78" s="12" t="n">
+        <v>49.8717825449843</v>
+      </c>
+      <c r="M78" s="13" t="n">
+        <v>48.5689660593947</v>
+      </c>
       <c r="N78" s="14" t="n">
-        <v>46.2232970532991</v>
-      </c>
-      <c r="O78" s="15"/>
-      <c r="P78" s="16"/>
-      <c r="Q78" s="17"/>
-      <c r="R78" s="18"/>
-      <c r="S78" s="19"/>
+        <v>48.5689660593947</v>
+      </c>
+      <c r="O78" s="15" t="n">
+        <v>0.030722043700248</v>
+      </c>
+      <c r="P78" s="16" t="n">
+        <v>-0.0660106037460623</v>
+      </c>
+      <c r="Q78" s="17" t="n">
+        <v>0.0311988358350557</v>
+      </c>
+      <c r="R78" s="18" t="n">
+        <v>0.99125297834343</v>
+      </c>
+      <c r="S78" s="19" t="n">
+        <v>1.02372854137997</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="s">
@@ -6001,16 +6027,16 @@
       </c>
       <c r="B79" s="2"/>
       <c r="C79" s="3" t="n">
-        <v>48.779394229133</v>
+        <v>53.3567297272142</v>
       </c>
       <c r="D79" s="4" t="n">
-        <v>60.8343835218166</v>
+        <v>63.2077361022718</v>
       </c>
       <c r="E79" s="5" t="n">
-        <v>39.113231097474</v>
+        <v>45.0410152734556</v>
       </c>
       <c r="F79" s="6" t="n">
-        <v>1.08430201466051</v>
+        <v>1.08420320387331</v>
       </c>
       <c r="G79" s="7"/>
       <c r="H79" s="8"/>
@@ -6020,7 +6046,7 @@
       <c r="L79" s="12"/>
       <c r="M79" s="13"/>
       <c r="N79" s="14" t="n">
-        <v>44.986907309589</v>
+        <v>49.2128500788391</v>
       </c>
       <c r="O79" s="15"/>
       <c r="P79" s="16"/>
@@ -6034,16 +6060,16 @@
       </c>
       <c r="B80" s="2"/>
       <c r="C80" s="3" t="n">
-        <v>41.1188859496109</v>
+        <v>44.408156163364</v>
       </c>
       <c r="D80" s="4" t="n">
-        <v>53.4763814959196</v>
+        <v>55.0594388643171</v>
       </c>
       <c r="E80" s="5" t="n">
-        <v>31.6170005232333</v>
+        <v>35.8173707271068</v>
       </c>
       <c r="F80" s="6" t="n">
-        <v>0.958990209941539</v>
+        <v>0.949284620925011</v>
       </c>
       <c r="G80" s="7"/>
       <c r="H80" s="8"/>
@@ -6053,7 +6079,7 @@
       <c r="L80" s="12"/>
       <c r="M80" s="13"/>
       <c r="N80" s="14" t="n">
-        <v>42.8772739526898</v>
+        <v>46.7806548051852</v>
       </c>
       <c r="O80" s="15"/>
       <c r="P80" s="16"/>
@@ -6067,16 +6093,16 @@
       </c>
       <c r="B81" s="2"/>
       <c r="C81" s="3" t="n">
-        <v>40.7615352549826</v>
+        <v>43.8855026246574</v>
       </c>
       <c r="D81" s="4" t="n">
-        <v>54.9603691374794</v>
+        <v>56.4889056877402</v>
       </c>
       <c r="E81" s="5" t="n">
-        <v>30.2309242535663</v>
+        <v>34.0940812566811</v>
       </c>
       <c r="F81" s="6" t="n">
-        <v>0.97516304352839</v>
+        <v>0.944965943186777</v>
       </c>
       <c r="G81" s="7"/>
       <c r="H81" s="8"/>
@@ -6086,7 +6112,7 @@
       <c r="L81" s="12"/>
       <c r="M81" s="13"/>
       <c r="N81" s="14" t="n">
-        <v>41.7997129049281</v>
+        <v>46.4413590151822</v>
       </c>
       <c r="O81" s="15"/>
       <c r="P81" s="16"/>
@@ -6099,10 +6125,18 @@
         <v>133</v>
       </c>
       <c r="B82" s="2"/>
-      <c r="C82" s="3"/>
-      <c r="D82" s="4"/>
-      <c r="E82" s="5"/>
-      <c r="F82" s="6"/>
+      <c r="C82" s="3" t="n">
+        <v>49.6001833426889</v>
+      </c>
+      <c r="D82" s="4" t="n">
+        <v>65.9595144156489</v>
+      </c>
+      <c r="E82" s="5" t="n">
+        <v>37.2983065358146</v>
+      </c>
+      <c r="F82" s="6" t="n">
+        <v>1.02810051962122</v>
+      </c>
       <c r="G82" s="7"/>
       <c r="H82" s="8"/>
       <c r="I82" s="9"/>
@@ -6110,7 +6144,9 @@
       <c r="K82" s="11"/>
       <c r="L82" s="12"/>
       <c r="M82" s="13"/>
-      <c r="N82" s="14"/>
+      <c r="N82" s="14" t="n">
+        <v>48.2444881566279</v>
+      </c>
       <c r="O82" s="15"/>
       <c r="P82" s="16"/>
       <c r="Q82" s="17"/>
@@ -6608,7 +6644,7 @@
         <v>170</v>
       </c>
       <c r="B5" s="1" t="n">
-        <v>0.268324339798877</v>
+        <v>0.267073623824962</v>
       </c>
     </row>
     <row r="6">
@@ -6616,7 +6652,7 @@
         <v>171</v>
       </c>
       <c r="B6" s="1" t="n">
-        <v>0.0923100736222232</v>
+        <v>0.0917729098765798</v>
       </c>
     </row>
     <row r="7">
@@ -6624,7 +6660,7 @@
         <v>172</v>
       </c>
       <c r="B7" s="1" t="n">
-        <v>-0.0904329959563043</v>
+        <v>-0.101591197816669</v>
       </c>
     </row>
     <row r="8">
@@ -6632,7 +6668,7 @@
         <v>173</v>
       </c>
       <c r="B8" s="1" t="n">
-        <v>-0.021206475320898</v>
+        <v>-0.0378731121203328</v>
       </c>
     </row>
     <row r="9">
@@ -6640,7 +6676,7 @@
         <v>174</v>
       </c>
       <c r="B9" s="1" t="n">
-        <v>0.158706776034639</v>
+        <v>0.153567091693256</v>
       </c>
     </row>
     <row r="10">
@@ -6648,7 +6684,7 @@
         <v>175</v>
       </c>
       <c r="B10" s="1" t="n">
-        <v>0.165413094411826</v>
+        <v>0.180422989245343</v>
       </c>
     </row>
     <row r="11">
@@ -6656,7 +6692,7 @@
         <v>176</v>
       </c>
       <c r="B11" s="1" t="n">
-        <v>-0.0237510641572777</v>
+        <v>-0.0153338005175825</v>
       </c>
     </row>
     <row r="12">
@@ -6664,7 +6700,7 @@
         <v>177</v>
       </c>
       <c r="B12" s="1" t="n">
-        <v>-0.208647825294298</v>
+        <v>-0.206910441047629</v>
       </c>
     </row>
     <row r="13">
@@ -6672,7 +6708,7 @@
         <v>178</v>
       </c>
       <c r="B13" s="1" t="n">
-        <v>-0.178440807103116</v>
+        <v>-0.15026699368972</v>
       </c>
     </row>
     <row r="14">
